--- a/Programmes Seguimiento LE_2.xlsx
+++ b/Programmes Seguimiento LE_2.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372">
   <si>
     <t/>
   </si>
@@ -1081,6 +1081,57 @@
   </si>
   <si>
     <t>24:09:13</t>
+  </si>
+  <si>
+    <t>06:58:10</t>
+  </si>
+  <si>
+    <t>08:01:12</t>
+  </si>
+  <si>
+    <t>08:01:13</t>
+  </si>
+  <si>
+    <t>08:59:56</t>
+  </si>
+  <si>
+    <t>08:59:57</t>
+  </si>
+  <si>
+    <t>13:29:56</t>
+  </si>
+  <si>
+    <t>15:29:55</t>
+  </si>
+  <si>
+    <t>15:29:56</t>
+  </si>
+  <si>
+    <t>20:29:41</t>
+  </si>
+  <si>
+    <t>20:29:42</t>
+  </si>
+  <si>
+    <t>21:29:46</t>
+  </si>
+  <si>
+    <t>21:29:47</t>
+  </si>
+  <si>
+    <t>22:29:54</t>
+  </si>
+  <si>
+    <t>22:29:55</t>
+  </si>
+  <si>
+    <t>23:06:14</t>
+  </si>
+  <si>
+    <t>23:06:15</t>
+  </si>
+  <si>
+    <t>24:02:04</t>
   </si>
 </sst>
 </file>
@@ -1506,7 +1557,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:H563"/>
+  <dimension ref="A2:H577"/>
   <sheetData>
     <row r="2" ht="15">
       <c r="A2" s="1" t="s">
@@ -14435,6 +14486,328 @@
       </c>
       <c r="G563" s="5">
         <v>1049.84653</v>
+      </c>
+    </row>
+    <row r="564" ht="15">
+      <c r="A564" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B564" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C564" s="2">
+        <v>46062</v>
+      </c>
+      <c r="D564" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="E564" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="F564" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G564" s="5">
+        <v>962.17147</v>
+      </c>
+    </row>
+    <row r="565" ht="15">
+      <c r="A565" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B565" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C565" s="2">
+        <v>46062</v>
+      </c>
+      <c r="D565" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="E565" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="F565" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G565" s="5">
+        <v>1153.275526</v>
+      </c>
+    </row>
+    <row r="566" ht="15">
+      <c r="A566" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B566" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C566" s="2">
+        <v>46062</v>
+      </c>
+      <c r="D566" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="E566" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="F566" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G566" s="5">
+        <v>1358.2</v>
+      </c>
+    </row>
+    <row r="567" ht="15">
+      <c r="A567" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B567" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C567" s="2">
+        <v>46062</v>
+      </c>
+      <c r="D567" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="E567" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="F567" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G567" s="5">
+        <v>1483.888807</v>
+      </c>
+    </row>
+    <row r="568" ht="15">
+      <c r="A568" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B568" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C568" s="2">
+        <v>46062</v>
+      </c>
+      <c r="D568" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="E568" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="F568" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G568" s="5">
+        <v>1574.513733</v>
+      </c>
+    </row>
+    <row r="569" ht="15">
+      <c r="A569" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B569" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C569" s="2">
+        <v>46062</v>
+      </c>
+      <c r="D569" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="E569" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="F569" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G569" s="5">
+        <v>1980.194758</v>
+      </c>
+    </row>
+    <row r="570" ht="15">
+      <c r="A570" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B570" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C570" s="2">
+        <v>46062</v>
+      </c>
+      <c r="D570" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="E570" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="F570" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G570" s="5">
+        <v>2478.350255</v>
+      </c>
+    </row>
+    <row r="571" ht="15">
+      <c r="A571" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B571" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C571" s="2">
+        <v>46062</v>
+      </c>
+      <c r="D571" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="E571" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="F571" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G571" s="5">
+        <v>3037.936153</v>
+      </c>
+    </row>
+    <row r="572" ht="15">
+      <c r="A572" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B572" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C572" s="2">
+        <v>46062</v>
+      </c>
+      <c r="D572" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="E572" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="F572" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G572" s="5">
+        <v>3905.78662</v>
+      </c>
+    </row>
+    <row r="573" ht="15">
+      <c r="A573" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B573" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C573" s="2">
+        <v>46062</v>
+      </c>
+      <c r="D573" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="E573" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="F573" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G573" s="5">
+        <v>4649.970492</v>
+      </c>
+    </row>
+    <row r="574" ht="15">
+      <c r="A574" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B574" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C574" s="2">
+        <v>46062</v>
+      </c>
+      <c r="D574" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="E574" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="F574" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="G574" s="5">
+        <v>4585.097246</v>
+      </c>
+    </row>
+    <row r="575" ht="15">
+      <c r="A575" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B575" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C575" s="2">
+        <v>46062</v>
+      </c>
+      <c r="D575" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="E575" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="F575" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="G575" s="5">
+        <v>4453.263299</v>
+      </c>
+    </row>
+    <row r="576" ht="15">
+      <c r="A576" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B576" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C576" s="2">
+        <v>46062</v>
+      </c>
+      <c r="D576" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="E576" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="F576" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G576" s="5">
+        <v>3012.233895</v>
+      </c>
+    </row>
+    <row r="577" ht="15">
+      <c r="A577" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B577" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C577" s="2">
+        <v>46062</v>
+      </c>
+      <c r="D577" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="E577" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="F577" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G577" s="5">
+        <v>838.082097</v>
       </c>
     </row>
   </sheetData>

--- a/Programmes Seguimiento LE_2.xlsx
+++ b/Programmes Seguimiento LE_2.xlsx
@@ -1,22 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="6115"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://televisaunivision-my.sharepoint.com/personal/hector_copca_televisaunivision_com/Documents/Documentos/seguimiento LE/Seguimiento-LE/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_ABEEBD95B0BFB3B9460239F99892A4368643D113" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BA492D0-2EF0-42A8-B98B-C49B38A96B35}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="45" windowWidth="25875" windowHeight="15915" activeTab="0">
-</workbookView>
+    <workbookView xWindow="-23148" yWindow="-2340" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="0.001"/>
-  <oleSize ref="A1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2885" uniqueCount="382">
   <si>
     <t/>
   </si>
@@ -1167,53 +1171,42 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="50" formatCode="dd/MM/yyyy"/>
-    <numFmt numFmtId="51" formatCode="0.000000"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="none"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color indexed="9"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color indexed="9"/>
-      <sz val="11"/>
-      <scheme val="none"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color indexed="8"/>
-      <sz val="11"/>
-      <scheme val="none"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="000000"/>
-      <sz val="11"/>
-      <scheme val="none"/>
     </font>
   </fonts>
   <fills count="5">
     <fill>
-      <patternFill>
-        <fgColor auto="1"/>
-        <bgColor auto="1"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <fgColor auto="1"/>
-        <bgColor auto="1"/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1235,74 +1228,52 @@
     </fill>
   </fills>
   <borders count="2">
-    <border outline="0">
-      <left>
-        <color auto="1"/>
-      </left>
-      <right>
-        <color auto="1"/>
-      </right>
-      <top>
-        <color auto="1"/>
-      </top>
-      <bottom>
-        <color auto="1"/>
-      </bottom>
-      <diagonal>
-        <color auto="1"/>
-      </diagonal>
-      <vertical>
-        <color auto="1"/>
-      </vertical>
-      <horizontal>
-        <color auto="1"/>
-      </horizontal>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
-    <border outline="0">
-      <left>
-        <color indexed="64"/>
-      </left>
-      <right>
-        <color indexed="64"/>
-      </right>
-      <top>
-        <color indexed="64"/>
-      </top>
-      <bottom>
-        <color indexed="64"/>
-      </bottom>
-      <diagonal>
-        <color auto="1"/>
-      </diagonal>
-      <vertical>
-        <color auto="1"/>
-      </vertical>
-      <horizontal>
-        <color auto="1"/>
-      </horizontal>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="50" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1"/>
-    <xf numFmtId="51" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1340,15 +1311,15 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="?? ?????"/>
-        <a:font script="Hang" typeface="?? ??"/>
-        <a:font script="Hans" typeface="??"/>
-        <a:font script="Hant" typeface="????"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -1374,15 +1345,16 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="?? ?????"/>
-        <a:font script="Hang" typeface="?? ??"/>
-        <a:font script="Hans" typeface="??"/>
-        <a:font script="Hant" typeface="????"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -1408,9 +1380,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1583,13 +1556,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H577"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="7" width="11.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" ht="15">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1615,7 +1592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" ht="15">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -1638,7 +1615,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" ht="15">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>9</v>
       </c>
@@ -1658,10 +1635,10 @@
         <v>13</v>
       </c>
       <c r="G4" s="5">
-        <v>899.895067</v>
-      </c>
-    </row>
-    <row r="5" ht="15">
+        <v>899.89506700000004</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>9</v>
       </c>
@@ -1681,10 +1658,10 @@
         <v>16</v>
       </c>
       <c r="G5" s="5">
-        <v>1318.734002</v>
-      </c>
-    </row>
-    <row r="6" ht="15">
+        <v>1318.7340019999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>9</v>
       </c>
@@ -1707,7 +1684,7 @@
         <v>1737.04973</v>
       </c>
     </row>
-    <row r="7" ht="15">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -1727,10 +1704,10 @@
         <v>22</v>
       </c>
       <c r="G7" s="5">
-        <v>1569.797355</v>
-      </c>
-    </row>
-    <row r="8" ht="15">
+        <v>1569.7973549999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>9</v>
       </c>
@@ -1750,10 +1727,10 @@
         <v>25</v>
       </c>
       <c r="G8" s="5">
-        <v>1822.811534</v>
-      </c>
-    </row>
-    <row r="9" ht="15">
+        <v>1822.8115339999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>9</v>
       </c>
@@ -1773,10 +1750,10 @@
         <v>28</v>
       </c>
       <c r="G9" s="5">
-        <v>2234.424247</v>
-      </c>
-    </row>
-    <row r="10" ht="15">
+        <v>2234.4242469999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
@@ -1796,10 +1773,10 @@
         <v>31</v>
       </c>
       <c r="G10" s="5">
-        <v>2713.013601</v>
-      </c>
-    </row>
-    <row r="11" ht="15">
+        <v>2713.0136010000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>9</v>
       </c>
@@ -1822,7 +1799,7 @@
         <v>2927.810207</v>
       </c>
     </row>
-    <row r="12" ht="15">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>9</v>
       </c>
@@ -1842,10 +1819,10 @@
         <v>37</v>
       </c>
       <c r="G12" s="5">
-        <v>4170.38086</v>
-      </c>
-    </row>
-    <row r="13" ht="15">
+        <v>4170.3808600000002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>9</v>
       </c>
@@ -1865,10 +1842,10 @@
         <v>40</v>
       </c>
       <c r="G13" s="5">
-        <v>4828.519435</v>
-      </c>
-    </row>
-    <row r="14" ht="15">
+        <v>4828.5194350000002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>9</v>
       </c>
@@ -1888,10 +1865,10 @@
         <v>43</v>
       </c>
       <c r="G14" s="5">
-        <v>4324.84466</v>
-      </c>
-    </row>
-    <row r="15" ht="15">
+        <v>4324.8446599999997</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>9</v>
       </c>
@@ -1911,10 +1888,10 @@
         <v>46</v>
       </c>
       <c r="G15" s="5">
-        <v>4698.313801</v>
-      </c>
-    </row>
-    <row r="16" ht="15">
+        <v>4698.3138010000002</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>9</v>
       </c>
@@ -1934,10 +1911,10 @@
         <v>49</v>
       </c>
       <c r="G16" s="5">
-        <v>3156.966596</v>
-      </c>
-    </row>
-    <row r="17" ht="15">
+        <v>3156.9665960000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>9</v>
       </c>
@@ -1960,7 +1937,7 @@
         <v>1580.542856</v>
       </c>
     </row>
-    <row r="18" ht="15">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>9</v>
       </c>
@@ -1980,10 +1957,10 @@
         <v>13</v>
       </c>
       <c r="G18" s="5">
-        <v>991.330746</v>
-      </c>
-    </row>
-    <row r="19" ht="15">
+        <v>991.33074599999998</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>9</v>
       </c>
@@ -2003,10 +1980,10 @@
         <v>16</v>
       </c>
       <c r="G19" s="5">
-        <v>989.505004</v>
-      </c>
-    </row>
-    <row r="20" ht="15">
+        <v>989.50500399999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>9</v>
       </c>
@@ -2026,10 +2003,10 @@
         <v>19</v>
       </c>
       <c r="G20" s="5">
-        <v>1753.14613</v>
-      </c>
-    </row>
-    <row r="21" ht="15">
+        <v>1753.1461300000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>9</v>
       </c>
@@ -2052,7 +2029,7 @@
         <v>1748.600318</v>
       </c>
     </row>
-    <row r="22" ht="15">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>9</v>
       </c>
@@ -2072,10 +2049,10 @@
         <v>25</v>
       </c>
       <c r="G22" s="5">
-        <v>1909.546444</v>
-      </c>
-    </row>
-    <row r="23" ht="15">
+        <v>1909.5464440000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>9</v>
       </c>
@@ -2095,10 +2072,10 @@
         <v>28</v>
       </c>
       <c r="G23" s="5">
-        <v>2137.910336</v>
-      </c>
-    </row>
-    <row r="24" ht="15">
+        <v>2137.9103359999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>9</v>
       </c>
@@ -2118,10 +2095,10 @@
         <v>31</v>
       </c>
       <c r="G24" s="5">
-        <v>2541.401533</v>
-      </c>
-    </row>
-    <row r="25" ht="15">
+        <v>2541.4015330000002</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>9</v>
       </c>
@@ -2141,10 +2118,10 @@
         <v>34</v>
       </c>
       <c r="G25" s="5">
-        <v>3180.646353</v>
-      </c>
-    </row>
-    <row r="26" ht="15">
+        <v>3180.6463530000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>9</v>
       </c>
@@ -2164,10 +2141,10 @@
         <v>37</v>
       </c>
       <c r="G26" s="5">
-        <v>3947.517403</v>
-      </c>
-    </row>
-    <row r="27" ht="15">
+        <v>3947.5174029999998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>9</v>
       </c>
@@ -2187,10 +2164,10 @@
         <v>40</v>
       </c>
       <c r="G27" s="5">
-        <v>4279.893542</v>
-      </c>
-    </row>
-    <row r="28" ht="15">
+        <v>4279.8935419999998</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>9</v>
       </c>
@@ -2210,10 +2187,10 @@
         <v>43</v>
       </c>
       <c r="G28" s="5">
-        <v>4191.338699</v>
-      </c>
-    </row>
-    <row r="29" ht="15">
+        <v>4191.3386989999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>9</v>
       </c>
@@ -2236,7 +2213,7 @@
         <v>4558.17022</v>
       </c>
     </row>
-    <row r="30" ht="15">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>9</v>
       </c>
@@ -2256,10 +2233,10 @@
         <v>49</v>
       </c>
       <c r="G30" s="5">
-        <v>2614.732271</v>
-      </c>
-    </row>
-    <row r="31" ht="15">
+        <v>2614.7322709999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>9</v>
       </c>
@@ -2282,7 +2259,7 @@
         <v>1054.820729</v>
       </c>
     </row>
-    <row r="32" ht="15">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>9</v>
       </c>
@@ -2302,10 +2279,10 @@
         <v>13</v>
       </c>
       <c r="G32" s="5">
-        <v>896.097108</v>
-      </c>
-    </row>
-    <row r="33" ht="15">
+        <v>896.09710800000005</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>9</v>
       </c>
@@ -2328,7 +2305,7 @@
         <v>1365.334513</v>
       </c>
     </row>
-    <row r="34" ht="15">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>9</v>
       </c>
@@ -2348,10 +2325,10 @@
         <v>19</v>
       </c>
       <c r="G34" s="5">
-        <v>1735.050243</v>
-      </c>
-    </row>
-    <row r="35" ht="15">
+        <v>1735.0502429999999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>9</v>
       </c>
@@ -2371,10 +2348,10 @@
         <v>22</v>
       </c>
       <c r="G35" s="5">
-        <v>1647.447796</v>
-      </c>
-    </row>
-    <row r="36" ht="15">
+        <v>1647.4477959999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>9</v>
       </c>
@@ -2397,7 +2374,7 @@
         <v>2034.532224</v>
       </c>
     </row>
-    <row r="37" ht="15">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>9</v>
       </c>
@@ -2417,10 +2394,10 @@
         <v>28</v>
       </c>
       <c r="G37" s="5">
-        <v>2473.019188</v>
-      </c>
-    </row>
-    <row r="38" ht="15">
+        <v>2473.0191880000002</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
         <v>9</v>
       </c>
@@ -2440,10 +2417,10 @@
         <v>31</v>
       </c>
       <c r="G38" s="5">
-        <v>2612.069014</v>
-      </c>
-    </row>
-    <row r="39" ht="15">
+        <v>2612.0690140000002</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>9</v>
       </c>
@@ -2463,10 +2440,10 @@
         <v>34</v>
       </c>
       <c r="G39" s="5">
-        <v>3246.48394</v>
-      </c>
-    </row>
-    <row r="40" ht="15">
+        <v>3246.4839400000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>9</v>
       </c>
@@ -2486,10 +2463,10 @@
         <v>37</v>
       </c>
       <c r="G40" s="5">
-        <v>4641.952494</v>
-      </c>
-    </row>
-    <row r="41" ht="15">
+        <v>4641.9524940000001</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
         <v>9</v>
       </c>
@@ -2509,10 +2486,10 @@
         <v>40</v>
       </c>
       <c r="G41" s="5">
-        <v>4759.393743</v>
-      </c>
-    </row>
-    <row r="42" ht="15">
+        <v>4759.3937429999996</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
         <v>9</v>
       </c>
@@ -2535,7 +2512,7 @@
         <v>4535.74442</v>
       </c>
     </row>
-    <row r="43" ht="15">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
         <v>9</v>
       </c>
@@ -2555,10 +2532,10 @@
         <v>46</v>
       </c>
       <c r="G43" s="5">
-        <v>4461.412231</v>
-      </c>
-    </row>
-    <row r="44" ht="15">
+        <v>4461.4122310000002</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
         <v>9</v>
       </c>
@@ -2578,10 +2555,10 @@
         <v>49</v>
       </c>
       <c r="G44" s="5">
-        <v>2644.124604</v>
-      </c>
-    </row>
-    <row r="45" ht="15">
+        <v>2644.1246040000001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>9</v>
       </c>
@@ -2601,10 +2578,10 @@
         <v>52</v>
       </c>
       <c r="G45" s="5">
-        <v>1403.958497</v>
-      </c>
-    </row>
-    <row r="46" ht="15">
+        <v>1403.9584970000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
         <v>9</v>
       </c>
@@ -2624,10 +2601,10 @@
         <v>13</v>
       </c>
       <c r="G46" s="5">
-        <v>821.699167</v>
-      </c>
-    </row>
-    <row r="47" ht="15">
+        <v>821.69916699999999</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>9</v>
       </c>
@@ -2647,10 +2624,10 @@
         <v>16</v>
       </c>
       <c r="G47" s="5">
-        <v>1107.140957</v>
-      </c>
-    </row>
-    <row r="48" ht="15">
+        <v>1107.1409570000001</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
         <v>9</v>
       </c>
@@ -2673,7 +2650,7 @@
         <v>1629.659101</v>
       </c>
     </row>
-    <row r="49" ht="15">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>9</v>
       </c>
@@ -2696,7 +2673,7 @@
         <v>1643.526781</v>
       </c>
     </row>
-    <row r="50" ht="15">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
         <v>9</v>
       </c>
@@ -2716,10 +2693,10 @@
         <v>25</v>
       </c>
       <c r="G50" s="5">
-        <v>1861.286211</v>
-      </c>
-    </row>
-    <row r="51" ht="15">
+        <v>1861.2862110000001</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>9</v>
       </c>
@@ -2739,10 +2716,10 @@
         <v>28</v>
       </c>
       <c r="G51" s="5">
-        <v>2124.790146</v>
-      </c>
-    </row>
-    <row r="52" ht="15">
+        <v>2124.7901459999998</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
         <v>9</v>
       </c>
@@ -2765,7 +2742,7 @@
         <v>2497.306478</v>
       </c>
     </row>
-    <row r="53" ht="15">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>9</v>
       </c>
@@ -2785,10 +2762,10 @@
         <v>34</v>
       </c>
       <c r="G53" s="5">
-        <v>2692.705337</v>
-      </c>
-    </row>
-    <row r="54" ht="15">
+        <v>2692.7053369999999</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
         <v>9</v>
       </c>
@@ -2811,7 +2788,7 @@
         <v>3789.37041</v>
       </c>
     </row>
-    <row r="55" ht="15">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
         <v>9</v>
       </c>
@@ -2831,10 +2808,10 @@
         <v>40</v>
       </c>
       <c r="G55" s="5">
-        <v>4488.602875</v>
-      </c>
-    </row>
-    <row r="56" ht="15">
+        <v>4488.6028749999996</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
         <v>9</v>
       </c>
@@ -2854,10 +2831,10 @@
         <v>43</v>
       </c>
       <c r="G56" s="5">
-        <v>4218.808906</v>
-      </c>
-    </row>
-    <row r="57" ht="15">
+        <v>4218.8089060000002</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
         <v>9</v>
       </c>
@@ -2877,10 +2854,10 @@
         <v>46</v>
       </c>
       <c r="G57" s="5">
-        <v>4711.398062</v>
-      </c>
-    </row>
-    <row r="58" ht="15">
+        <v>4711.3980620000002</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
         <v>9</v>
       </c>
@@ -2900,10 +2877,10 @@
         <v>49</v>
       </c>
       <c r="G58" s="5">
-        <v>2621.457415</v>
-      </c>
-    </row>
-    <row r="59" ht="15">
+        <v>2621.4574149999999</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
         <v>9</v>
       </c>
@@ -2923,10 +2900,10 @@
         <v>52</v>
       </c>
       <c r="G59" s="5">
-        <v>1559.559144</v>
-      </c>
-    </row>
-    <row r="60" ht="15">
+        <v>1559.5591440000001</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
         <v>9</v>
       </c>
@@ -2949,7 +2926,7 @@
         <v>698.659132</v>
       </c>
     </row>
-    <row r="61" ht="15">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
         <v>9</v>
       </c>
@@ -2972,7 +2949,7 @@
         <v>1133.427762</v>
       </c>
     </row>
-    <row r="62" ht="15">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
         <v>9</v>
       </c>
@@ -2995,7 +2972,7 @@
         <v>1646.911102</v>
       </c>
     </row>
-    <row r="63" ht="15">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
         <v>9</v>
       </c>
@@ -3018,7 +2995,7 @@
         <v>1716.975109</v>
       </c>
     </row>
-    <row r="64" ht="15">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
         <v>9</v>
       </c>
@@ -3041,7 +3018,7 @@
         <v>1789.112789</v>
       </c>
     </row>
-    <row r="65" ht="15">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
         <v>9</v>
       </c>
@@ -3061,10 +3038,10 @@
         <v>28</v>
       </c>
       <c r="G65" s="5">
-        <v>2494.655372</v>
-      </c>
-    </row>
-    <row r="66" ht="15">
+        <v>2494.6553720000002</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
         <v>9</v>
       </c>
@@ -3084,10 +3061,10 @@
         <v>31</v>
       </c>
       <c r="G66" s="5">
-        <v>2696.948267</v>
-      </c>
-    </row>
-    <row r="67" ht="15">
+        <v>2696.9482670000002</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
         <v>9</v>
       </c>
@@ -3110,7 +3087,7 @@
         <v>3084.282874</v>
       </c>
     </row>
-    <row r="68" ht="15">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
         <v>9</v>
       </c>
@@ -3133,7 +3110,7 @@
         <v>4287.736637</v>
       </c>
     </row>
-    <row r="69" ht="15">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
         <v>9</v>
       </c>
@@ -3153,10 +3130,10 @@
         <v>40</v>
       </c>
       <c r="G69" s="5">
-        <v>4917.035955</v>
-      </c>
-    </row>
-    <row r="70" ht="15">
+        <v>4917.0359550000003</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
         <v>9</v>
       </c>
@@ -3176,10 +3153,10 @@
         <v>43</v>
       </c>
       <c r="G70" s="5">
-        <v>4434.697351</v>
-      </c>
-    </row>
-    <row r="71" ht="15">
+        <v>4434.6973509999998</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
         <v>9</v>
       </c>
@@ -3199,10 +3176,10 @@
         <v>46</v>
       </c>
       <c r="G71" s="5">
-        <v>4529.465318</v>
-      </c>
-    </row>
-    <row r="72" ht="15">
+        <v>4529.4653179999996</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
         <v>9</v>
       </c>
@@ -3222,10 +3199,10 @@
         <v>49</v>
       </c>
       <c r="G72" s="5">
-        <v>2879.649317</v>
-      </c>
-    </row>
-    <row r="73" ht="15">
+        <v>2879.6493169999999</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
         <v>9</v>
       </c>
@@ -3245,10 +3222,10 @@
         <v>52</v>
       </c>
       <c r="G73" s="5">
-        <v>1354.868245</v>
-      </c>
-    </row>
-    <row r="74" ht="15">
+        <v>1354.8682449999999</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
         <v>9</v>
       </c>
@@ -3268,10 +3245,10 @@
         <v>13</v>
       </c>
       <c r="G74" s="5">
-        <v>872.718515</v>
-      </c>
-    </row>
-    <row r="75" ht="15">
+        <v>872.71851500000002</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
         <v>9</v>
       </c>
@@ -3294,7 +3271,7 @@
         <v>1317.421034</v>
       </c>
     </row>
-    <row r="76" ht="15">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
         <v>9</v>
       </c>
@@ -3314,10 +3291,10 @@
         <v>19</v>
       </c>
       <c r="G76" s="5">
-        <v>1989.318304</v>
-      </c>
-    </row>
-    <row r="77" ht="15">
+        <v>1989.3183039999999</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
         <v>9</v>
       </c>
@@ -3337,10 +3314,10 @@
         <v>22</v>
       </c>
       <c r="G77" s="5">
-        <v>1839.483049</v>
-      </c>
-    </row>
-    <row r="78" ht="15">
+        <v>1839.4830489999999</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
         <v>9</v>
       </c>
@@ -3363,7 +3340,7 @@
         <v>1762.932354</v>
       </c>
     </row>
-    <row r="79" ht="15">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
         <v>9</v>
       </c>
@@ -3383,10 +3360,10 @@
         <v>28</v>
       </c>
       <c r="G79" s="5">
-        <v>2142.492611</v>
-      </c>
-    </row>
-    <row r="80" ht="15">
+        <v>2142.4926110000001</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
         <v>9</v>
       </c>
@@ -3406,10 +3383,10 @@
         <v>31</v>
       </c>
       <c r="G80" s="5">
-        <v>2398.118425</v>
-      </c>
-    </row>
-    <row r="81" ht="15">
+        <v>2398.1184250000001</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
         <v>9</v>
       </c>
@@ -3429,10 +3406,10 @@
         <v>34</v>
       </c>
       <c r="G81" s="5">
-        <v>2600.474327</v>
-      </c>
-    </row>
-    <row r="82" ht="15">
+        <v>2600.4743269999999</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
         <v>9</v>
       </c>
@@ -3452,10 +3429,10 @@
         <v>37</v>
       </c>
       <c r="G82" s="5">
-        <v>3724.187294</v>
-      </c>
-    </row>
-    <row r="83" ht="15">
+        <v>3724.1872939999998</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
         <v>9</v>
       </c>
@@ -3475,10 +3452,10 @@
         <v>40</v>
       </c>
       <c r="G83" s="5">
-        <v>4239.780958</v>
-      </c>
-    </row>
-    <row r="84" ht="15">
+        <v>4239.7809580000003</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
         <v>9</v>
       </c>
@@ -3498,10 +3475,10 @@
         <v>43</v>
       </c>
       <c r="G84" s="5">
-        <v>3536.623627</v>
-      </c>
-    </row>
-    <row r="85" ht="15">
+        <v>3536.6236269999999</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
         <v>9</v>
       </c>
@@ -3521,10 +3498,10 @@
         <v>46</v>
       </c>
       <c r="G85" s="5">
-        <v>4013.629957</v>
-      </c>
-    </row>
-    <row r="86" ht="15">
+        <v>4013.6299570000001</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
         <v>9</v>
       </c>
@@ -3544,10 +3521,10 @@
         <v>49</v>
       </c>
       <c r="G86" s="5">
-        <v>2395.48301</v>
-      </c>
-    </row>
-    <row r="87" ht="15">
+        <v>2395.4830099999999</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
         <v>9</v>
       </c>
@@ -3570,7 +3547,7 @@
         <v>1012.982616</v>
       </c>
     </row>
-    <row r="88" ht="15">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
         <v>9</v>
       </c>
@@ -3593,7 +3570,7 @@
         <v>615.745137</v>
       </c>
     </row>
-    <row r="89" ht="15">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
         <v>9</v>
       </c>
@@ -3613,10 +3590,10 @@
         <v>16</v>
       </c>
       <c r="G89" s="5">
-        <v>832.28063</v>
-      </c>
-    </row>
-    <row r="90" ht="15">
+        <v>832.28062999999997</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
         <v>9</v>
       </c>
@@ -3636,10 +3613,10 @@
         <v>19</v>
       </c>
       <c r="G90" s="5">
-        <v>1330.662254</v>
-      </c>
-    </row>
-    <row r="91" ht="15">
+        <v>1330.6622540000001</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
         <v>9</v>
       </c>
@@ -3659,10 +3636,10 @@
         <v>22</v>
       </c>
       <c r="G91" s="5">
-        <v>1229.782345</v>
-      </c>
-    </row>
-    <row r="92" ht="15">
+        <v>1229.7823450000001</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
         <v>9</v>
       </c>
@@ -3685,7 +3662,7 @@
         <v>1288.364159</v>
       </c>
     </row>
-    <row r="93" ht="15">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
         <v>9</v>
       </c>
@@ -3705,10 +3682,10 @@
         <v>28</v>
       </c>
       <c r="G93" s="5">
-        <v>1468.009616</v>
-      </c>
-    </row>
-    <row r="94" ht="15">
+        <v>1468.0096160000001</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
         <v>9</v>
       </c>
@@ -3731,7 +3708,7 @@
         <v>1874.710775</v>
       </c>
     </row>
-    <row r="95" ht="15">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
         <v>9</v>
       </c>
@@ -3751,10 +3728,10 @@
         <v>34</v>
       </c>
       <c r="G95" s="5">
-        <v>1853.367034</v>
-      </c>
-    </row>
-    <row r="96" ht="15">
+        <v>1853.3670340000001</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
         <v>9</v>
       </c>
@@ -3774,10 +3751,10 @@
         <v>37</v>
       </c>
       <c r="G96" s="5">
-        <v>2504.677135</v>
-      </c>
-    </row>
-    <row r="97" ht="15">
+        <v>2504.6771349999999</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
         <v>9</v>
       </c>
@@ -3797,10 +3774,10 @@
         <v>40</v>
       </c>
       <c r="G97" s="5">
-        <v>3193.089699</v>
-      </c>
-    </row>
-    <row r="98" ht="15">
+        <v>3193.0896990000001</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
         <v>9</v>
       </c>
@@ -3820,10 +3797,10 @@
         <v>43</v>
       </c>
       <c r="G98" s="5">
-        <v>2759.056129</v>
-      </c>
-    </row>
-    <row r="99" ht="15">
+        <v>2759.0561290000001</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
         <v>9</v>
       </c>
@@ -3843,10 +3820,10 @@
         <v>46</v>
       </c>
       <c r="G99" s="5">
-        <v>2732.972098</v>
-      </c>
-    </row>
-    <row r="100" ht="15">
+        <v>2732.9720980000002</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
         <v>9</v>
       </c>
@@ -3869,7 +3846,7 @@
         <v>2006.139819</v>
       </c>
     </row>
-    <row r="101" ht="15">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
         <v>9</v>
       </c>
@@ -3892,7 +3869,7 @@
         <v>1373.785836</v>
       </c>
     </row>
-    <row r="102" ht="15">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
         <v>9</v>
       </c>
@@ -3912,10 +3889,10 @@
         <v>13</v>
       </c>
       <c r="G102" s="5">
-        <v>381.759288</v>
-      </c>
-    </row>
-    <row r="103" ht="15">
+        <v>381.75928800000003</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
         <v>9</v>
       </c>
@@ -3935,10 +3912,10 @@
         <v>16</v>
       </c>
       <c r="G103" s="5">
-        <v>643.594496</v>
-      </c>
-    </row>
-    <row r="104" ht="15">
+        <v>643.59449600000005</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
         <v>9</v>
       </c>
@@ -3958,10 +3935,10 @@
         <v>19</v>
       </c>
       <c r="G104" s="5">
-        <v>1270.33677</v>
-      </c>
-    </row>
-    <row r="105" ht="15">
+        <v>1270.3367699999999</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
         <v>9</v>
       </c>
@@ -3984,7 +3961,7 @@
         <v>1442.536932</v>
       </c>
     </row>
-    <row r="106" ht="15">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
         <v>9</v>
       </c>
@@ -4004,10 +3981,10 @@
         <v>25</v>
       </c>
       <c r="G106" s="5">
-        <v>1732.478315</v>
-      </c>
-    </row>
-    <row r="107" ht="15">
+        <v>1732.4783150000001</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
         <v>9</v>
       </c>
@@ -4030,7 +4007,7 @@
         <v>2029.984426</v>
       </c>
     </row>
-    <row r="108" ht="15">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
         <v>9</v>
       </c>
@@ -4050,10 +4027,10 @@
         <v>31</v>
       </c>
       <c r="G108" s="5">
-        <v>2411.054097</v>
-      </c>
-    </row>
-    <row r="109" ht="15">
+        <v>2411.0540970000002</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
         <v>9</v>
       </c>
@@ -4073,10 +4050,10 @@
         <v>34</v>
       </c>
       <c r="G109" s="5">
-        <v>2468.803344</v>
-      </c>
-    </row>
-    <row r="110" ht="15">
+        <v>2468.8033439999999</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
         <v>9</v>
       </c>
@@ -4099,7 +4076,7 @@
         <v>2672.468507</v>
       </c>
     </row>
-    <row r="111" ht="15">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
         <v>9</v>
       </c>
@@ -4119,10 +4096,10 @@
         <v>40</v>
       </c>
       <c r="G111" s="5">
-        <v>3117.132232</v>
-      </c>
-    </row>
-    <row r="112" ht="15">
+        <v>3117.1322319999999</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
         <v>9</v>
       </c>
@@ -4142,10 +4119,10 @@
         <v>43</v>
       </c>
       <c r="G112" s="5">
-        <v>3468.011256</v>
-      </c>
-    </row>
-    <row r="113" ht="15">
+        <v>3468.0112559999998</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
         <v>9</v>
       </c>
@@ -4165,10 +4142,10 @@
         <v>46</v>
       </c>
       <c r="G113" s="5">
-        <v>3570.074095</v>
-      </c>
-    </row>
-    <row r="114" ht="15">
+        <v>3570.0740949999999</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
         <v>9</v>
       </c>
@@ -4188,10 +4165,10 @@
         <v>49</v>
       </c>
       <c r="G114" s="5">
-        <v>1990.383645</v>
-      </c>
-    </row>
-    <row r="115" ht="15">
+        <v>1990.3836449999999</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
         <v>9</v>
       </c>
@@ -4211,10 +4188,10 @@
         <v>143</v>
       </c>
       <c r="G115" s="5">
-        <v>1116.3911</v>
-      </c>
-    </row>
-    <row r="116" ht="15">
+        <v>1116.3911000000001</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
         <v>9</v>
       </c>
@@ -4234,10 +4211,10 @@
         <v>13</v>
       </c>
       <c r="G116" s="5">
-        <v>569.307041</v>
-      </c>
-    </row>
-    <row r="117" ht="15">
+        <v>569.30704100000003</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
         <v>9</v>
       </c>
@@ -4257,10 +4234,10 @@
         <v>16</v>
       </c>
       <c r="G117" s="5">
-        <v>783.06324</v>
-      </c>
-    </row>
-    <row r="118" ht="15">
+        <v>783.06323999999995</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
         <v>9</v>
       </c>
@@ -4280,10 +4257,10 @@
         <v>19</v>
       </c>
       <c r="G118" s="5">
-        <v>1335.932265</v>
-      </c>
-    </row>
-    <row r="119" ht="15">
+        <v>1335.9322649999999</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
         <v>9</v>
       </c>
@@ -4306,7 +4283,7 @@
         <v>1423.410699</v>
       </c>
     </row>
-    <row r="120" ht="15">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
         <v>9</v>
       </c>
@@ -4329,7 +4306,7 @@
         <v>1692.05971</v>
       </c>
     </row>
-    <row r="121" ht="15">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
         <v>9</v>
       </c>
@@ -4352,7 +4329,7 @@
         <v>2042.642533</v>
       </c>
     </row>
-    <row r="122" ht="15">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
         <v>9</v>
       </c>
@@ -4372,10 +4349,10 @@
         <v>31</v>
       </c>
       <c r="G122" s="5">
-        <v>2680.30147</v>
-      </c>
-    </row>
-    <row r="123" ht="15">
+        <v>2680.3014699999999</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
         <v>9</v>
       </c>
@@ -4395,10 +4372,10 @@
         <v>34</v>
       </c>
       <c r="G123" s="5">
-        <v>2953.847951</v>
-      </c>
-    </row>
-    <row r="124" ht="15">
+        <v>2953.8479510000002</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
         <v>9</v>
       </c>
@@ -4418,10 +4395,10 @@
         <v>37</v>
       </c>
       <c r="G124" s="5">
-        <v>3833.003288</v>
-      </c>
-    </row>
-    <row r="125" ht="15">
+        <v>3833.0032879999999</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
         <v>9</v>
       </c>
@@ -4441,10 +4418,10 @@
         <v>40</v>
       </c>
       <c r="G125" s="5">
-        <v>4356.529843</v>
-      </c>
-    </row>
-    <row r="126" ht="15">
+        <v>4356.5298430000003</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
         <v>9</v>
       </c>
@@ -4464,10 +4441,10 @@
         <v>43</v>
       </c>
       <c r="G126" s="5">
-        <v>4289.264376</v>
-      </c>
-    </row>
-    <row r="127" ht="15">
+        <v>4289.2643760000001</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
         <v>9</v>
       </c>
@@ -4487,10 +4464,10 @@
         <v>46</v>
       </c>
       <c r="G127" s="5">
-        <v>4392.935787</v>
-      </c>
-    </row>
-    <row r="128" ht="15">
+        <v>4392.9357870000003</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
         <v>9</v>
       </c>
@@ -4510,10 +4487,10 @@
         <v>49</v>
       </c>
       <c r="G128" s="5">
-        <v>2491.625283</v>
-      </c>
-    </row>
-    <row r="129" ht="15">
+        <v>2491.6252829999999</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
         <v>9</v>
       </c>
@@ -4533,10 +4510,10 @@
         <v>143</v>
       </c>
       <c r="G129" s="5">
-        <v>968.887454</v>
-      </c>
-    </row>
-    <row r="130" ht="15">
+        <v>968.88745400000005</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
         <v>9</v>
       </c>
@@ -4556,10 +4533,10 @@
         <v>13</v>
       </c>
       <c r="G130" s="5">
-        <v>846.996154</v>
-      </c>
-    </row>
-    <row r="131" ht="15">
+        <v>846.99615400000005</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
         <v>9</v>
       </c>
@@ -4582,7 +4559,7 @@
         <v>1128.554351</v>
       </c>
     </row>
-    <row r="132" ht="15">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
         <v>9</v>
       </c>
@@ -4602,10 +4579,10 @@
         <v>19</v>
       </c>
       <c r="G132" s="5">
-        <v>1860.569318</v>
-      </c>
-    </row>
-    <row r="133" ht="15">
+        <v>1860.5693180000001</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
         <v>9</v>
       </c>
@@ -4625,10 +4602,10 @@
         <v>22</v>
       </c>
       <c r="G133" s="5">
-        <v>1788.354395</v>
-      </c>
-    </row>
-    <row r="134" ht="15">
+        <v>1788.3543950000001</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
         <v>9</v>
       </c>
@@ -4648,10 +4625,10 @@
         <v>25</v>
       </c>
       <c r="G134" s="5">
-        <v>1966.077637</v>
-      </c>
-    </row>
-    <row r="135" ht="15">
+        <v>1966.0776370000001</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
         <v>9</v>
       </c>
@@ -4671,10 +4648,10 @@
         <v>28</v>
       </c>
       <c r="G135" s="5">
-        <v>2334.426643</v>
-      </c>
-    </row>
-    <row r="136" ht="15">
+        <v>2334.4266429999998</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
         <v>9</v>
       </c>
@@ -4694,10 +4671,10 @@
         <v>31</v>
       </c>
       <c r="G136" s="5">
-        <v>2675.690856</v>
-      </c>
-    </row>
-    <row r="137" ht="15">
+        <v>2675.6908560000002</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
         <v>9</v>
       </c>
@@ -4720,7 +4697,7 @@
         <v>2982.863499</v>
       </c>
     </row>
-    <row r="138" ht="15">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
         <v>9</v>
       </c>
@@ -4740,10 +4717,10 @@
         <v>37</v>
       </c>
       <c r="G138" s="5">
-        <v>4133.427119</v>
-      </c>
-    </row>
-    <row r="139" ht="15">
+        <v>4133.4271189999999</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="4" t="s">
         <v>9</v>
       </c>
@@ -4763,10 +4740,10 @@
         <v>40</v>
       </c>
       <c r="G139" s="5">
-        <v>4682.502038</v>
-      </c>
-    </row>
-    <row r="140" ht="15">
+        <v>4682.5020379999996</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
         <v>9</v>
       </c>
@@ -4786,10 +4763,10 @@
         <v>43</v>
       </c>
       <c r="G140" s="5">
-        <v>4257.943462</v>
-      </c>
-    </row>
-    <row r="141" ht="15">
+        <v>4257.9434620000002</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="4" t="s">
         <v>9</v>
       </c>
@@ -4809,10 +4786,10 @@
         <v>46</v>
       </c>
       <c r="G141" s="5">
-        <v>4637.991465</v>
-      </c>
-    </row>
-    <row r="142" ht="15">
+        <v>4637.9914650000001</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
         <v>9</v>
       </c>
@@ -4832,10 +4809,10 @@
         <v>49</v>
       </c>
       <c r="G142" s="5">
-        <v>3536.83737</v>
-      </c>
-    </row>
-    <row r="143" ht="15">
+        <v>3536.8373700000002</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
         <v>9</v>
       </c>
@@ -4855,10 +4832,10 @@
         <v>143</v>
       </c>
       <c r="G143" s="5">
-        <v>2016.181739</v>
-      </c>
-    </row>
-    <row r="144" ht="15">
+        <v>2016.1817390000001</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
         <v>9</v>
       </c>
@@ -4878,10 +4855,10 @@
         <v>13</v>
       </c>
       <c r="G144" s="5">
-        <v>798.296545</v>
-      </c>
-    </row>
-    <row r="145" ht="15">
+        <v>798.29654500000004</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
         <v>9</v>
       </c>
@@ -4901,10 +4878,10 @@
         <v>16</v>
       </c>
       <c r="G145" s="5">
-        <v>1084.354792</v>
-      </c>
-    </row>
-    <row r="146" ht="15">
+        <v>1084.3547920000001</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
         <v>9</v>
       </c>
@@ -4924,10 +4901,10 @@
         <v>19</v>
       </c>
       <c r="G146" s="5">
-        <v>1663.653304</v>
-      </c>
-    </row>
-    <row r="147" ht="15">
+        <v>1663.6533039999999</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
         <v>9</v>
       </c>
@@ -4947,10 +4924,10 @@
         <v>22</v>
       </c>
       <c r="G147" s="5">
-        <v>1731.402037</v>
-      </c>
-    </row>
-    <row r="148" ht="15">
+        <v>1731.4020370000001</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
         <v>9</v>
       </c>
@@ -4970,10 +4947,10 @@
         <v>25</v>
       </c>
       <c r="G148" s="5">
-        <v>1851.124549</v>
-      </c>
-    </row>
-    <row r="149" ht="15">
+        <v>1851.1245489999999</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="s">
         <v>9</v>
       </c>
@@ -4993,10 +4970,10 @@
         <v>28</v>
       </c>
       <c r="G149" s="5">
-        <v>2339.495052</v>
-      </c>
-    </row>
-    <row r="150" ht="15">
+        <v>2339.4950520000002</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
         <v>9</v>
       </c>
@@ -5016,10 +4993,10 @@
         <v>31</v>
       </c>
       <c r="G150" s="5">
-        <v>2416.255668</v>
-      </c>
-    </row>
-    <row r="151" ht="15">
+        <v>2416.2556679999998</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="s">
         <v>9</v>
       </c>
@@ -5039,10 +5016,10 @@
         <v>34</v>
       </c>
       <c r="G151" s="5">
-        <v>2852.250643</v>
-      </c>
-    </row>
-    <row r="152" ht="15">
+        <v>2852.2506429999999</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
         <v>9</v>
       </c>
@@ -5065,7 +5042,7 @@
         <v>3722.88132</v>
       </c>
     </row>
-    <row r="153" ht="15">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
         <v>9</v>
       </c>
@@ -5085,10 +5062,10 @@
         <v>40</v>
       </c>
       <c r="G153" s="5">
-        <v>4450.351371</v>
-      </c>
-    </row>
-    <row r="154" ht="15">
+        <v>4450.3513709999997</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
         <v>9</v>
       </c>
@@ -5108,10 +5085,10 @@
         <v>43</v>
       </c>
       <c r="G154" s="5">
-        <v>4389.854204</v>
-      </c>
-    </row>
-    <row r="155" ht="15">
+        <v>4389.8542040000002</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="s">
         <v>9</v>
       </c>
@@ -5131,10 +5108,10 @@
         <v>46</v>
       </c>
       <c r="G155" s="5">
-        <v>4335.13214</v>
-      </c>
-    </row>
-    <row r="156" ht="15">
+        <v>4335.1321399999997</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
         <v>9</v>
       </c>
@@ -5157,7 +5134,7 @@
         <v>2693.24694</v>
       </c>
     </row>
-    <row r="157" ht="15">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
         <v>9</v>
       </c>
@@ -5177,10 +5154,10 @@
         <v>143</v>
       </c>
       <c r="G157" s="5">
-        <v>1446.42297</v>
-      </c>
-    </row>
-    <row r="158" ht="15">
+        <v>1446.4229700000001</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
         <v>9</v>
       </c>
@@ -5200,10 +5177,10 @@
         <v>13</v>
       </c>
       <c r="G158" s="5">
-        <v>784.845362</v>
-      </c>
-    </row>
-    <row r="159" ht="15">
+        <v>784.84536200000002</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="s">
         <v>9</v>
       </c>
@@ -5223,10 +5200,10 @@
         <v>16</v>
       </c>
       <c r="G159" s="5">
-        <v>1231.236288</v>
-      </c>
-    </row>
-    <row r="160" ht="15">
+        <v>1231.2362880000001</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
         <v>9</v>
       </c>
@@ -5249,7 +5226,7 @@
         <v>1575.173843</v>
       </c>
     </row>
-    <row r="161" ht="15">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" s="4" t="s">
         <v>9</v>
       </c>
@@ -5269,10 +5246,10 @@
         <v>22</v>
       </c>
       <c r="G161" s="5">
-        <v>1315.623847</v>
-      </c>
-    </row>
-    <row r="162" ht="15">
+        <v>1315.6238470000001</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
         <v>9</v>
       </c>
@@ -5292,10 +5269,10 @@
         <v>25</v>
       </c>
       <c r="G162" s="5">
-        <v>1384.344852</v>
-      </c>
-    </row>
-    <row r="163" ht="15">
+        <v>1384.3448519999999</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" s="4" t="s">
         <v>9</v>
       </c>
@@ -5315,10 +5292,10 @@
         <v>28</v>
       </c>
       <c r="G163" s="5">
-        <v>2053.918006</v>
-      </c>
-    </row>
-    <row r="164" ht="15">
+        <v>2053.9180059999999</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
         <v>9</v>
       </c>
@@ -5338,10 +5315,10 @@
         <v>31</v>
       </c>
       <c r="G164" s="5">
-        <v>2051.89763</v>
-      </c>
-    </row>
-    <row r="165" ht="15">
+        <v>2051.8976299999999</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" s="4" t="s">
         <v>9</v>
       </c>
@@ -5361,10 +5338,10 @@
         <v>34</v>
       </c>
       <c r="G165" s="5">
-        <v>2347.754519</v>
-      </c>
-    </row>
-    <row r="166" ht="15">
+        <v>2347.7545190000001</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
         <v>9</v>
       </c>
@@ -5384,10 +5361,10 @@
         <v>37</v>
       </c>
       <c r="G166" s="5">
-        <v>2736.753349</v>
-      </c>
-    </row>
-    <row r="167" ht="15">
+        <v>2736.7533490000001</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" s="4" t="s">
         <v>9</v>
       </c>
@@ -5407,10 +5384,10 @@
         <v>40</v>
       </c>
       <c r="G167" s="5">
-        <v>2563.664694</v>
-      </c>
-    </row>
-    <row r="168" ht="15">
+        <v>2563.6646940000001</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
         <v>9</v>
       </c>
@@ -5430,10 +5407,10 @@
         <v>43</v>
       </c>
       <c r="G168" s="5">
-        <v>2380.593391</v>
-      </c>
-    </row>
-    <row r="169" ht="15">
+        <v>2380.5933909999999</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" s="4" t="s">
         <v>9</v>
       </c>
@@ -5453,10 +5430,10 @@
         <v>46</v>
       </c>
       <c r="G169" s="5">
-        <v>3050.567565</v>
-      </c>
-    </row>
-    <row r="170" ht="15">
+        <v>3050.5675649999998</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
         <v>9</v>
       </c>
@@ -5476,10 +5453,10 @@
         <v>49</v>
       </c>
       <c r="G170" s="5">
-        <v>2774.098021</v>
-      </c>
-    </row>
-    <row r="171" ht="15">
+        <v>2774.0980209999998</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" s="4" t="s">
         <v>9</v>
       </c>
@@ -5499,10 +5476,10 @@
         <v>179</v>
       </c>
       <c r="G171" s="5">
-        <v>2631.605499</v>
-      </c>
-    </row>
-    <row r="172" ht="15">
+        <v>2631.6054989999998</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
         <v>9</v>
       </c>
@@ -5522,10 +5499,10 @@
         <v>13</v>
       </c>
       <c r="G172" s="5">
-        <v>136.805404</v>
-      </c>
-    </row>
-    <row r="173" ht="15">
+        <v>136.80540400000001</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" s="4" t="s">
         <v>9</v>
       </c>
@@ -5548,7 +5525,7 @@
         <v>416.252546</v>
       </c>
     </row>
-    <row r="174" ht="15">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
         <v>9</v>
       </c>
@@ -5568,10 +5545,10 @@
         <v>19</v>
       </c>
       <c r="G174" s="5">
-        <v>1124.142945</v>
-      </c>
-    </row>
-    <row r="175" ht="15">
+        <v>1124.1429450000001</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" s="4" t="s">
         <v>9</v>
       </c>
@@ -5591,10 +5568,10 @@
         <v>22</v>
       </c>
       <c r="G175" s="5">
-        <v>1197.22656</v>
-      </c>
-    </row>
-    <row r="176" ht="15">
+        <v>1197.2265600000001</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
         <v>9</v>
       </c>
@@ -5614,10 +5591,10 @@
         <v>25</v>
       </c>
       <c r="G176" s="5">
-        <v>1395.841834</v>
-      </c>
-    </row>
-    <row r="177" ht="15">
+        <v>1395.8418340000001</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" s="4" t="s">
         <v>9</v>
       </c>
@@ -5637,10 +5614,10 @@
         <v>28</v>
       </c>
       <c r="G177" s="5">
-        <v>1783.064683</v>
-      </c>
-    </row>
-    <row r="178" ht="15">
+        <v>1783.0646830000001</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
         <v>9</v>
       </c>
@@ -5663,7 +5640,7 @@
         <v>1996.48837</v>
       </c>
     </row>
-    <row r="179" ht="15">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" s="4" t="s">
         <v>9</v>
       </c>
@@ -5683,10 +5660,10 @@
         <v>34</v>
       </c>
       <c r="G179" s="5">
-        <v>2355.68035</v>
-      </c>
-    </row>
-    <row r="180" ht="15">
+        <v>2355.6803500000001</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
         <v>9</v>
       </c>
@@ -5706,10 +5683,10 @@
         <v>37</v>
       </c>
       <c r="G180" s="5">
-        <v>3277.299012</v>
-      </c>
-    </row>
-    <row r="181" ht="15">
+        <v>3277.2990119999999</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" s="4" t="s">
         <v>9</v>
       </c>
@@ -5729,10 +5706,10 @@
         <v>40</v>
       </c>
       <c r="G181" s="5">
-        <v>4161.610816</v>
-      </c>
-    </row>
-    <row r="182" ht="15">
+        <v>4161.6108160000003</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
         <v>9</v>
       </c>
@@ -5752,10 +5729,10 @@
         <v>43</v>
       </c>
       <c r="G182" s="5">
-        <v>3760.768836</v>
-      </c>
-    </row>
-    <row r="183" ht="15">
+        <v>3760.7688360000002</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" s="4" t="s">
         <v>9</v>
       </c>
@@ -5775,10 +5752,10 @@
         <v>46</v>
       </c>
       <c r="G183" s="5">
-        <v>3608.270549</v>
-      </c>
-    </row>
-    <row r="184" ht="15">
+        <v>3608.2705489999998</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
         <v>9</v>
       </c>
@@ -5801,7 +5778,7 @@
         <v>2108.722217</v>
       </c>
     </row>
-    <row r="185" ht="15">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" s="4" t="s">
         <v>9</v>
       </c>
@@ -5821,10 +5798,10 @@
         <v>143</v>
       </c>
       <c r="G185" s="5">
-        <v>990.304868</v>
-      </c>
-    </row>
-    <row r="186" ht="15">
+        <v>990.30486800000006</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
         <v>9</v>
       </c>
@@ -5844,10 +5821,10 @@
         <v>13</v>
       </c>
       <c r="G186" s="5">
-        <v>604.619157</v>
-      </c>
-    </row>
-    <row r="187" ht="15">
+        <v>604.61915699999997</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" s="4" t="s">
         <v>9</v>
       </c>
@@ -5867,10 +5844,10 @@
         <v>16</v>
       </c>
       <c r="G187" s="5">
-        <v>2352.294857</v>
-      </c>
-    </row>
-    <row r="188" ht="15">
+        <v>2352.2948569999999</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
         <v>9</v>
       </c>
@@ -5893,7 +5870,7 @@
         <v>2015.809659</v>
       </c>
     </row>
-    <row r="189" ht="15">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="s">
         <v>9</v>
       </c>
@@ -5913,10 +5890,10 @@
         <v>22</v>
       </c>
       <c r="G189" s="5">
-        <v>1819.203999</v>
-      </c>
-    </row>
-    <row r="190" ht="15">
+        <v>1819.2039990000001</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
         <v>9</v>
       </c>
@@ -5936,10 +5913,10 @@
         <v>25</v>
       </c>
       <c r="G190" s="5">
-        <v>1881.53795</v>
-      </c>
-    </row>
-    <row r="191" ht="15">
+        <v>1881.5379499999999</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" s="4" t="s">
         <v>9</v>
       </c>
@@ -5959,10 +5936,10 @@
         <v>28</v>
       </c>
       <c r="G191" s="5">
-        <v>2341.573213</v>
-      </c>
-    </row>
-    <row r="192" ht="15">
+        <v>2341.5732130000001</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
         <v>9</v>
       </c>
@@ -5982,10 +5959,10 @@
         <v>31</v>
       </c>
       <c r="G192" s="5">
-        <v>2833.738835</v>
-      </c>
-    </row>
-    <row r="193" ht="15">
+        <v>2833.7388350000001</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" s="4" t="s">
         <v>9</v>
       </c>
@@ -6005,10 +5982,10 @@
         <v>34</v>
       </c>
       <c r="G193" s="5">
-        <v>3163.805358</v>
-      </c>
-    </row>
-    <row r="194" ht="15">
+        <v>3163.8053580000001</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
         <v>9</v>
       </c>
@@ -6028,10 +6005,10 @@
         <v>37</v>
       </c>
       <c r="G194" s="5">
-        <v>4373.073916</v>
-      </c>
-    </row>
-    <row r="195" ht="15">
+        <v>4373.0739160000003</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" s="4" t="s">
         <v>9</v>
       </c>
@@ -6051,10 +6028,10 @@
         <v>40</v>
       </c>
       <c r="G195" s="5">
-        <v>4998.301438</v>
-      </c>
-    </row>
-    <row r="196" ht="15">
+        <v>4998.3014380000004</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
         <v>9</v>
       </c>
@@ -6074,10 +6051,10 @@
         <v>43</v>
       </c>
       <c r="G196" s="5">
-        <v>4354.833324</v>
-      </c>
-    </row>
-    <row r="197" ht="15">
+        <v>4354.8333240000002</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" s="4" t="s">
         <v>9</v>
       </c>
@@ -6097,10 +6074,10 @@
         <v>46</v>
       </c>
       <c r="G197" s="5">
-        <v>4980.621299</v>
-      </c>
-    </row>
-    <row r="198" ht="15">
+        <v>4980.6212990000004</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
         <v>9</v>
       </c>
@@ -6120,10 +6097,10 @@
         <v>49</v>
       </c>
       <c r="G198" s="5">
-        <v>3610.438969</v>
-      </c>
-    </row>
-    <row r="199" ht="15">
+        <v>3610.4389689999998</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" s="4" t="s">
         <v>9</v>
       </c>
@@ -6143,10 +6120,10 @@
         <v>143</v>
       </c>
       <c r="G199" s="5">
-        <v>1721.715836</v>
-      </c>
-    </row>
-    <row r="200" ht="15">
+        <v>1721.7158360000001</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
         <v>9</v>
       </c>
@@ -6166,10 +6143,10 @@
         <v>13</v>
       </c>
       <c r="G200" s="5">
-        <v>892.747726</v>
-      </c>
-    </row>
-    <row r="201" ht="15">
+        <v>892.74772599999994</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" s="4" t="s">
         <v>9</v>
       </c>
@@ -6192,7 +6169,7 @@
         <v>1092.511178</v>
       </c>
     </row>
-    <row r="202" ht="15">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
         <v>9</v>
       </c>
@@ -6215,7 +6192,7 @@
         <v>1701.370302</v>
       </c>
     </row>
-    <row r="203" ht="15">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203" s="4" t="s">
         <v>9</v>
       </c>
@@ -6238,7 +6215,7 @@
         <v>1797.719681</v>
       </c>
     </row>
-    <row r="204" ht="15">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
         <v>9</v>
       </c>
@@ -6258,10 +6235,10 @@
         <v>25</v>
       </c>
       <c r="G204" s="5">
-        <v>1976.010652</v>
-      </c>
-    </row>
-    <row r="205" ht="15">
+        <v>1976.0106519999999</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205" s="4" t="s">
         <v>9</v>
       </c>
@@ -6281,10 +6258,10 @@
         <v>28</v>
       </c>
       <c r="G205" s="5">
-        <v>2297.980095</v>
-      </c>
-    </row>
-    <row r="206" ht="15">
+        <v>2297.9800949999999</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
         <v>9</v>
       </c>
@@ -6304,10 +6281,10 @@
         <v>31</v>
       </c>
       <c r="G206" s="5">
-        <v>2685.788839</v>
-      </c>
-    </row>
-    <row r="207" ht="15">
+        <v>2685.7888389999998</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" s="4" t="s">
         <v>9</v>
       </c>
@@ -6330,7 +6307,7 @@
         <v>3049.78802</v>
       </c>
     </row>
-    <row r="208" ht="15">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
         <v>9</v>
       </c>
@@ -6350,10 +6327,10 @@
         <v>37</v>
       </c>
       <c r="G208" s="5">
-        <v>4441.044626</v>
-      </c>
-    </row>
-    <row r="209" ht="15">
+        <v>4441.0446259999999</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209" s="4" t="s">
         <v>9</v>
       </c>
@@ -6373,10 +6350,10 @@
         <v>40</v>
       </c>
       <c r="G209" s="5">
-        <v>4873.911588</v>
-      </c>
-    </row>
-    <row r="210" ht="15">
+        <v>4873.9115879999999</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
         <v>9</v>
       </c>
@@ -6396,10 +6373,10 @@
         <v>43</v>
       </c>
       <c r="G210" s="5">
-        <v>4291.553327</v>
-      </c>
-    </row>
-    <row r="211" ht="15">
+        <v>4291.5533269999996</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211" s="4" t="s">
         <v>9</v>
       </c>
@@ -6419,10 +6396,10 @@
         <v>46</v>
       </c>
       <c r="G211" s="5">
-        <v>4411.564221</v>
-      </c>
-    </row>
-    <row r="212" ht="15">
+        <v>4411.5642209999996</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
         <v>9</v>
       </c>
@@ -6442,10 +6419,10 @@
         <v>49</v>
       </c>
       <c r="G212" s="5">
-        <v>3361.101203</v>
-      </c>
-    </row>
-    <row r="213" ht="15">
+        <v>3361.1012030000002</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213" s="4" t="s">
         <v>9</v>
       </c>
@@ -6468,7 +6445,7 @@
         <v>1623.01297</v>
       </c>
     </row>
-    <row r="214" ht="15">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
         <v>9</v>
       </c>
@@ -6488,10 +6465,10 @@
         <v>13</v>
       </c>
       <c r="G214" s="5">
-        <v>958.378957</v>
-      </c>
-    </row>
-    <row r="215" ht="15">
+        <v>958.37895700000001</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215" s="4" t="s">
         <v>9</v>
       </c>
@@ -6514,7 +6491,7 @@
         <v>1283.197441</v>
       </c>
     </row>
-    <row r="216" ht="15">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
         <v>9</v>
       </c>
@@ -6537,7 +6514,7 @@
         <v>1803.519407</v>
       </c>
     </row>
-    <row r="217" ht="15">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A217" s="4" t="s">
         <v>9</v>
       </c>
@@ -6557,10 +6534,10 @@
         <v>22</v>
       </c>
       <c r="G217" s="5">
-        <v>1704.639611</v>
-      </c>
-    </row>
-    <row r="218" ht="15">
+        <v>1704.6396110000001</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
         <v>9</v>
       </c>
@@ -6583,7 +6560,7 @@
         <v>1603.41121</v>
       </c>
     </row>
-    <row r="219" ht="15">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219" s="4" t="s">
         <v>9</v>
       </c>
@@ -6603,10 +6580,10 @@
         <v>28</v>
       </c>
       <c r="G219" s="5">
-        <v>2058.893263</v>
-      </c>
-    </row>
-    <row r="220" ht="15">
+        <v>2058.8932629999999</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
         <v>9</v>
       </c>
@@ -6626,10 +6603,10 @@
         <v>31</v>
       </c>
       <c r="G220" s="5">
-        <v>2684.858533</v>
-      </c>
-    </row>
-    <row r="221" ht="15">
+        <v>2684.8585330000001</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221" s="4" t="s">
         <v>9</v>
       </c>
@@ -6649,10 +6626,10 @@
         <v>34</v>
       </c>
       <c r="G221" s="5">
-        <v>3056.678307</v>
-      </c>
-    </row>
-    <row r="222" ht="15">
+        <v>3056.6783070000001</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
         <v>9</v>
       </c>
@@ -6672,10 +6649,10 @@
         <v>37</v>
       </c>
       <c r="G222" s="5">
-        <v>4036.964556</v>
-      </c>
-    </row>
-    <row r="223" ht="15">
+        <v>4036.9645559999999</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A223" s="4" t="s">
         <v>9</v>
       </c>
@@ -6695,10 +6672,10 @@
         <v>40</v>
       </c>
       <c r="G223" s="5">
-        <v>4478.499209</v>
-      </c>
-    </row>
-    <row r="224" ht="15">
+        <v>4478.4992089999996</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
         <v>9</v>
       </c>
@@ -6718,10 +6695,10 @@
         <v>43</v>
       </c>
       <c r="G224" s="5">
-        <v>4305.693575</v>
-      </c>
-    </row>
-    <row r="225" ht="15">
+        <v>4305.6935750000002</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225" s="4" t="s">
         <v>9</v>
       </c>
@@ -6741,10 +6718,10 @@
         <v>46</v>
       </c>
       <c r="G225" s="5">
-        <v>4541.317281</v>
-      </c>
-    </row>
-    <row r="226" ht="15">
+        <v>4541.3172809999996</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
         <v>9</v>
       </c>
@@ -6764,10 +6741,10 @@
         <v>49</v>
       </c>
       <c r="G226" s="5">
-        <v>2538.642364</v>
-      </c>
-    </row>
-    <row r="227" ht="15">
+        <v>2538.6423639999998</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A227" s="4" t="s">
         <v>9</v>
       </c>
@@ -6787,10 +6764,10 @@
         <v>143</v>
       </c>
       <c r="G227" s="5">
-        <v>1070.243989</v>
-      </c>
-    </row>
-    <row r="228" ht="15">
+        <v>1070.2439890000001</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
         <v>9</v>
       </c>
@@ -6813,7 +6790,7 @@
         <v>973.246309</v>
       </c>
     </row>
-    <row r="229" ht="15">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A229" s="4" t="s">
         <v>9</v>
       </c>
@@ -6833,10 +6810,10 @@
         <v>16</v>
       </c>
       <c r="G229" s="5">
-        <v>1211.815735</v>
-      </c>
-    </row>
-    <row r="230" ht="15">
+        <v>1211.8157349999999</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
         <v>9</v>
       </c>
@@ -6859,7 +6836,7 @@
         <v>1643.501935</v>
       </c>
     </row>
-    <row r="231" ht="15">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A231" s="4" t="s">
         <v>9</v>
       </c>
@@ -6879,10 +6856,10 @@
         <v>22</v>
       </c>
       <c r="G231" s="5">
-        <v>1675.371064</v>
-      </c>
-    </row>
-    <row r="232" ht="15">
+        <v>1675.3710639999999</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
         <v>9</v>
       </c>
@@ -6905,7 +6882,7 @@
         <v>1658.304699</v>
       </c>
     </row>
-    <row r="233" ht="15">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A233" s="4" t="s">
         <v>9</v>
       </c>
@@ -6925,10 +6902,10 @@
         <v>28</v>
       </c>
       <c r="G233" s="5">
-        <v>1964.273765</v>
-      </c>
-    </row>
-    <row r="234" ht="15">
+        <v>1964.2737649999999</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
         <v>9</v>
       </c>
@@ -6948,10 +6925,10 @@
         <v>31</v>
       </c>
       <c r="G234" s="5">
-        <v>2442.555872</v>
-      </c>
-    </row>
-    <row r="235" ht="15">
+        <v>2442.5558719999999</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A235" s="4" t="s">
         <v>9</v>
       </c>
@@ -6971,10 +6948,10 @@
         <v>34</v>
       </c>
       <c r="G235" s="5">
-        <v>3053.807762</v>
-      </c>
-    </row>
-    <row r="236" ht="15">
+        <v>3053.8077619999999</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
         <v>9</v>
       </c>
@@ -6997,7 +6974,7 @@
         <v>4188.362572</v>
       </c>
     </row>
-    <row r="237" ht="15">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A237" s="4" t="s">
         <v>9</v>
       </c>
@@ -7017,10 +6994,10 @@
         <v>40</v>
       </c>
       <c r="G237" s="5">
-        <v>4581.209199</v>
-      </c>
-    </row>
-    <row r="238" ht="15">
+        <v>4581.2091989999999</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
         <v>9</v>
       </c>
@@ -7040,10 +7017,10 @@
         <v>43</v>
       </c>
       <c r="G238" s="5">
-        <v>4542.563859</v>
-      </c>
-    </row>
-    <row r="239" ht="15">
+        <v>4542.5638589999999</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A239" s="4" t="s">
         <v>9</v>
       </c>
@@ -7063,10 +7040,10 @@
         <v>46</v>
       </c>
       <c r="G239" s="5">
-        <v>4752.791799</v>
-      </c>
-    </row>
-    <row r="240" ht="15">
+        <v>4752.7917989999996</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A240" s="4" t="s">
         <v>9</v>
       </c>
@@ -7089,7 +7066,7 @@
         <v>3037.644233</v>
       </c>
     </row>
-    <row r="241" ht="15">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A241" s="4" t="s">
         <v>9</v>
       </c>
@@ -7109,10 +7086,10 @@
         <v>230</v>
       </c>
       <c r="G241" s="5">
-        <v>1073.677726</v>
-      </c>
-    </row>
-    <row r="242" ht="15">
+        <v>1073.6777259999999</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A242" s="4" t="s">
         <v>9</v>
       </c>
@@ -7132,10 +7109,10 @@
         <v>13</v>
       </c>
       <c r="G242" s="5">
-        <v>858.852517</v>
-      </c>
-    </row>
-    <row r="243" ht="15">
+        <v>858.85251700000003</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A243" s="4" t="s">
         <v>9</v>
       </c>
@@ -7158,7 +7135,7 @@
         <v>1101.104059</v>
       </c>
     </row>
-    <row r="244" ht="15">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A244" s="4" t="s">
         <v>9</v>
       </c>
@@ -7178,10 +7155,10 @@
         <v>19</v>
       </c>
       <c r="G244" s="5">
-        <v>1625.857598</v>
-      </c>
-    </row>
-    <row r="245" ht="15">
+        <v>1625.8575980000001</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A245" s="4" t="s">
         <v>9</v>
       </c>
@@ -7201,10 +7178,10 @@
         <v>22</v>
       </c>
       <c r="G245" s="5">
-        <v>1664.91846</v>
-      </c>
-    </row>
-    <row r="246" ht="15">
+        <v>1664.9184600000001</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A246" s="4" t="s">
         <v>9</v>
       </c>
@@ -7224,10 +7201,10 @@
         <v>25</v>
       </c>
       <c r="G246" s="5">
-        <v>1947.19017</v>
-      </c>
-    </row>
-    <row r="247" ht="15">
+        <v>1947.1901700000001</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A247" s="4" t="s">
         <v>9</v>
       </c>
@@ -7247,10 +7224,10 @@
         <v>28</v>
       </c>
       <c r="G247" s="5">
-        <v>2444.721405</v>
-      </c>
-    </row>
-    <row r="248" ht="15">
+        <v>2444.7214049999998</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A248" s="4" t="s">
         <v>9</v>
       </c>
@@ -7270,10 +7247,10 @@
         <v>31</v>
       </c>
       <c r="G248" s="5">
-        <v>2623.804961</v>
-      </c>
-    </row>
-    <row r="249" ht="15">
+        <v>2623.8049609999998</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A249" s="4" t="s">
         <v>9</v>
       </c>
@@ -7293,10 +7270,10 @@
         <v>34</v>
       </c>
       <c r="G249" s="5">
-        <v>2961.629094</v>
-      </c>
-    </row>
-    <row r="250" ht="15">
+        <v>2961.6290939999999</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A250" s="4" t="s">
         <v>9</v>
       </c>
@@ -7319,7 +7296,7 @@
         <v>4065.382157</v>
       </c>
     </row>
-    <row r="251" ht="15">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A251" s="4" t="s">
         <v>9</v>
       </c>
@@ -7339,10 +7316,10 @@
         <v>40</v>
       </c>
       <c r="G251" s="5">
-        <v>4940.732818</v>
-      </c>
-    </row>
-    <row r="252" ht="15">
+        <v>4940.7328180000004</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A252" s="4" t="s">
         <v>9</v>
       </c>
@@ -7362,10 +7339,10 @@
         <v>43</v>
       </c>
       <c r="G252" s="5">
-        <v>4581.779907</v>
-      </c>
-    </row>
-    <row r="253" ht="15">
+        <v>4581.7799070000001</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A253" s="4" t="s">
         <v>9</v>
       </c>
@@ -7385,10 +7362,10 @@
         <v>46</v>
       </c>
       <c r="G253" s="5">
-        <v>4899.816114</v>
-      </c>
-    </row>
-    <row r="254" ht="15">
+        <v>4899.8161140000002</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A254" s="4" t="s">
         <v>9</v>
       </c>
@@ -7408,10 +7385,10 @@
         <v>49</v>
       </c>
       <c r="G254" s="5">
-        <v>3038.800892</v>
-      </c>
-    </row>
-    <row r="255" ht="15">
+        <v>3038.8008920000002</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A255" s="4" t="s">
         <v>9</v>
       </c>
@@ -7431,10 +7408,10 @@
         <v>143</v>
       </c>
       <c r="G255" s="5">
-        <v>1366.086091</v>
-      </c>
-    </row>
-    <row r="256" ht="15">
+        <v>1366.0860909999999</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A256" s="4" t="s">
         <v>9</v>
       </c>
@@ -7454,10 +7431,10 @@
         <v>13</v>
       </c>
       <c r="G256" s="5">
-        <v>851.948319</v>
-      </c>
-    </row>
-    <row r="257" ht="15">
+        <v>851.94831899999997</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A257" s="4" t="s">
         <v>9</v>
       </c>
@@ -7477,10 +7454,10 @@
         <v>16</v>
       </c>
       <c r="G257" s="5">
-        <v>906.57946</v>
-      </c>
-    </row>
-    <row r="258" ht="15">
+        <v>906.57946000000004</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A258" s="4" t="s">
         <v>9</v>
       </c>
@@ -7500,10 +7477,10 @@
         <v>19</v>
       </c>
       <c r="G258" s="5">
-        <v>1633.448732</v>
-      </c>
-    </row>
-    <row r="259" ht="15">
+        <v>1633.4487320000001</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A259" s="4" t="s">
         <v>9</v>
       </c>
@@ -7526,7 +7503,7 @@
         <v>1906.258996</v>
       </c>
     </row>
-    <row r="260" ht="15">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A260" s="4" t="s">
         <v>9</v>
       </c>
@@ -7549,7 +7526,7 @@
         <v>1999.845026</v>
       </c>
     </row>
-    <row r="261" ht="15">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A261" s="4" t="s">
         <v>9</v>
       </c>
@@ -7572,7 +7549,7 @@
         <v>2158.256566</v>
       </c>
     </row>
-    <row r="262" ht="15">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A262" s="4" t="s">
         <v>9</v>
       </c>
@@ -7592,10 +7569,10 @@
         <v>31</v>
       </c>
       <c r="G262" s="5">
-        <v>2632.553881</v>
-      </c>
-    </row>
-    <row r="263" ht="15">
+        <v>2632.5538809999998</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A263" s="4" t="s">
         <v>9</v>
       </c>
@@ -7615,10 +7592,10 @@
         <v>34</v>
       </c>
       <c r="G263" s="5">
-        <v>3175.717903</v>
-      </c>
-    </row>
-    <row r="264" ht="15">
+        <v>3175.7179030000002</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A264" s="4" t="s">
         <v>9</v>
       </c>
@@ -7638,10 +7615,10 @@
         <v>37</v>
       </c>
       <c r="G264" s="5">
-        <v>3920.479731</v>
-      </c>
-    </row>
-    <row r="265" ht="15">
+        <v>3920.4797309999999</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A265" s="4" t="s">
         <v>9</v>
       </c>
@@ -7661,10 +7638,10 @@
         <v>40</v>
       </c>
       <c r="G265" s="5">
-        <v>4591.900287</v>
-      </c>
-    </row>
-    <row r="266" ht="15">
+        <v>4591.9002870000004</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A266" s="4" t="s">
         <v>9</v>
       </c>
@@ -7684,10 +7661,10 @@
         <v>43</v>
       </c>
       <c r="G266" s="5">
-        <v>4229.060441</v>
-      </c>
-    </row>
-    <row r="267" ht="15">
+        <v>4229.0604409999996</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A267" s="4" t="s">
         <v>9</v>
       </c>
@@ -7707,10 +7684,10 @@
         <v>46</v>
       </c>
       <c r="G267" s="5">
-        <v>4714.246225</v>
-      </c>
-    </row>
-    <row r="268" ht="15">
+        <v>4714.2462249999999</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A268" s="4" t="s">
         <v>9</v>
       </c>
@@ -7730,10 +7707,10 @@
         <v>49</v>
       </c>
       <c r="G268" s="5">
-        <v>2864.073332</v>
-      </c>
-    </row>
-    <row r="269" ht="15">
+        <v>2864.0733319999999</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A269" s="4" t="s">
         <v>9</v>
       </c>
@@ -7753,10 +7730,10 @@
         <v>143</v>
       </c>
       <c r="G269" s="5">
-        <v>1493.66573</v>
-      </c>
-    </row>
-    <row r="270" ht="15">
+        <v>1493.6657299999999</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A270" s="4" t="s">
         <v>9</v>
       </c>
@@ -7776,10 +7753,10 @@
         <v>13</v>
       </c>
       <c r="G270" s="5">
-        <v>950.151409</v>
-      </c>
-    </row>
-    <row r="271" ht="15">
+        <v>950.15140899999994</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A271" s="4" t="s">
         <v>9</v>
       </c>
@@ -7802,7 +7779,7 @@
         <v>1031.591353</v>
       </c>
     </row>
-    <row r="272" ht="15">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A272" s="4" t="s">
         <v>9</v>
       </c>
@@ -7825,7 +7802,7 @@
         <v>1586.694058</v>
       </c>
     </row>
-    <row r="273" ht="15">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A273" s="4" t="s">
         <v>9</v>
       </c>
@@ -7845,10 +7822,10 @@
         <v>22</v>
       </c>
       <c r="G273" s="5">
-        <v>1588.904641</v>
-      </c>
-    </row>
-    <row r="274" ht="15">
+        <v>1588.9046410000001</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A274" s="4" t="s">
         <v>9</v>
       </c>
@@ -7871,7 +7848,7 @@
         <v>1628.89741</v>
       </c>
     </row>
-    <row r="275" ht="15">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A275" s="4" t="s">
         <v>9</v>
       </c>
@@ -7891,10 +7868,10 @@
         <v>28</v>
       </c>
       <c r="G275" s="5">
-        <v>2075.453247</v>
-      </c>
-    </row>
-    <row r="276" ht="15">
+        <v>2075.4532469999999</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A276" s="4" t="s">
         <v>9</v>
       </c>
@@ -7914,10 +7891,10 @@
         <v>31</v>
       </c>
       <c r="G276" s="5">
-        <v>2496.244645</v>
-      </c>
-    </row>
-    <row r="277" ht="15">
+        <v>2496.2446450000002</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A277" s="4" t="s">
         <v>9</v>
       </c>
@@ -7937,10 +7914,10 @@
         <v>34</v>
       </c>
       <c r="G277" s="5">
-        <v>2919.669071</v>
-      </c>
-    </row>
-    <row r="278" ht="15">
+        <v>2919.6690709999998</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A278" s="4" t="s">
         <v>9</v>
       </c>
@@ -7960,10 +7937,10 @@
         <v>37</v>
       </c>
       <c r="G278" s="5">
-        <v>3553.327282</v>
-      </c>
-    </row>
-    <row r="279" ht="15">
+        <v>3553.3272820000002</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A279" s="4" t="s">
         <v>9</v>
       </c>
@@ -7983,10 +7960,10 @@
         <v>40</v>
       </c>
       <c r="G279" s="5">
-        <v>4358.423203</v>
-      </c>
-    </row>
-    <row r="280" ht="15">
+        <v>4358.4232030000003</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A280" s="4" t="s">
         <v>9</v>
       </c>
@@ -8006,10 +7983,10 @@
         <v>43</v>
       </c>
       <c r="G280" s="5">
-        <v>4148.800233</v>
-      </c>
-    </row>
-    <row r="281" ht="15">
+        <v>4148.8002329999999</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A281" s="4" t="s">
         <v>9</v>
       </c>
@@ -8032,7 +8009,7 @@
         <v>4517.464207</v>
       </c>
     </row>
-    <row r="282" ht="15">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A282" s="4" t="s">
         <v>9</v>
       </c>
@@ -8052,10 +8029,10 @@
         <v>49</v>
       </c>
       <c r="G282" s="5">
-        <v>2845.475533</v>
-      </c>
-    </row>
-    <row r="283" ht="15">
+        <v>2845.4755329999998</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A283" s="4" t="s">
         <v>9</v>
       </c>
@@ -8075,10 +8052,10 @@
         <v>250</v>
       </c>
       <c r="G283" s="5">
-        <v>766.076991</v>
-      </c>
-    </row>
-    <row r="284" ht="15">
+        <v>766.07699100000002</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A284" s="4" t="s">
         <v>9</v>
       </c>
@@ -8098,10 +8075,10 @@
         <v>13</v>
       </c>
       <c r="G284" s="5">
-        <v>904.389496</v>
-      </c>
-    </row>
-    <row r="285" ht="15">
+        <v>904.38949600000001</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A285" s="4" t="s">
         <v>9</v>
       </c>
@@ -8121,10 +8098,10 @@
         <v>16</v>
       </c>
       <c r="G285" s="5">
-        <v>990.838988</v>
-      </c>
-    </row>
-    <row r="286" ht="15">
+        <v>990.83898799999997</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A286" s="4" t="s">
         <v>9</v>
       </c>
@@ -8144,10 +8121,10 @@
         <v>19</v>
       </c>
       <c r="G286" s="5">
-        <v>1495.761284</v>
-      </c>
-    </row>
-    <row r="287" ht="15">
+        <v>1495.7612839999999</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A287" s="4" t="s">
         <v>9</v>
       </c>
@@ -8170,7 +8147,7 @@
         <v>1718.101647</v>
       </c>
     </row>
-    <row r="288" ht="15">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A288" s="4" t="s">
         <v>9</v>
       </c>
@@ -8190,10 +8167,10 @@
         <v>25</v>
       </c>
       <c r="G288" s="5">
-        <v>1875.993713</v>
-      </c>
-    </row>
-    <row r="289" ht="15">
+        <v>1875.9937130000001</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A289" s="4" t="s">
         <v>9</v>
       </c>
@@ -8213,10 +8190,10 @@
         <v>28</v>
       </c>
       <c r="G289" s="5">
-        <v>2082.396965</v>
-      </c>
-    </row>
-    <row r="290" ht="15">
+        <v>2082.3969649999999</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A290" s="4" t="s">
         <v>9</v>
       </c>
@@ -8236,10 +8213,10 @@
         <v>31</v>
       </c>
       <c r="G290" s="5">
-        <v>2459.569141</v>
-      </c>
-    </row>
-    <row r="291" ht="15">
+        <v>2459.5691409999999</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A291" s="4" t="s">
         <v>9</v>
       </c>
@@ -8259,10 +8236,10 @@
         <v>34</v>
       </c>
       <c r="G291" s="5">
-        <v>2852.109433</v>
-      </c>
-    </row>
-    <row r="292" ht="15">
+        <v>2852.1094330000001</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A292" s="4" t="s">
         <v>9</v>
       </c>
@@ -8282,10 +8259,10 @@
         <v>37</v>
       </c>
       <c r="G292" s="5">
-        <v>3943.1067</v>
-      </c>
-    </row>
-    <row r="293" ht="15">
+        <v>3943.1066999999998</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A293" s="4" t="s">
         <v>9</v>
       </c>
@@ -8305,10 +8282,10 @@
         <v>40</v>
       </c>
       <c r="G293" s="5">
-        <v>4671.426768</v>
-      </c>
-    </row>
-    <row r="294" ht="15">
+        <v>4671.4267680000003</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A294" s="4" t="s">
         <v>9</v>
       </c>
@@ -8328,10 +8305,10 @@
         <v>43</v>
       </c>
       <c r="G294" s="5">
-        <v>4353.105293</v>
-      </c>
-    </row>
-    <row r="295" ht="15">
+        <v>4353.1052929999996</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A295" s="4" t="s">
         <v>9</v>
       </c>
@@ -8351,10 +8328,10 @@
         <v>46</v>
       </c>
       <c r="G295" s="5">
-        <v>4839.665432</v>
-      </c>
-    </row>
-    <row r="296" ht="15">
+        <v>4839.6654319999998</v>
+      </c>
+    </row>
+    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A296" s="4" t="s">
         <v>9</v>
       </c>
@@ -8374,10 +8351,10 @@
         <v>49</v>
       </c>
       <c r="G296" s="5">
-        <v>3083.092972</v>
-      </c>
-    </row>
-    <row r="297" ht="15">
+        <v>3083.0929719999999</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A297" s="4" t="s">
         <v>9</v>
       </c>
@@ -8397,10 +8374,10 @@
         <v>143</v>
       </c>
       <c r="G297" s="5">
-        <v>1373.810807</v>
-      </c>
-    </row>
-    <row r="298" ht="15">
+        <v>1373.8108070000001</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A298" s="4" t="s">
         <v>9</v>
       </c>
@@ -8423,7 +8400,7 @@
         <v>1222.528697</v>
       </c>
     </row>
-    <row r="299" ht="15">
+    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A299" s="4" t="s">
         <v>9</v>
       </c>
@@ -8443,10 +8420,10 @@
         <v>16</v>
       </c>
       <c r="G299" s="5">
-        <v>1245.212969</v>
-      </c>
-    </row>
-    <row r="300" ht="15">
+        <v>1245.2129689999999</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A300" s="4" t="s">
         <v>9</v>
       </c>
@@ -8466,10 +8443,10 @@
         <v>19</v>
       </c>
       <c r="G300" s="5">
-        <v>1569.650757</v>
-      </c>
-    </row>
-    <row r="301" ht="15">
+        <v>1569.6507570000001</v>
+      </c>
+    </row>
+    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A301" s="4" t="s">
         <v>9</v>
       </c>
@@ -8489,10 +8466,10 @@
         <v>22</v>
       </c>
       <c r="G301" s="5">
-        <v>1512.916231</v>
-      </c>
-    </row>
-    <row r="302" ht="15">
+        <v>1512.9162309999999</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A302" s="4" t="s">
         <v>9</v>
       </c>
@@ -8512,10 +8489,10 @@
         <v>25</v>
       </c>
       <c r="G302" s="5">
-        <v>1790.528346</v>
-      </c>
-    </row>
-    <row r="303" ht="15">
+        <v>1790.5283460000001</v>
+      </c>
+    </row>
+    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A303" s="4" t="s">
         <v>9</v>
       </c>
@@ -8535,10 +8512,10 @@
         <v>28</v>
       </c>
       <c r="G303" s="5">
-        <v>2269.423486</v>
-      </c>
-    </row>
-    <row r="304" ht="15">
+        <v>2269.4234860000001</v>
+      </c>
+    </row>
+    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A304" s="4" t="s">
         <v>9</v>
       </c>
@@ -8558,10 +8535,10 @@
         <v>31</v>
       </c>
       <c r="G304" s="5">
-        <v>2796.237508</v>
-      </c>
-    </row>
-    <row r="305" ht="15">
+        <v>2796.2375080000002</v>
+      </c>
+    </row>
+    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A305" s="4" t="s">
         <v>9</v>
       </c>
@@ -8581,10 +8558,10 @@
         <v>34</v>
       </c>
       <c r="G305" s="5">
-        <v>3346.535955</v>
-      </c>
-    </row>
-    <row r="306" ht="15">
+        <v>3346.5359549999998</v>
+      </c>
+    </row>
+    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A306" s="4" t="s">
         <v>9</v>
       </c>
@@ -8604,10 +8581,10 @@
         <v>37</v>
       </c>
       <c r="G306" s="5">
-        <v>4148.918355</v>
-      </c>
-    </row>
-    <row r="307" ht="15">
+        <v>4148.9183549999998</v>
+      </c>
+    </row>
+    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A307" s="4" t="s">
         <v>9</v>
       </c>
@@ -8630,7 +8607,7 @@
         <v>4810.628514</v>
       </c>
     </row>
-    <row r="308" ht="15">
+    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A308" s="4" t="s">
         <v>9</v>
       </c>
@@ -8650,10 +8627,10 @@
         <v>43</v>
       </c>
       <c r="G308" s="5">
-        <v>4445.557059</v>
-      </c>
-    </row>
-    <row r="309" ht="15">
+        <v>4445.5570589999998</v>
+      </c>
+    </row>
+    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A309" s="4" t="s">
         <v>9</v>
       </c>
@@ -8673,10 +8650,10 @@
         <v>46</v>
       </c>
       <c r="G309" s="5">
-        <v>4804.228665</v>
-      </c>
-    </row>
-    <row r="310" ht="15">
+        <v>4804.2286649999996</v>
+      </c>
+    </row>
+    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A310" s="4" t="s">
         <v>9</v>
       </c>
@@ -8699,7 +8676,7 @@
         <v>3113.34573</v>
       </c>
     </row>
-    <row r="311" ht="15">
+    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A311" s="4" t="s">
         <v>9</v>
       </c>
@@ -8719,10 +8696,10 @@
         <v>230</v>
       </c>
       <c r="G311" s="5">
-        <v>885.290314</v>
-      </c>
-    </row>
-    <row r="312" ht="15">
+        <v>885.29031399999997</v>
+      </c>
+    </row>
+    <row r="312" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A312" s="4" t="s">
         <v>9</v>
       </c>
@@ -8742,10 +8719,10 @@
         <v>13</v>
       </c>
       <c r="G312" s="5">
-        <v>1378.594406</v>
-      </c>
-    </row>
-    <row r="313" ht="15">
+        <v>1378.5944059999999</v>
+      </c>
+    </row>
+    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A313" s="4" t="s">
         <v>9</v>
       </c>
@@ -8765,10 +8742,10 @@
         <v>16</v>
       </c>
       <c r="G313" s="5">
-        <v>1339.401281</v>
-      </c>
-    </row>
-    <row r="314" ht="15">
+        <v>1339.4012809999999</v>
+      </c>
+    </row>
+    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A314" s="4" t="s">
         <v>9</v>
       </c>
@@ -8791,7 +8768,7 @@
         <v>1633.845683</v>
       </c>
     </row>
-    <row r="315" ht="15">
+    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A315" s="4" t="s">
         <v>9</v>
       </c>
@@ -8811,10 +8788,10 @@
         <v>22</v>
       </c>
       <c r="G315" s="5">
-        <v>1785.743286</v>
-      </c>
-    </row>
-    <row r="316" ht="15">
+        <v>1785.7432859999999</v>
+      </c>
+    </row>
+    <row r="316" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A316" s="4" t="s">
         <v>9</v>
       </c>
@@ -8834,10 +8811,10 @@
         <v>25</v>
       </c>
       <c r="G316" s="5">
-        <v>1814.219755</v>
-      </c>
-    </row>
-    <row r="317" ht="15">
+        <v>1814.2197550000001</v>
+      </c>
+    </row>
+    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A317" s="4" t="s">
         <v>9</v>
       </c>
@@ -8857,10 +8834,10 @@
         <v>28</v>
       </c>
       <c r="G317" s="5">
-        <v>2297.557567</v>
-      </c>
-    </row>
-    <row r="318" ht="15">
+        <v>2297.5575669999998</v>
+      </c>
+    </row>
+    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A318" s="4" t="s">
         <v>9</v>
       </c>
@@ -8880,10 +8857,10 @@
         <v>31</v>
       </c>
       <c r="G318" s="5">
-        <v>2800.446198</v>
-      </c>
-    </row>
-    <row r="319" ht="15">
+        <v>2800.4461980000001</v>
+      </c>
+    </row>
+    <row r="319" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A319" s="4" t="s">
         <v>9</v>
       </c>
@@ -8903,10 +8880,10 @@
         <v>34</v>
       </c>
       <c r="G319" s="5">
-        <v>3427.327555</v>
-      </c>
-    </row>
-    <row r="320" ht="15">
+        <v>3427.3275549999998</v>
+      </c>
+    </row>
+    <row r="320" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A320" s="4" t="s">
         <v>9</v>
       </c>
@@ -8926,10 +8903,10 @@
         <v>37</v>
       </c>
       <c r="G320" s="5">
-        <v>4260.629548</v>
-      </c>
-    </row>
-    <row r="321" ht="15">
+        <v>4260.6295479999999</v>
+      </c>
+    </row>
+    <row r="321" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A321" s="4" t="s">
         <v>9</v>
       </c>
@@ -8949,10 +8926,10 @@
         <v>40</v>
       </c>
       <c r="G321" s="5">
-        <v>4548.52145</v>
-      </c>
-    </row>
-    <row r="322" ht="15">
+        <v>4548.5214500000002</v>
+      </c>
+    </row>
+    <row r="322" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A322" s="4" t="s">
         <v>9</v>
       </c>
@@ -8972,10 +8949,10 @@
         <v>43</v>
       </c>
       <c r="G322" s="5">
-        <v>4556.407627</v>
-      </c>
-    </row>
-    <row r="323" ht="15">
+        <v>4556.4076269999996</v>
+      </c>
+    </row>
+    <row r="323" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A323" s="4" t="s">
         <v>9</v>
       </c>
@@ -8998,7 +8975,7 @@
         <v>4999.893795</v>
       </c>
     </row>
-    <row r="324" ht="15">
+    <row r="324" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A324" s="4" t="s">
         <v>9</v>
       </c>
@@ -9018,10 +8995,10 @@
         <v>49</v>
       </c>
       <c r="G324" s="5">
-        <v>3009.90225</v>
-      </c>
-    </row>
-    <row r="325" ht="15">
+        <v>3009.9022500000001</v>
+      </c>
+    </row>
+    <row r="325" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A325" s="4" t="s">
         <v>9</v>
       </c>
@@ -9044,7 +9021,7 @@
         <v>1045.489824</v>
       </c>
     </row>
-    <row r="326" ht="15">
+    <row r="326" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A326" s="4" t="s">
         <v>9</v>
       </c>
@@ -9064,10 +9041,10 @@
         <v>13</v>
       </c>
       <c r="G326" s="5">
-        <v>1108.553878</v>
-      </c>
-    </row>
-    <row r="327" ht="15">
+        <v>1108.5538779999999</v>
+      </c>
+    </row>
+    <row r="327" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A327" s="4" t="s">
         <v>9</v>
       </c>
@@ -9090,7 +9067,7 @@
         <v>1199.967621</v>
       </c>
     </row>
-    <row r="328" ht="15">
+    <row r="328" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A328" s="4" t="s">
         <v>9</v>
       </c>
@@ -9113,7 +9090,7 @@
         <v>1421.887657</v>
       </c>
     </row>
-    <row r="329" ht="15">
+    <row r="329" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A329" s="4" t="s">
         <v>9</v>
       </c>
@@ -9136,7 +9113,7 @@
         <v>1543.636949</v>
       </c>
     </row>
-    <row r="330" ht="15">
+    <row r="330" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A330" s="4" t="s">
         <v>9</v>
       </c>
@@ -9156,10 +9133,10 @@
         <v>25</v>
       </c>
       <c r="G330" s="5">
-        <v>1633.373283</v>
-      </c>
-    </row>
-    <row r="331" ht="15">
+        <v>1633.3732829999999</v>
+      </c>
+    </row>
+    <row r="331" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A331" s="4" t="s">
         <v>9</v>
       </c>
@@ -9179,10 +9156,10 @@
         <v>28</v>
       </c>
       <c r="G331" s="5">
-        <v>2093.462791</v>
-      </c>
-    </row>
-    <row r="332" ht="15">
+        <v>2093.4627909999999</v>
+      </c>
+    </row>
+    <row r="332" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A332" s="4" t="s">
         <v>9</v>
       </c>
@@ -9205,7 +9182,7 @@
         <v>2658.719016</v>
       </c>
     </row>
-    <row r="333" ht="15">
+    <row r="333" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A333" s="4" t="s">
         <v>9</v>
       </c>
@@ -9225,10 +9202,10 @@
         <v>34</v>
       </c>
       <c r="G333" s="5">
-        <v>2956.571301</v>
-      </c>
-    </row>
-    <row r="334" ht="15">
+        <v>2956.5713009999999</v>
+      </c>
+    </row>
+    <row r="334" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A334" s="4" t="s">
         <v>9</v>
       </c>
@@ -9248,10 +9225,10 @@
         <v>37</v>
       </c>
       <c r="G334" s="5">
-        <v>3741.137372</v>
-      </c>
-    </row>
-    <row r="335" ht="15">
+        <v>3741.1373720000001</v>
+      </c>
+    </row>
+    <row r="335" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A335" s="4" t="s">
         <v>9</v>
       </c>
@@ -9271,10 +9248,10 @@
         <v>40</v>
       </c>
       <c r="G335" s="5">
-        <v>4869.443533</v>
-      </c>
-    </row>
-    <row r="336" ht="15">
+        <v>4869.4435329999997</v>
+      </c>
+    </row>
+    <row r="336" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A336" s="4" t="s">
         <v>9</v>
       </c>
@@ -9294,10 +9271,10 @@
         <v>43</v>
       </c>
       <c r="G336" s="5">
-        <v>4302.610153</v>
-      </c>
-    </row>
-    <row r="337" ht="15">
+        <v>4302.6101529999996</v>
+      </c>
+    </row>
+    <row r="337" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A337" s="4" t="s">
         <v>9</v>
       </c>
@@ -9317,10 +9294,10 @@
         <v>46</v>
       </c>
       <c r="G337" s="5">
-        <v>4717.654385</v>
-      </c>
-    </row>
-    <row r="338" ht="15">
+        <v>4717.6543849999998</v>
+      </c>
+    </row>
+    <row r="338" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A338" s="4" t="s">
         <v>9</v>
       </c>
@@ -9340,10 +9317,10 @@
         <v>49</v>
       </c>
       <c r="G338" s="5">
-        <v>2908.361403</v>
-      </c>
-    </row>
-    <row r="339" ht="15">
+        <v>2908.3614029999999</v>
+      </c>
+    </row>
+    <row r="339" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A339" s="4" t="s">
         <v>9</v>
       </c>
@@ -9363,10 +9340,10 @@
         <v>143</v>
       </c>
       <c r="G339" s="5">
-        <v>1028.461821</v>
-      </c>
-    </row>
-    <row r="340" ht="15">
+        <v>1028.4618210000001</v>
+      </c>
+    </row>
+    <row r="340" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A340" s="4" t="s">
         <v>9</v>
       </c>
@@ -9389,7 +9366,7 @@
         <v>1182.095296</v>
       </c>
     </row>
-    <row r="341" ht="15">
+    <row r="341" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A341" s="4" t="s">
         <v>9</v>
       </c>
@@ -9412,7 +9389,7 @@
         <v>1248.948218</v>
       </c>
     </row>
-    <row r="342" ht="15">
+    <row r="342" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A342" s="4" t="s">
         <v>9</v>
       </c>
@@ -9432,10 +9409,10 @@
         <v>19</v>
       </c>
       <c r="G342" s="5">
-        <v>1574.539085</v>
-      </c>
-    </row>
-    <row r="343" ht="15">
+        <v>1574.5390849999999</v>
+      </c>
+    </row>
+    <row r="343" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A343" s="4" t="s">
         <v>9</v>
       </c>
@@ -9455,10 +9432,10 @@
         <v>22</v>
       </c>
       <c r="G343" s="5">
-        <v>1593.030838</v>
-      </c>
-    </row>
-    <row r="344" ht="15">
+        <v>1593.0308379999999</v>
+      </c>
+    </row>
+    <row r="344" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A344" s="4" t="s">
         <v>9</v>
       </c>
@@ -9481,7 +9458,7 @@
         <v>1831.113578</v>
       </c>
     </row>
-    <row r="345" ht="15">
+    <row r="345" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A345" s="4" t="s">
         <v>9</v>
       </c>
@@ -9501,10 +9478,10 @@
         <v>28</v>
       </c>
       <c r="G345" s="5">
-        <v>2288.611528</v>
-      </c>
-    </row>
-    <row r="346" ht="15">
+        <v>2288.6115279999999</v>
+      </c>
+    </row>
+    <row r="346" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A346" s="4" t="s">
         <v>9</v>
       </c>
@@ -9524,10 +9501,10 @@
         <v>31</v>
       </c>
       <c r="G346" s="5">
-        <v>2655.853434</v>
-      </c>
-    </row>
-    <row r="347" ht="15">
+        <v>2655.8534340000001</v>
+      </c>
+    </row>
+    <row r="347" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A347" s="4" t="s">
         <v>9</v>
       </c>
@@ -9550,7 +9527,7 @@
         <v>2712.347514</v>
       </c>
     </row>
-    <row r="348" ht="15">
+    <row r="348" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A348" s="4" t="s">
         <v>9</v>
       </c>
@@ -9570,10 +9547,10 @@
         <v>37</v>
       </c>
       <c r="G348" s="5">
-        <v>3664.90905</v>
-      </c>
-    </row>
-    <row r="349" ht="15">
+        <v>3664.9090500000002</v>
+      </c>
+    </row>
+    <row r="349" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A349" s="4" t="s">
         <v>9</v>
       </c>
@@ -9593,10 +9570,10 @@
         <v>40</v>
       </c>
       <c r="G349" s="5">
-        <v>4512.559669</v>
-      </c>
-    </row>
-    <row r="350" ht="15">
+        <v>4512.5596690000002</v>
+      </c>
+    </row>
+    <row r="350" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A350" s="4" t="s">
         <v>9</v>
       </c>
@@ -9616,10 +9593,10 @@
         <v>43</v>
       </c>
       <c r="G350" s="5">
-        <v>4354.391068</v>
-      </c>
-    </row>
-    <row r="351" ht="15">
+        <v>4354.3910679999999</v>
+      </c>
+    </row>
+    <row r="351" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A351" s="4" t="s">
         <v>9</v>
       </c>
@@ -9639,10 +9616,10 @@
         <v>283</v>
       </c>
       <c r="G351" s="5">
-        <v>4773.782635</v>
-      </c>
-    </row>
-    <row r="352" ht="15">
+        <v>4773.7826349999996</v>
+      </c>
+    </row>
+    <row r="352" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A352" s="4" t="s">
         <v>9</v>
       </c>
@@ -9665,7 +9642,7 @@
         <v>3120.424074</v>
       </c>
     </row>
-    <row r="353" ht="15">
+    <row r="353" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A353" s="4" t="s">
         <v>9</v>
       </c>
@@ -9685,10 +9662,10 @@
         <v>250</v>
       </c>
       <c r="G353" s="5">
-        <v>955.2065</v>
-      </c>
-    </row>
-    <row r="354" ht="15">
+        <v>955.20650000000001</v>
+      </c>
+    </row>
+    <row r="354" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A354" s="4" t="s">
         <v>9</v>
       </c>
@@ -9708,10 +9685,10 @@
         <v>13</v>
       </c>
       <c r="G354" s="5">
-        <v>972.858157</v>
-      </c>
-    </row>
-    <row r="355" ht="15">
+        <v>972.85815700000001</v>
+      </c>
+    </row>
+    <row r="355" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A355" s="4" t="s">
         <v>9</v>
       </c>
@@ -9731,10 +9708,10 @@
         <v>16</v>
       </c>
       <c r="G355" s="5">
-        <v>1225.540676</v>
-      </c>
-    </row>
-    <row r="356" ht="15">
+        <v>1225.5406760000001</v>
+      </c>
+    </row>
+    <row r="356" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A356" s="4" t="s">
         <v>9</v>
       </c>
@@ -9754,10 +9731,10 @@
         <v>19</v>
       </c>
       <c r="G356" s="5">
-        <v>1586.706894</v>
-      </c>
-    </row>
-    <row r="357" ht="15">
+        <v>1586.7068939999999</v>
+      </c>
+    </row>
+    <row r="357" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A357" s="4" t="s">
         <v>9</v>
       </c>
@@ -9780,7 +9757,7 @@
         <v>1624.012156</v>
       </c>
     </row>
-    <row r="358" ht="15">
+    <row r="358" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A358" s="4" t="s">
         <v>9</v>
       </c>
@@ -9800,10 +9777,10 @@
         <v>25</v>
       </c>
       <c r="G358" s="5">
-        <v>1932.082155</v>
-      </c>
-    </row>
-    <row r="359" ht="15">
+        <v>1932.0821550000001</v>
+      </c>
+    </row>
+    <row r="359" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A359" s="4" t="s">
         <v>9</v>
       </c>
@@ -9823,10 +9800,10 @@
         <v>28</v>
       </c>
       <c r="G359" s="5">
-        <v>2208.803263</v>
-      </c>
-    </row>
-    <row r="360" ht="15">
+        <v>2208.8032629999998</v>
+      </c>
+    </row>
+    <row r="360" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A360" s="4" t="s">
         <v>9</v>
       </c>
@@ -9846,10 +9823,10 @@
         <v>31</v>
       </c>
       <c r="G360" s="5">
-        <v>2598.052308</v>
-      </c>
-    </row>
-    <row r="361" ht="15">
+        <v>2598.0523079999998</v>
+      </c>
+    </row>
+    <row r="361" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A361" s="4" t="s">
         <v>9</v>
       </c>
@@ -9872,7 +9849,7 @@
         <v>3154.824341</v>
       </c>
     </row>
-    <row r="362" ht="15">
+    <row r="362" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A362" s="4" t="s">
         <v>9</v>
       </c>
@@ -9892,10 +9869,10 @@
         <v>37</v>
       </c>
       <c r="G362" s="5">
-        <v>3925.909438</v>
-      </c>
-    </row>
-    <row r="363" ht="15">
+        <v>3925.9094380000001</v>
+      </c>
+    </row>
+    <row r="363" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A363" s="4" t="s">
         <v>9</v>
       </c>
@@ -9915,10 +9892,10 @@
         <v>40</v>
       </c>
       <c r="G363" s="5">
-        <v>4511.845192</v>
-      </c>
-    </row>
-    <row r="364" ht="15">
+        <v>4511.8451919999998</v>
+      </c>
+    </row>
+    <row r="364" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A364" s="4" t="s">
         <v>9</v>
       </c>
@@ -9938,10 +9915,10 @@
         <v>43</v>
       </c>
       <c r="G364" s="5">
-        <v>4540.962628</v>
-      </c>
-    </row>
-    <row r="365" ht="15">
+        <v>4540.9626280000002</v>
+      </c>
+    </row>
+    <row r="365" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A365" s="4" t="s">
         <v>9</v>
       </c>
@@ -9961,10 +9938,10 @@
         <v>283</v>
       </c>
       <c r="G365" s="5">
-        <v>4696.604596</v>
-      </c>
-    </row>
-    <row r="366" ht="15">
+        <v>4696.6045960000001</v>
+      </c>
+    </row>
+    <row r="366" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A366" s="4" t="s">
         <v>9</v>
       </c>
@@ -9984,10 +9961,10 @@
         <v>49</v>
       </c>
       <c r="G366" s="5">
-        <v>2588.617903</v>
-      </c>
-    </row>
-    <row r="367" ht="15">
+        <v>2588.6179029999998</v>
+      </c>
+    </row>
+    <row r="367" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A367" s="4" t="s">
         <v>9</v>
       </c>
@@ -10007,10 +9984,10 @@
         <v>291</v>
       </c>
       <c r="G367" s="5">
-        <v>806.907992</v>
-      </c>
-    </row>
-    <row r="368" ht="15">
+        <v>806.90799200000004</v>
+      </c>
+    </row>
+    <row r="368" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A368" s="4" t="s">
         <v>9</v>
       </c>
@@ -10030,10 +10007,10 @@
         <v>13</v>
       </c>
       <c r="G368" s="5">
-        <v>1154.600307</v>
-      </c>
-    </row>
-    <row r="369" ht="15">
+        <v>1154.6003069999999</v>
+      </c>
+    </row>
+    <row r="369" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A369" s="4" t="s">
         <v>9</v>
       </c>
@@ -10053,10 +10030,10 @@
         <v>16</v>
       </c>
       <c r="G369" s="5">
-        <v>1254.197158</v>
-      </c>
-    </row>
-    <row r="370" ht="15">
+        <v>1254.1971579999999</v>
+      </c>
+    </row>
+    <row r="370" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A370" s="4" t="s">
         <v>9</v>
       </c>
@@ -10079,7 +10056,7 @@
         <v>1557.734406</v>
       </c>
     </row>
-    <row r="371" ht="15">
+    <row r="371" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A371" s="4" t="s">
         <v>9</v>
       </c>
@@ -10099,10 +10076,10 @@
         <v>22</v>
       </c>
       <c r="G371" s="5">
-        <v>1503.491061</v>
-      </c>
-    </row>
-    <row r="372" ht="15">
+        <v>1503.4910609999999</v>
+      </c>
+    </row>
+    <row r="372" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A372" s="4" t="s">
         <v>9</v>
       </c>
@@ -10122,10 +10099,10 @@
         <v>25</v>
       </c>
       <c r="G372" s="5">
-        <v>1681.62271</v>
-      </c>
-    </row>
-    <row r="373" ht="15">
+        <v>1681.6227100000001</v>
+      </c>
+    </row>
+    <row r="373" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A373" s="4" t="s">
         <v>9</v>
       </c>
@@ -10145,10 +10122,10 @@
         <v>28</v>
       </c>
       <c r="G373" s="5">
-        <v>2211.663948</v>
-      </c>
-    </row>
-    <row r="374" ht="15">
+        <v>2211.6639479999999</v>
+      </c>
+    </row>
+    <row r="374" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A374" s="4" t="s">
         <v>9</v>
       </c>
@@ -10171,7 +10148,7 @@
         <v>2799.962184</v>
       </c>
     </row>
-    <row r="375" ht="15">
+    <row r="375" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A375" s="4" t="s">
         <v>9</v>
       </c>
@@ -10191,10 +10168,10 @@
         <v>34</v>
       </c>
       <c r="G375" s="5">
-        <v>2841.892811</v>
-      </c>
-    </row>
-    <row r="376" ht="15">
+        <v>2841.8928110000002</v>
+      </c>
+    </row>
+    <row r="376" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A376" s="4" t="s">
         <v>9</v>
       </c>
@@ -10214,10 +10191,10 @@
         <v>37</v>
       </c>
       <c r="G376" s="5">
-        <v>4076.713251</v>
-      </c>
-    </row>
-    <row r="377" ht="15">
+        <v>4076.7132510000001</v>
+      </c>
+    </row>
+    <row r="377" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A377" s="4" t="s">
         <v>9</v>
       </c>
@@ -10237,10 +10214,10 @@
         <v>40</v>
       </c>
       <c r="G377" s="5">
-        <v>4679.101438</v>
-      </c>
-    </row>
-    <row r="378" ht="15">
+        <v>4679.1014379999997</v>
+      </c>
+    </row>
+    <row r="378" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A378" s="4" t="s">
         <v>9</v>
       </c>
@@ -10260,10 +10237,10 @@
         <v>43</v>
       </c>
       <c r="G378" s="5">
-        <v>4412.920339</v>
-      </c>
-    </row>
-    <row r="379" ht="15">
+        <v>4412.9203390000002</v>
+      </c>
+    </row>
+    <row r="379" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A379" s="4" t="s">
         <v>9</v>
       </c>
@@ -10283,10 +10260,10 @@
         <v>283</v>
       </c>
       <c r="G379" s="5">
-        <v>4893.829895</v>
-      </c>
-    </row>
-    <row r="380" ht="15">
+        <v>4893.8298949999999</v>
+      </c>
+    </row>
+    <row r="380" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A380" s="4" t="s">
         <v>9</v>
       </c>
@@ -10309,7 +10286,7 @@
         <v>2890.199368</v>
       </c>
     </row>
-    <row r="381" ht="15">
+    <row r="381" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A381" s="4" t="s">
         <v>9</v>
       </c>
@@ -10329,10 +10306,10 @@
         <v>230</v>
       </c>
       <c r="G381" s="5">
-        <v>737.937625</v>
-      </c>
-    </row>
-    <row r="382" ht="15">
+        <v>737.93762500000003</v>
+      </c>
+    </row>
+    <row r="382" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A382" s="4" t="s">
         <v>9</v>
       </c>
@@ -10352,10 +10329,10 @@
         <v>13</v>
       </c>
       <c r="G382" s="5">
-        <v>997.996292</v>
-      </c>
-    </row>
-    <row r="383" ht="15">
+        <v>997.99629200000004</v>
+      </c>
+    </row>
+    <row r="383" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A383" s="4" t="s">
         <v>9</v>
       </c>
@@ -10375,10 +10352,10 @@
         <v>16</v>
       </c>
       <c r="G383" s="5">
-        <v>1251.03686</v>
-      </c>
-    </row>
-    <row r="384" ht="15">
+        <v>1251.0368599999999</v>
+      </c>
+    </row>
+    <row r="384" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A384" s="4" t="s">
         <v>9</v>
       </c>
@@ -10401,7 +10378,7 @@
         <v>1411.304414</v>
       </c>
     </row>
-    <row r="385" ht="15">
+    <row r="385" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A385" s="4" t="s">
         <v>9</v>
       </c>
@@ -10424,7 +10401,7 @@
         <v>1457.626004</v>
       </c>
     </row>
-    <row r="386" ht="15">
+    <row r="386" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A386" s="4" t="s">
         <v>9</v>
       </c>
@@ -10447,7 +10424,7 @@
         <v>1566.023907</v>
       </c>
     </row>
-    <row r="387" ht="15">
+    <row r="387" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A387" s="4" t="s">
         <v>9</v>
       </c>
@@ -10467,10 +10444,10 @@
         <v>28</v>
       </c>
       <c r="G387" s="5">
-        <v>2150.581617</v>
-      </c>
-    </row>
-    <row r="388" ht="15">
+        <v>2150.5816169999998</v>
+      </c>
+    </row>
+    <row r="388" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A388" s="4" t="s">
         <v>9</v>
       </c>
@@ -10493,7 +10470,7 @@
         <v>2399.07089</v>
       </c>
     </row>
-    <row r="389" ht="15">
+    <row r="389" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A389" s="4" t="s">
         <v>9</v>
       </c>
@@ -10513,10 +10490,10 @@
         <v>34</v>
       </c>
       <c r="G389" s="5">
-        <v>2892.770977</v>
-      </c>
-    </row>
-    <row r="390" ht="15">
+        <v>2892.7709770000001</v>
+      </c>
+    </row>
+    <row r="390" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A390" s="4" t="s">
         <v>9</v>
       </c>
@@ -10536,10 +10513,10 @@
         <v>37</v>
       </c>
       <c r="G390" s="5">
-        <v>3976.678575</v>
-      </c>
-    </row>
-    <row r="391" ht="15">
+        <v>3976.6785749999999</v>
+      </c>
+    </row>
+    <row r="391" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A391" s="4" t="s">
         <v>9</v>
       </c>
@@ -10559,10 +10536,10 @@
         <v>40</v>
       </c>
       <c r="G391" s="5">
-        <v>4655.106415</v>
-      </c>
-    </row>
-    <row r="392" ht="15">
+        <v>4655.1064150000002</v>
+      </c>
+    </row>
+    <row r="392" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A392" s="4" t="s">
         <v>9</v>
       </c>
@@ -10582,10 +10559,10 @@
         <v>43</v>
       </c>
       <c r="G392" s="5">
-        <v>4737.994179</v>
-      </c>
-    </row>
-    <row r="393" ht="15">
+        <v>4737.9941790000003</v>
+      </c>
+    </row>
+    <row r="393" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A393" s="4" t="s">
         <v>9</v>
       </c>
@@ -10605,10 +10582,10 @@
         <v>283</v>
       </c>
       <c r="G393" s="5">
-        <v>5202.250273</v>
-      </c>
-    </row>
-    <row r="394" ht="15">
+        <v>5202.2502729999997</v>
+      </c>
+    </row>
+    <row r="394" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A394" s="4" t="s">
         <v>9</v>
       </c>
@@ -10631,7 +10608,7 @@
         <v>3009.56178</v>
       </c>
     </row>
-    <row r="395" ht="15">
+    <row r="395" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A395" s="4" t="s">
         <v>9</v>
       </c>
@@ -10651,10 +10628,10 @@
         <v>291</v>
       </c>
       <c r="G395" s="5">
-        <v>1291.691649</v>
-      </c>
-    </row>
-    <row r="396" ht="15">
+        <v>1291.6916490000001</v>
+      </c>
+    </row>
+    <row r="396" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A396" s="4" t="s">
         <v>9</v>
       </c>
@@ -10674,10 +10651,10 @@
         <v>13</v>
       </c>
       <c r="G396" s="5">
-        <v>1198.16576</v>
-      </c>
-    </row>
-    <row r="397" ht="15">
+        <v>1198.1657600000001</v>
+      </c>
+    </row>
+    <row r="397" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A397" s="4" t="s">
         <v>9</v>
       </c>
@@ -10700,7 +10677,7 @@
         <v>1452.074932</v>
       </c>
     </row>
-    <row r="398" ht="15">
+    <row r="398" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A398" s="4" t="s">
         <v>9</v>
       </c>
@@ -10723,7 +10700,7 @@
         <v>1586.423536</v>
       </c>
     </row>
-    <row r="399" ht="15">
+    <row r="399" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A399" s="4" t="s">
         <v>9</v>
       </c>
@@ -10743,10 +10720,10 @@
         <v>22</v>
       </c>
       <c r="G399" s="5">
-        <v>1684.996479</v>
-      </c>
-    </row>
-    <row r="400" ht="15">
+        <v>1684.9964789999999</v>
+      </c>
+    </row>
+    <row r="400" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A400" s="4" t="s">
         <v>9</v>
       </c>
@@ -10766,10 +10743,10 @@
         <v>25</v>
       </c>
       <c r="G400" s="5">
-        <v>1893.411909</v>
-      </c>
-    </row>
-    <row r="401" ht="15">
+        <v>1893.4119089999999</v>
+      </c>
+    </row>
+    <row r="401" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A401" s="4" t="s">
         <v>9</v>
       </c>
@@ -10789,10 +10766,10 @@
         <v>28</v>
       </c>
       <c r="G401" s="5">
-        <v>2384.23877</v>
-      </c>
-    </row>
-    <row r="402" ht="15">
+        <v>2384.2387699999999</v>
+      </c>
+    </row>
+    <row r="402" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A402" s="4" t="s">
         <v>9</v>
       </c>
@@ -10812,10 +10789,10 @@
         <v>31</v>
       </c>
       <c r="G402" s="5">
-        <v>2562.739553</v>
-      </c>
-    </row>
-    <row r="403" ht="15">
+        <v>2562.7395529999999</v>
+      </c>
+    </row>
+    <row r="403" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A403" s="4" t="s">
         <v>9</v>
       </c>
@@ -10835,10 +10812,10 @@
         <v>34</v>
       </c>
       <c r="G403" s="5">
-        <v>3296.104787</v>
-      </c>
-    </row>
-    <row r="404" ht="15">
+        <v>3296.1047870000002</v>
+      </c>
+    </row>
+    <row r="404" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A404" s="4" t="s">
         <v>9</v>
       </c>
@@ -10858,10 +10835,10 @@
         <v>37</v>
       </c>
       <c r="G404" s="5">
-        <v>4046.23874</v>
-      </c>
-    </row>
-    <row r="405" ht="15">
+        <v>4046.2387399999998</v>
+      </c>
+    </row>
+    <row r="405" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A405" s="4" t="s">
         <v>9</v>
       </c>
@@ -10881,10 +10858,10 @@
         <v>40</v>
       </c>
       <c r="G405" s="5">
-        <v>4542.985024</v>
-      </c>
-    </row>
-    <row r="406" ht="15">
+        <v>4542.9850239999996</v>
+      </c>
+    </row>
+    <row r="406" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A406" s="4" t="s">
         <v>9</v>
       </c>
@@ -10904,10 +10881,10 @@
         <v>43</v>
       </c>
       <c r="G406" s="5">
-        <v>4298.311427</v>
-      </c>
-    </row>
-    <row r="407" ht="15">
+        <v>4298.3114269999996</v>
+      </c>
+    </row>
+    <row r="407" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A407" s="4" t="s">
         <v>9</v>
       </c>
@@ -10927,10 +10904,10 @@
         <v>283</v>
       </c>
       <c r="G407" s="5">
-        <v>4687.312542</v>
-      </c>
-    </row>
-    <row r="408" ht="15">
+        <v>4687.3125419999997</v>
+      </c>
+    </row>
+    <row r="408" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A408" s="4" t="s">
         <v>9</v>
       </c>
@@ -10950,10 +10927,10 @@
         <v>49</v>
       </c>
       <c r="G408" s="5">
-        <v>3249.928313</v>
-      </c>
-    </row>
-    <row r="409" ht="15">
+        <v>3249.9283129999999</v>
+      </c>
+    </row>
+    <row r="409" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A409" s="4" t="s">
         <v>9</v>
       </c>
@@ -10973,10 +10950,10 @@
         <v>291</v>
       </c>
       <c r="G409" s="5">
-        <v>1437.008232</v>
-      </c>
-    </row>
-    <row r="410" ht="15">
+        <v>1437.0082319999999</v>
+      </c>
+    </row>
+    <row r="410" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A410" s="4" t="s">
         <v>9</v>
       </c>
@@ -10999,7 +10976,7 @@
         <v>1127.058141</v>
       </c>
     </row>
-    <row r="411" ht="15">
+    <row r="411" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A411" s="4" t="s">
         <v>9</v>
       </c>
@@ -11022,7 +10999,7 @@
         <v>1152.044099</v>
       </c>
     </row>
-    <row r="412" ht="15">
+    <row r="412" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A412" s="4" t="s">
         <v>9</v>
       </c>
@@ -11045,7 +11022,7 @@
         <v>1497.652327</v>
       </c>
     </row>
-    <row r="413" ht="15">
+    <row r="413" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A413" s="4" t="s">
         <v>9</v>
       </c>
@@ -11065,10 +11042,10 @@
         <v>22</v>
       </c>
       <c r="G413" s="5">
-        <v>1500.67973</v>
-      </c>
-    </row>
-    <row r="414" ht="15">
+        <v>1500.6797300000001</v>
+      </c>
+    </row>
+    <row r="414" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A414" s="4" t="s">
         <v>9</v>
       </c>
@@ -11091,7 +11068,7 @@
         <v>1734.929807</v>
       </c>
     </row>
-    <row r="415" ht="15">
+    <row r="415" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A415" s="4" t="s">
         <v>9</v>
       </c>
@@ -11114,7 +11091,7 @@
         <v>2108.302709</v>
       </c>
     </row>
-    <row r="416" ht="15">
+    <row r="416" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A416" s="4" t="s">
         <v>9</v>
       </c>
@@ -11137,7 +11114,7 @@
         <v>2632.396076</v>
       </c>
     </row>
-    <row r="417" ht="15">
+    <row r="417" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A417" s="4" t="s">
         <v>9</v>
       </c>
@@ -11157,10 +11134,10 @@
         <v>34</v>
       </c>
       <c r="G417" s="5">
-        <v>3190.967841</v>
-      </c>
-    </row>
-    <row r="418" ht="15">
+        <v>3190.9678410000001</v>
+      </c>
+    </row>
+    <row r="418" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A418" s="4" t="s">
         <v>9</v>
       </c>
@@ -11183,7 +11160,7 @@
         <v>3737.663368</v>
       </c>
     </row>
-    <row r="419" ht="15">
+    <row r="419" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A419" s="4" t="s">
         <v>9</v>
       </c>
@@ -11203,10 +11180,10 @@
         <v>40</v>
       </c>
       <c r="G419" s="5">
-        <v>4477.360801</v>
-      </c>
-    </row>
-    <row r="420" ht="15">
+        <v>4477.3608009999998</v>
+      </c>
+    </row>
+    <row r="420" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A420" s="4" t="s">
         <v>9</v>
       </c>
@@ -11226,10 +11203,10 @@
         <v>43</v>
       </c>
       <c r="G420" s="5">
-        <v>4324.897874</v>
-      </c>
-    </row>
-    <row r="421" ht="15">
+        <v>4324.8978740000002</v>
+      </c>
+    </row>
+    <row r="421" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A421" s="4" t="s">
         <v>9</v>
       </c>
@@ -11249,10 +11226,10 @@
         <v>283</v>
       </c>
       <c r="G421" s="5">
-        <v>4825.184242</v>
-      </c>
-    </row>
-    <row r="422" ht="15">
+        <v>4825.1842420000003</v>
+      </c>
+    </row>
+    <row r="422" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A422" s="4" t="s">
         <v>9</v>
       </c>
@@ -11272,10 +11249,10 @@
         <v>49</v>
       </c>
       <c r="G422" s="5">
-        <v>3022.531659</v>
-      </c>
-    </row>
-    <row r="423" ht="15">
+        <v>3022.5316590000002</v>
+      </c>
+    </row>
+    <row r="423" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A423" s="4" t="s">
         <v>9</v>
       </c>
@@ -11295,10 +11272,10 @@
         <v>250</v>
       </c>
       <c r="G423" s="5">
-        <v>884.517667</v>
-      </c>
-    </row>
-    <row r="424" ht="15">
+        <v>884.51766699999996</v>
+      </c>
+    </row>
+    <row r="424" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A424" s="4" t="s">
         <v>9</v>
       </c>
@@ -11318,10 +11295,10 @@
         <v>13</v>
       </c>
       <c r="G424" s="5">
-        <v>982.313208</v>
-      </c>
-    </row>
-    <row r="425" ht="15">
+        <v>982.31320800000003</v>
+      </c>
+    </row>
+    <row r="425" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A425" s="4" t="s">
         <v>9</v>
       </c>
@@ -11344,7 +11321,7 @@
         <v>1111.961706</v>
       </c>
     </row>
-    <row r="426" ht="15">
+    <row r="426" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A426" s="4" t="s">
         <v>9</v>
       </c>
@@ -11367,7 +11344,7 @@
         <v>1590.053719</v>
       </c>
     </row>
-    <row r="427" ht="15">
+    <row r="427" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A427" s="4" t="s">
         <v>9</v>
       </c>
@@ -11387,10 +11364,10 @@
         <v>22</v>
       </c>
       <c r="G427" s="5">
-        <v>1611.302362</v>
-      </c>
-    </row>
-    <row r="428" ht="15">
+        <v>1611.3023619999999</v>
+      </c>
+    </row>
+    <row r="428" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A428" s="4" t="s">
         <v>9</v>
       </c>
@@ -11413,7 +11390,7 @@
         <v>1812.726373</v>
       </c>
     </row>
-    <row r="429" ht="15">
+    <row r="429" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A429" s="4" t="s">
         <v>9</v>
       </c>
@@ -11433,10 +11410,10 @@
         <v>28</v>
       </c>
       <c r="G429" s="5">
-        <v>2160.901407</v>
-      </c>
-    </row>
-    <row r="430" ht="15">
+        <v>2160.9014069999998</v>
+      </c>
+    </row>
+    <row r="430" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A430" s="4" t="s">
         <v>9</v>
       </c>
@@ -11459,7 +11436,7 @@
         <v>2490.245676</v>
       </c>
     </row>
-    <row r="431" ht="15">
+    <row r="431" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A431" s="4" t="s">
         <v>9</v>
       </c>
@@ -11479,10 +11456,10 @@
         <v>34</v>
       </c>
       <c r="G431" s="5">
-        <v>3057.076859</v>
-      </c>
-    </row>
-    <row r="432" ht="15">
+        <v>3057.0768589999998</v>
+      </c>
+    </row>
+    <row r="432" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A432" s="4" t="s">
         <v>9</v>
       </c>
@@ -11505,7 +11482,7 @@
         <v>3822.968715</v>
       </c>
     </row>
-    <row r="433" ht="15">
+    <row r="433" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A433" s="4" t="s">
         <v>9</v>
       </c>
@@ -11525,10 +11502,10 @@
         <v>40</v>
       </c>
       <c r="G433" s="5">
-        <v>4545.88587</v>
-      </c>
-    </row>
-    <row r="434" ht="15">
+        <v>4545.8858700000001</v>
+      </c>
+    </row>
+    <row r="434" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A434" s="4" t="s">
         <v>9</v>
       </c>
@@ -11548,10 +11525,10 @@
         <v>43</v>
       </c>
       <c r="G434" s="5">
-        <v>4136.111986</v>
-      </c>
-    </row>
-    <row r="435" ht="15">
+        <v>4136.1119859999999</v>
+      </c>
+    </row>
+    <row r="435" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A435" s="4" t="s">
         <v>9</v>
       </c>
@@ -11571,10 +11548,10 @@
         <v>283</v>
       </c>
       <c r="G435" s="5">
-        <v>4871.394503</v>
-      </c>
-    </row>
-    <row r="436" ht="15">
+        <v>4871.3945030000004</v>
+      </c>
+    </row>
+    <row r="436" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A436" s="4" t="s">
         <v>9</v>
       </c>
@@ -11597,7 +11574,7 @@
         <v>3078.06288</v>
       </c>
     </row>
-    <row r="437" ht="15">
+    <row r="437" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A437" s="4" t="s">
         <v>9</v>
       </c>
@@ -11617,10 +11594,10 @@
         <v>291</v>
       </c>
       <c r="G437" s="5">
-        <v>934.135064</v>
-      </c>
-    </row>
-    <row r="438" ht="15">
+        <v>934.13506400000006</v>
+      </c>
+    </row>
+    <row r="438" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A438" s="4" t="s">
         <v>9</v>
       </c>
@@ -11643,7 +11620,7 @@
         <v>1164.55645</v>
       </c>
     </row>
-    <row r="439" ht="15">
+    <row r="439" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A439" s="4" t="s">
         <v>9</v>
       </c>
@@ -11666,7 +11643,7 @@
         <v>1224.224833</v>
       </c>
     </row>
-    <row r="440" ht="15">
+    <row r="440" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A440" s="4" t="s">
         <v>9</v>
       </c>
@@ -11686,10 +11663,10 @@
         <v>19</v>
       </c>
       <c r="G440" s="5">
-        <v>1718.406087</v>
-      </c>
-    </row>
-    <row r="441" ht="15">
+        <v>1718.4060870000001</v>
+      </c>
+    </row>
+    <row r="441" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A441" s="4" t="s">
         <v>9</v>
       </c>
@@ -11709,10 +11686,10 @@
         <v>22</v>
       </c>
       <c r="G441" s="5">
-        <v>1589.785571</v>
-      </c>
-    </row>
-    <row r="442" ht="15">
+        <v>1589.7855709999999</v>
+      </c>
+    </row>
+    <row r="442" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A442" s="4" t="s">
         <v>9</v>
       </c>
@@ -11735,7 +11712,7 @@
         <v>1606.206584</v>
       </c>
     </row>
-    <row r="443" ht="15">
+    <row r="443" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A443" s="4" t="s">
         <v>9</v>
       </c>
@@ -11758,7 +11735,7 @@
         <v>2147.978963</v>
       </c>
     </row>
-    <row r="444" ht="15">
+    <row r="444" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A444" s="4" t="s">
         <v>9</v>
       </c>
@@ -11778,10 +11755,10 @@
         <v>31</v>
       </c>
       <c r="G444" s="5">
-        <v>2595.310137</v>
-      </c>
-    </row>
-    <row r="445" ht="15">
+        <v>2595.3101369999999</v>
+      </c>
+    </row>
+    <row r="445" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A445" s="4" t="s">
         <v>9</v>
       </c>
@@ -11801,10 +11778,10 @@
         <v>34</v>
       </c>
       <c r="G445" s="5">
-        <v>3233.806565</v>
-      </c>
-    </row>
-    <row r="446" ht="15">
+        <v>3233.8065649999999</v>
+      </c>
+    </row>
+    <row r="446" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A446" s="4" t="s">
         <v>9</v>
       </c>
@@ -11824,10 +11801,10 @@
         <v>37</v>
       </c>
       <c r="G446" s="5">
-        <v>3904.662</v>
-      </c>
-    </row>
-    <row r="447" ht="15">
+        <v>3904.6619999999998</v>
+      </c>
+    </row>
+    <row r="447" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A447" s="4" t="s">
         <v>9</v>
       </c>
@@ -11847,10 +11824,10 @@
         <v>40</v>
       </c>
       <c r="G447" s="5">
-        <v>4545.789368</v>
-      </c>
-    </row>
-    <row r="448" ht="15">
+        <v>4545.7893679999997</v>
+      </c>
+    </row>
+    <row r="448" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A448" s="4" t="s">
         <v>9</v>
       </c>
@@ -11870,10 +11847,10 @@
         <v>43</v>
       </c>
       <c r="G448" s="5">
-        <v>4685.138527</v>
-      </c>
-    </row>
-    <row r="449" ht="15">
+        <v>4685.1385270000001</v>
+      </c>
+    </row>
+    <row r="449" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A449" s="4" t="s">
         <v>9</v>
       </c>
@@ -11893,10 +11870,10 @@
         <v>283</v>
       </c>
       <c r="G449" s="5">
-        <v>4885.78049</v>
-      </c>
-    </row>
-    <row r="450" ht="15">
+        <v>4885.7804900000001</v>
+      </c>
+    </row>
+    <row r="450" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A450" s="4" t="s">
         <v>9</v>
       </c>
@@ -11916,10 +11893,10 @@
         <v>49</v>
       </c>
       <c r="G450" s="5">
-        <v>2963.706726</v>
-      </c>
-    </row>
-    <row r="451" ht="15">
+        <v>2963.7067259999999</v>
+      </c>
+    </row>
+    <row r="451" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A451" s="4" t="s">
         <v>9</v>
       </c>
@@ -11939,10 +11916,10 @@
         <v>230</v>
       </c>
       <c r="G451" s="5">
-        <v>946.910941</v>
-      </c>
-    </row>
-    <row r="452" ht="15">
+        <v>946.91094099999998</v>
+      </c>
+    </row>
+    <row r="452" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A452" s="4" t="s">
         <v>9</v>
       </c>
@@ -11962,10 +11939,10 @@
         <v>13</v>
       </c>
       <c r="G452" s="5">
-        <v>1042.02128</v>
-      </c>
-    </row>
-    <row r="453" ht="15">
+        <v>1042.0212799999999</v>
+      </c>
+    </row>
+    <row r="453" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A453" s="4" t="s">
         <v>9</v>
       </c>
@@ -11988,7 +11965,7 @@
         <v>1139.440775</v>
       </c>
     </row>
-    <row r="454" ht="15">
+    <row r="454" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A454" s="4" t="s">
         <v>9</v>
       </c>
@@ -12011,7 +11988,7 @@
         <v>1433.383595</v>
       </c>
     </row>
-    <row r="455" ht="15">
+    <row r="455" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A455" s="4" t="s">
         <v>9</v>
       </c>
@@ -12034,7 +12011,7 @@
         <v>1434.787278</v>
       </c>
     </row>
-    <row r="456" ht="15">
+    <row r="456" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A456" s="4" t="s">
         <v>9</v>
       </c>
@@ -12057,7 +12034,7 @@
         <v>1534.099839</v>
       </c>
     </row>
-    <row r="457" ht="15">
+    <row r="457" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A457" s="4" t="s">
         <v>9</v>
       </c>
@@ -12077,10 +12054,10 @@
         <v>28</v>
       </c>
       <c r="G457" s="5">
-        <v>2069.18926</v>
-      </c>
-    </row>
-    <row r="458" ht="15">
+        <v>2069.1892600000001</v>
+      </c>
+    </row>
+    <row r="458" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A458" s="4" t="s">
         <v>9</v>
       </c>
@@ -12100,10 +12077,10 @@
         <v>31</v>
       </c>
       <c r="G458" s="5">
-        <v>2299.578521</v>
-      </c>
-    </row>
-    <row r="459" ht="15">
+        <v>2299.5785209999999</v>
+      </c>
+    </row>
+    <row r="459" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A459" s="4" t="s">
         <v>9</v>
       </c>
@@ -12123,10 +12100,10 @@
         <v>34</v>
       </c>
       <c r="G459" s="5">
-        <v>3086.656132</v>
-      </c>
-    </row>
-    <row r="460" ht="15">
+        <v>3086.6561320000001</v>
+      </c>
+    </row>
+    <row r="460" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A460" s="4" t="s">
         <v>9</v>
       </c>
@@ -12146,10 +12123,10 @@
         <v>37</v>
       </c>
       <c r="G460" s="5">
-        <v>3849.288092</v>
-      </c>
-    </row>
-    <row r="461" ht="15">
+        <v>3849.2880919999998</v>
+      </c>
+    </row>
+    <row r="461" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A461" s="4" t="s">
         <v>9</v>
       </c>
@@ -12169,10 +12146,10 @@
         <v>40</v>
       </c>
       <c r="G461" s="5">
-        <v>4749.218528</v>
-      </c>
-    </row>
-    <row r="462" ht="15">
+        <v>4749.2185280000003</v>
+      </c>
+    </row>
+    <row r="462" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A462" s="4" t="s">
         <v>9</v>
       </c>
@@ -12192,10 +12169,10 @@
         <v>43</v>
       </c>
       <c r="G462" s="5">
-        <v>4980.096525</v>
-      </c>
-    </row>
-    <row r="463" ht="15">
+        <v>4980.0965249999999</v>
+      </c>
+    </row>
+    <row r="463" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A463" s="4" t="s">
         <v>9</v>
       </c>
@@ -12215,10 +12192,10 @@
         <v>283</v>
       </c>
       <c r="G463" s="5">
-        <v>4960.357641</v>
-      </c>
-    </row>
-    <row r="464" ht="15">
+        <v>4960.3576409999996</v>
+      </c>
+    </row>
+    <row r="464" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A464" s="4" t="s">
         <v>9</v>
       </c>
@@ -12238,10 +12215,10 @@
         <v>49</v>
       </c>
       <c r="G464" s="5">
-        <v>3078.759463</v>
-      </c>
-    </row>
-    <row r="465" ht="15">
+        <v>3078.7594629999999</v>
+      </c>
+    </row>
+    <row r="465" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A465" s="4" t="s">
         <v>9</v>
       </c>
@@ -12264,7 +12241,7 @@
         <v>1087.392587</v>
       </c>
     </row>
-    <row r="466" ht="15">
+    <row r="466" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A466" s="4" t="s">
         <v>9</v>
       </c>
@@ -12284,10 +12261,10 @@
         <v>13</v>
       </c>
       <c r="G466" s="5">
-        <v>813.698254</v>
-      </c>
-    </row>
-    <row r="467" ht="15">
+        <v>813.69825400000002</v>
+      </c>
+    </row>
+    <row r="467" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A467" s="4" t="s">
         <v>9</v>
       </c>
@@ -12307,10 +12284,10 @@
         <v>16</v>
       </c>
       <c r="G467" s="5">
-        <v>866.790768</v>
-      </c>
-    </row>
-    <row r="468" ht="15">
+        <v>866.79076799999996</v>
+      </c>
+    </row>
+    <row r="468" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A468" s="4" t="s">
         <v>9</v>
       </c>
@@ -12330,10 +12307,10 @@
         <v>19</v>
       </c>
       <c r="G468" s="5">
-        <v>1659.632428</v>
-      </c>
-    </row>
-    <row r="469" ht="15">
+        <v>1659.6324279999999</v>
+      </c>
+    </row>
+    <row r="469" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A469" s="4" t="s">
         <v>9</v>
       </c>
@@ -12356,7 +12333,7 @@
         <v>1569.256496</v>
       </c>
     </row>
-    <row r="470" ht="15">
+    <row r="470" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A470" s="4" t="s">
         <v>9</v>
       </c>
@@ -12376,10 +12353,10 @@
         <v>25</v>
       </c>
       <c r="G470" s="5">
-        <v>1674.582297</v>
-      </c>
-    </row>
-    <row r="471" ht="15">
+        <v>1674.5822969999999</v>
+      </c>
+    </row>
+    <row r="471" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A471" s="4" t="s">
         <v>9</v>
       </c>
@@ -12399,10 +12376,10 @@
         <v>28</v>
       </c>
       <c r="G471" s="5">
-        <v>2170.544644</v>
-      </c>
-    </row>
-    <row r="472" ht="15">
+        <v>2170.5446440000001</v>
+      </c>
+    </row>
+    <row r="472" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A472" s="4" t="s">
         <v>9</v>
       </c>
@@ -12422,10 +12399,10 @@
         <v>31</v>
       </c>
       <c r="G472" s="5">
-        <v>2658.432285</v>
-      </c>
-    </row>
-    <row r="473" ht="15">
+        <v>2658.4322849999999</v>
+      </c>
+    </row>
+    <row r="473" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A473" s="4" t="s">
         <v>9</v>
       </c>
@@ -12445,10 +12422,10 @@
         <v>34</v>
       </c>
       <c r="G473" s="5">
-        <v>3128.449784</v>
-      </c>
-    </row>
-    <row r="474" ht="15">
+        <v>3128.4497839999999</v>
+      </c>
+    </row>
+    <row r="474" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A474" s="4" t="s">
         <v>9</v>
       </c>
@@ -12468,10 +12445,10 @@
         <v>37</v>
       </c>
       <c r="G474" s="5">
-        <v>3887.819506</v>
-      </c>
-    </row>
-    <row r="475" ht="15">
+        <v>3887.8195059999998</v>
+      </c>
+    </row>
+    <row r="475" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A475" s="4" t="s">
         <v>9</v>
       </c>
@@ -12491,10 +12468,10 @@
         <v>40</v>
       </c>
       <c r="G475" s="5">
-        <v>4826.370916</v>
-      </c>
-    </row>
-    <row r="476" ht="15">
+        <v>4826.3709159999999</v>
+      </c>
+    </row>
+    <row r="476" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A476" s="4" t="s">
         <v>9</v>
       </c>
@@ -12517,7 +12494,7 @@
         <v>5495.082692</v>
       </c>
     </row>
-    <row r="477" ht="15">
+    <row r="477" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A477" s="4" t="s">
         <v>9</v>
       </c>
@@ -12537,10 +12514,10 @@
         <v>283</v>
       </c>
       <c r="G477" s="5">
-        <v>5091.896252</v>
-      </c>
-    </row>
-    <row r="478" ht="15">
+        <v>5091.8962519999995</v>
+      </c>
+    </row>
+    <row r="478" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A478" s="4" t="s">
         <v>9</v>
       </c>
@@ -12560,10 +12537,10 @@
         <v>49</v>
       </c>
       <c r="G478" s="5">
-        <v>2627.472042</v>
-      </c>
-    </row>
-    <row r="479" ht="15">
+        <v>2627.4720419999999</v>
+      </c>
+    </row>
+    <row r="479" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A479" s="4" t="s">
         <v>9</v>
       </c>
@@ -12586,7 +12563,7 @@
         <v>1233.266331</v>
       </c>
     </row>
-    <row r="480" ht="15">
+    <row r="480" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A480" s="4" t="s">
         <v>9</v>
       </c>
@@ -12609,7 +12586,7 @@
         <v>538.448216</v>
       </c>
     </row>
-    <row r="481" ht="15">
+    <row r="481" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A481" s="4" t="s">
         <v>9</v>
       </c>
@@ -12629,10 +12606,10 @@
         <v>16</v>
       </c>
       <c r="G481" s="5">
-        <v>865.278667</v>
-      </c>
-    </row>
-    <row r="482" ht="15">
+        <v>865.27866700000004</v>
+      </c>
+    </row>
+    <row r="482" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A482" s="4" t="s">
         <v>9</v>
       </c>
@@ -12652,10 +12629,10 @@
         <v>19</v>
       </c>
       <c r="G482" s="5">
-        <v>1749.386551</v>
-      </c>
-    </row>
-    <row r="483" ht="15">
+        <v>1749.3865510000001</v>
+      </c>
+    </row>
+    <row r="483" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A483" s="4" t="s">
         <v>9</v>
       </c>
@@ -12678,7 +12655,7 @@
         <v>1633.001606</v>
       </c>
     </row>
-    <row r="484" ht="15">
+    <row r="484" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A484" s="4" t="s">
         <v>9</v>
       </c>
@@ -12698,10 +12675,10 @@
         <v>25</v>
       </c>
       <c r="G484" s="5">
-        <v>1797.666388</v>
-      </c>
-    </row>
-    <row r="485" ht="15">
+        <v>1797.6663880000001</v>
+      </c>
+    </row>
+    <row r="485" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A485" s="4" t="s">
         <v>9</v>
       </c>
@@ -12721,10 +12698,10 @@
         <v>28</v>
       </c>
       <c r="G485" s="5">
-        <v>2206.846445</v>
-      </c>
-    </row>
-    <row r="486" ht="15">
+        <v>2206.8464450000001</v>
+      </c>
+    </row>
+    <row r="486" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A486" s="4" t="s">
         <v>9</v>
       </c>
@@ -12744,10 +12721,10 @@
         <v>31</v>
       </c>
       <c r="G486" s="5">
-        <v>2783.79446</v>
-      </c>
-    </row>
-    <row r="487" ht="15">
+        <v>2783.7944600000001</v>
+      </c>
+    </row>
+    <row r="487" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A487" s="4" t="s">
         <v>9</v>
       </c>
@@ -12767,10 +12744,10 @@
         <v>34</v>
       </c>
       <c r="G487" s="5">
-        <v>3000.983242</v>
-      </c>
-    </row>
-    <row r="488" ht="15">
+        <v>3000.9832419999998</v>
+      </c>
+    </row>
+    <row r="488" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A488" s="4" t="s">
         <v>9</v>
       </c>
@@ -12790,10 +12767,10 @@
         <v>37</v>
       </c>
       <c r="G488" s="5">
-        <v>3645.348844</v>
-      </c>
-    </row>
-    <row r="489" ht="15">
+        <v>3645.3488440000001</v>
+      </c>
+    </row>
+    <row r="489" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A489" s="4" t="s">
         <v>9</v>
       </c>
@@ -12813,10 +12790,10 @@
         <v>40</v>
       </c>
       <c r="G489" s="5">
-        <v>4449.508953</v>
-      </c>
-    </row>
-    <row r="490" ht="15">
+        <v>4449.5089529999996</v>
+      </c>
+    </row>
+    <row r="490" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A490" s="4" t="s">
         <v>9</v>
       </c>
@@ -12836,10 +12813,10 @@
         <v>328</v>
       </c>
       <c r="G490" s="5">
-        <v>4411.241803</v>
-      </c>
-    </row>
-    <row r="491" ht="15">
+        <v>4411.2418029999999</v>
+      </c>
+    </row>
+    <row r="491" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A491" s="4" t="s">
         <v>9</v>
       </c>
@@ -12859,10 +12836,10 @@
         <v>283</v>
       </c>
       <c r="G491" s="5">
-        <v>4429.402177</v>
-      </c>
-    </row>
-    <row r="492" ht="15">
+        <v>4429.4021769999999</v>
+      </c>
+    </row>
+    <row r="492" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A492" s="4" t="s">
         <v>9</v>
       </c>
@@ -12882,10 +12859,10 @@
         <v>49</v>
       </c>
       <c r="G492" s="5">
-        <v>2668.110431</v>
-      </c>
-    </row>
-    <row r="493" ht="15">
+        <v>2668.1104310000001</v>
+      </c>
+    </row>
+    <row r="493" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A493" s="4" t="s">
         <v>9</v>
       </c>
@@ -12905,10 +12882,10 @@
         <v>250</v>
       </c>
       <c r="G493" s="5">
-        <v>974.30621</v>
-      </c>
-    </row>
-    <row r="494" ht="15">
+        <v>974.30620999999996</v>
+      </c>
+    </row>
+    <row r="494" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A494" s="4" t="s">
         <v>9</v>
       </c>
@@ -12928,10 +12905,10 @@
         <v>13</v>
       </c>
       <c r="G494" s="5">
-        <v>1203.948291</v>
-      </c>
-    </row>
-    <row r="495" ht="15">
+        <v>1203.9482909999999</v>
+      </c>
+    </row>
+    <row r="495" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A495" s="4" t="s">
         <v>9</v>
       </c>
@@ -12954,7 +12931,7 @@
         <v>1283.347231</v>
       </c>
     </row>
-    <row r="496" ht="15">
+    <row r="496" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A496" s="4" t="s">
         <v>9</v>
       </c>
@@ -12974,10 +12951,10 @@
         <v>19</v>
       </c>
       <c r="G496" s="5">
-        <v>1822.673052</v>
-      </c>
-    </row>
-    <row r="497" ht="15">
+        <v>1822.6730520000001</v>
+      </c>
+    </row>
+    <row r="497" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A497" s="4" t="s">
         <v>9</v>
       </c>
@@ -12997,10 +12974,10 @@
         <v>22</v>
       </c>
       <c r="G497" s="5">
-        <v>1562.252947</v>
-      </c>
-    </row>
-    <row r="498" ht="15">
+        <v>1562.2529469999999</v>
+      </c>
+    </row>
+    <row r="498" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A498" s="4" t="s">
         <v>9</v>
       </c>
@@ -13023,7 +13000,7 @@
         <v>1409.06062</v>
       </c>
     </row>
-    <row r="499" ht="15">
+    <row r="499" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A499" s="4" t="s">
         <v>9</v>
       </c>
@@ -13046,7 +13023,7 @@
         <v>2018.7935</v>
       </c>
     </row>
-    <row r="500" ht="15">
+    <row r="500" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A500" s="4" t="s">
         <v>9</v>
       </c>
@@ -13066,10 +13043,10 @@
         <v>31</v>
       </c>
       <c r="G500" s="5">
-        <v>2303.648779</v>
-      </c>
-    </row>
-    <row r="501" ht="15">
+        <v>2303.6487790000001</v>
+      </c>
+    </row>
+    <row r="501" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A501" s="4" t="s">
         <v>9</v>
       </c>
@@ -13089,10 +13066,10 @@
         <v>34</v>
       </c>
       <c r="G501" s="5">
-        <v>3290.91378</v>
-      </c>
-    </row>
-    <row r="502" ht="15">
+        <v>3290.9137799999999</v>
+      </c>
+    </row>
+    <row r="502" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A502" s="4" t="s">
         <v>9</v>
       </c>
@@ -13112,10 +13089,10 @@
         <v>37</v>
       </c>
       <c r="G502" s="5">
-        <v>3697.067895</v>
-      </c>
-    </row>
-    <row r="503" ht="15">
+        <v>3697.0678950000001</v>
+      </c>
+    </row>
+    <row r="503" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A503" s="4" t="s">
         <v>9</v>
       </c>
@@ -13135,10 +13112,10 @@
         <v>40</v>
       </c>
       <c r="G503" s="5">
-        <v>4683.582382</v>
-      </c>
-    </row>
-    <row r="504" ht="15">
+        <v>4683.5823819999996</v>
+      </c>
+    </row>
+    <row r="504" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A504" s="4" t="s">
         <v>9</v>
       </c>
@@ -13161,7 +13138,7 @@
         <v>4482.651081</v>
       </c>
     </row>
-    <row r="505" ht="15">
+    <row r="505" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A505" s="4" t="s">
         <v>9</v>
       </c>
@@ -13181,10 +13158,10 @@
         <v>283</v>
       </c>
       <c r="G505" s="5">
-        <v>4405.982635</v>
-      </c>
-    </row>
-    <row r="506" ht="15">
+        <v>4405.9826350000003</v>
+      </c>
+    </row>
+    <row r="506" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A506" s="4" t="s">
         <v>9</v>
       </c>
@@ -13207,7 +13184,7 @@
         <v>2736.572776</v>
       </c>
     </row>
-    <row r="507" ht="15">
+    <row r="507" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A507" s="4" t="s">
         <v>9</v>
       </c>
@@ -13230,7 +13207,7 @@
         <v>1088.947551</v>
       </c>
     </row>
-    <row r="508" ht="15">
+    <row r="508" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A508" s="4" t="s">
         <v>9</v>
       </c>
@@ -13250,10 +13227,10 @@
         <v>13</v>
       </c>
       <c r="G508" s="5">
-        <v>1210.995213</v>
-      </c>
-    </row>
-    <row r="509" ht="15">
+        <v>1210.9952129999999</v>
+      </c>
+    </row>
+    <row r="509" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A509" s="4" t="s">
         <v>9</v>
       </c>
@@ -13273,10 +13250,10 @@
         <v>16</v>
       </c>
       <c r="G509" s="5">
-        <v>1408.850329</v>
-      </c>
-    </row>
-    <row r="510" ht="15">
+        <v>1408.8503290000001</v>
+      </c>
+    </row>
+    <row r="510" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A510" s="4" t="s">
         <v>9</v>
       </c>
@@ -13296,10 +13273,10 @@
         <v>19</v>
       </c>
       <c r="G510" s="5">
-        <v>1690.890262</v>
-      </c>
-    </row>
-    <row r="511" ht="15">
+        <v>1690.8902619999999</v>
+      </c>
+    </row>
+    <row r="511" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A511" s="4" t="s">
         <v>9</v>
       </c>
@@ -13319,10 +13296,10 @@
         <v>22</v>
       </c>
       <c r="G511" s="5">
-        <v>1435.4043</v>
-      </c>
-    </row>
-    <row r="512" ht="15">
+        <v>1435.4042999999999</v>
+      </c>
+    </row>
+    <row r="512" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A512" s="4" t="s">
         <v>9</v>
       </c>
@@ -13345,7 +13322,7 @@
         <v>1538.147921</v>
       </c>
     </row>
-    <row r="513" ht="15">
+    <row r="513" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A513" s="4" t="s">
         <v>9</v>
       </c>
@@ -13365,10 +13342,10 @@
         <v>28</v>
       </c>
       <c r="G513" s="5">
-        <v>2201.923537</v>
-      </c>
-    </row>
-    <row r="514" ht="15">
+        <v>2201.9235370000001</v>
+      </c>
+    </row>
+    <row r="514" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A514" s="4" t="s">
         <v>9</v>
       </c>
@@ -13388,10 +13365,10 @@
         <v>31</v>
       </c>
       <c r="G514" s="5">
-        <v>2429.828843</v>
-      </c>
-    </row>
-    <row r="515" ht="15">
+        <v>2429.8288429999998</v>
+      </c>
+    </row>
+    <row r="515" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A515" s="4" t="s">
         <v>9</v>
       </c>
@@ -13411,10 +13388,10 @@
         <v>34</v>
       </c>
       <c r="G515" s="5">
-        <v>3213.236325</v>
-      </c>
-    </row>
-    <row r="516" ht="15">
+        <v>3213.2363249999999</v>
+      </c>
+    </row>
+    <row r="516" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A516" s="4" t="s">
         <v>9</v>
       </c>
@@ -13434,10 +13411,10 @@
         <v>37</v>
       </c>
       <c r="G516" s="5">
-        <v>3439.618051</v>
-      </c>
-    </row>
-    <row r="517" ht="15">
+        <v>3439.6180509999999</v>
+      </c>
+    </row>
+    <row r="517" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A517" s="4" t="s">
         <v>9</v>
       </c>
@@ -13457,10 +13434,10 @@
         <v>40</v>
       </c>
       <c r="G517" s="5">
-        <v>4252.399517</v>
-      </c>
-    </row>
-    <row r="518" ht="15">
+        <v>4252.3995169999998</v>
+      </c>
+    </row>
+    <row r="518" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A518" s="4" t="s">
         <v>9</v>
       </c>
@@ -13480,10 +13457,10 @@
         <v>328</v>
       </c>
       <c r="G518" s="5">
-        <v>4264.241737</v>
-      </c>
-    </row>
-    <row r="519" ht="15">
+        <v>4264.2417370000003</v>
+      </c>
+    </row>
+    <row r="519" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A519" s="4" t="s">
         <v>9</v>
       </c>
@@ -13503,10 +13480,10 @@
         <v>283</v>
       </c>
       <c r="G519" s="5">
-        <v>4392.792262</v>
-      </c>
-    </row>
-    <row r="520" ht="15">
+        <v>4392.7922619999999</v>
+      </c>
+    </row>
+    <row r="520" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A520" s="4" t="s">
         <v>9</v>
       </c>
@@ -13526,10 +13503,10 @@
         <v>49</v>
       </c>
       <c r="G520" s="5">
-        <v>2712.296713</v>
-      </c>
-    </row>
-    <row r="521" ht="15">
+        <v>2712.2967130000002</v>
+      </c>
+    </row>
+    <row r="521" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A521" s="4" t="s">
         <v>9</v>
       </c>
@@ -13549,10 +13526,10 @@
         <v>230</v>
       </c>
       <c r="G521" s="5">
-        <v>862.879553</v>
-      </c>
-    </row>
-    <row r="522" ht="15">
+        <v>862.87955299999999</v>
+      </c>
+    </row>
+    <row r="522" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A522" s="4" t="s">
         <v>9</v>
       </c>
@@ -13572,10 +13549,10 @@
         <v>13</v>
       </c>
       <c r="G522" s="5">
-        <v>1048.337112</v>
-      </c>
-    </row>
-    <row r="523" ht="15">
+        <v>1048.3371119999999</v>
+      </c>
+    </row>
+    <row r="523" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A523" s="4" t="s">
         <v>9</v>
       </c>
@@ -13595,10 +13572,10 @@
         <v>16</v>
       </c>
       <c r="G523" s="5">
-        <v>1404.306483</v>
-      </c>
-    </row>
-    <row r="524" ht="15">
+        <v>1404.3064830000001</v>
+      </c>
+    </row>
+    <row r="524" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A524" s="4" t="s">
         <v>9</v>
       </c>
@@ -13618,10 +13595,10 @@
         <v>19</v>
       </c>
       <c r="G524" s="5">
-        <v>1709.533575</v>
-      </c>
-    </row>
-    <row r="525" ht="15">
+        <v>1709.5335749999999</v>
+      </c>
+    </row>
+    <row r="525" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A525" s="4" t="s">
         <v>9</v>
       </c>
@@ -13644,7 +13621,7 @@
         <v>1727.604973</v>
       </c>
     </row>
-    <row r="526" ht="15">
+    <row r="526" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A526" s="4" t="s">
         <v>9</v>
       </c>
@@ -13664,10 +13641,10 @@
         <v>25</v>
       </c>
       <c r="G526" s="5">
-        <v>1842.851511</v>
-      </c>
-    </row>
-    <row r="527" ht="15">
+        <v>1842.8515110000001</v>
+      </c>
+    </row>
+    <row r="527" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A527" s="4" t="s">
         <v>9</v>
       </c>
@@ -13687,10 +13664,10 @@
         <v>28</v>
       </c>
       <c r="G527" s="5">
-        <v>2264.375635</v>
-      </c>
-    </row>
-    <row r="528" ht="15">
+        <v>2264.3756349999999</v>
+      </c>
+    </row>
+    <row r="528" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A528" s="4" t="s">
         <v>9</v>
       </c>
@@ -13710,10 +13687,10 @@
         <v>31</v>
       </c>
       <c r="G528" s="5">
-        <v>2605.167913</v>
-      </c>
-    </row>
-    <row r="529" ht="15">
+        <v>2605.1679130000002</v>
+      </c>
+    </row>
+    <row r="529" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A529" s="4" t="s">
         <v>9</v>
       </c>
@@ -13733,10 +13710,10 @@
         <v>34</v>
       </c>
       <c r="G529" s="5">
-        <v>3459.002134</v>
-      </c>
-    </row>
-    <row r="530" ht="15">
+        <v>3459.0021339999998</v>
+      </c>
+    </row>
+    <row r="530" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A530" s="4" t="s">
         <v>9</v>
       </c>
@@ -13756,10 +13733,10 @@
         <v>37</v>
       </c>
       <c r="G530" s="5">
-        <v>4333.607362</v>
-      </c>
-    </row>
-    <row r="531" ht="15">
+        <v>4333.6073619999997</v>
+      </c>
+    </row>
+    <row r="531" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A531" s="4" t="s">
         <v>9</v>
       </c>
@@ -13779,10 +13756,10 @@
         <v>40</v>
       </c>
       <c r="G531" s="5">
-        <v>4952.465885</v>
-      </c>
-    </row>
-    <row r="532" ht="15">
+        <v>4952.4658849999996</v>
+      </c>
+    </row>
+    <row r="532" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A532" s="4" t="s">
         <v>9</v>
       </c>
@@ -13802,10 +13779,10 @@
         <v>328</v>
       </c>
       <c r="G532" s="5">
-        <v>4880.619673</v>
-      </c>
-    </row>
-    <row r="533" ht="15">
+        <v>4880.6196730000001</v>
+      </c>
+    </row>
+    <row r="533" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A533" s="4" t="s">
         <v>9</v>
       </c>
@@ -13825,10 +13802,10 @@
         <v>283</v>
       </c>
       <c r="G533" s="5">
-        <v>4736.377218</v>
-      </c>
-    </row>
-    <row r="534" ht="15">
+        <v>4736.3772179999996</v>
+      </c>
+    </row>
+    <row r="534" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A534" s="4" t="s">
         <v>9</v>
       </c>
@@ -13851,7 +13828,7 @@
         <v>2972.043874</v>
       </c>
     </row>
-    <row r="535" ht="15">
+    <row r="535" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A535" s="4" t="s">
         <v>9</v>
       </c>
@@ -13871,10 +13848,10 @@
         <v>291</v>
       </c>
       <c r="G535" s="5">
-        <v>1351.382763</v>
-      </c>
-    </row>
-    <row r="536" ht="15">
+        <v>1351.3827630000001</v>
+      </c>
+    </row>
+    <row r="536" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A536" s="4" t="s">
         <v>9</v>
       </c>
@@ -13894,10 +13871,10 @@
         <v>13</v>
       </c>
       <c r="G536" s="5">
-        <v>995.823052</v>
-      </c>
-    </row>
-    <row r="537" ht="15">
+        <v>995.82305199999996</v>
+      </c>
+    </row>
+    <row r="537" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A537" s="4" t="s">
         <v>9</v>
       </c>
@@ -13920,7 +13897,7 @@
         <v>1328.114114</v>
       </c>
     </row>
-    <row r="538" ht="15">
+    <row r="538" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A538" s="4" t="s">
         <v>9</v>
       </c>
@@ -13943,7 +13920,7 @@
         <v>1588.620445</v>
       </c>
     </row>
-    <row r="539" ht="15">
+    <row r="539" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A539" s="4" t="s">
         <v>9</v>
       </c>
@@ -13966,7 +13943,7 @@
         <v>1519.460403</v>
       </c>
     </row>
-    <row r="540" ht="15">
+    <row r="540" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A540" s="4" t="s">
         <v>9</v>
       </c>
@@ -13989,7 +13966,7 @@
         <v>1712.884059</v>
       </c>
     </row>
-    <row r="541" ht="15">
+    <row r="541" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A541" s="4" t="s">
         <v>9</v>
       </c>
@@ -14009,10 +13986,10 @@
         <v>28</v>
       </c>
       <c r="G541" s="5">
-        <v>2020.215679</v>
-      </c>
-    </row>
-    <row r="542" ht="15">
+        <v>2020.2156789999999</v>
+      </c>
+    </row>
+    <row r="542" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A542" s="4" t="s">
         <v>9</v>
       </c>
@@ -14032,10 +14009,10 @@
         <v>31</v>
       </c>
       <c r="G542" s="5">
-        <v>2510.511245</v>
-      </c>
-    </row>
-    <row r="543" ht="15">
+        <v>2510.5112450000001</v>
+      </c>
+    </row>
+    <row r="543" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A543" s="4" t="s">
         <v>9</v>
       </c>
@@ -14055,10 +14032,10 @@
         <v>34</v>
       </c>
       <c r="G543" s="5">
-        <v>2845.123939</v>
-      </c>
-    </row>
-    <row r="544" ht="15">
+        <v>2845.1239390000001</v>
+      </c>
+    </row>
+    <row r="544" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A544" s="4" t="s">
         <v>9</v>
       </c>
@@ -14078,10 +14055,10 @@
         <v>37</v>
       </c>
       <c r="G544" s="5">
-        <v>3643.373667</v>
-      </c>
-    </row>
-    <row r="545" ht="15">
+        <v>3643.3736669999998</v>
+      </c>
+    </row>
+    <row r="545" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A545" s="4" t="s">
         <v>9</v>
       </c>
@@ -14101,10 +14078,10 @@
         <v>40</v>
       </c>
       <c r="G545" s="5">
-        <v>4395.082164</v>
-      </c>
-    </row>
-    <row r="546" ht="15">
+        <v>4395.0821640000004</v>
+      </c>
+    </row>
+    <row r="546" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A546" s="4" t="s">
         <v>9</v>
       </c>
@@ -14124,10 +14101,10 @@
         <v>328</v>
       </c>
       <c r="G546" s="5">
-        <v>4343.04308</v>
-      </c>
-    </row>
-    <row r="547" ht="15">
+        <v>4343.0430800000004</v>
+      </c>
+    </row>
+    <row r="547" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A547" s="4" t="s">
         <v>9</v>
       </c>
@@ -14147,10 +14124,10 @@
         <v>283</v>
       </c>
       <c r="G547" s="5">
-        <v>4242.454168</v>
-      </c>
-    </row>
-    <row r="548" ht="15">
+        <v>4242.4541680000002</v>
+      </c>
+    </row>
+    <row r="548" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A548" s="4" t="s">
         <v>9</v>
       </c>
@@ -14170,10 +14147,10 @@
         <v>49</v>
       </c>
       <c r="G548" s="5">
-        <v>2497.456135</v>
-      </c>
-    </row>
-    <row r="549" ht="15">
+        <v>2497.4561349999999</v>
+      </c>
+    </row>
+    <row r="549" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A549" s="4" t="s">
         <v>9</v>
       </c>
@@ -14196,7 +14173,7 @@
         <v>1049.84653</v>
       </c>
     </row>
-    <row r="550" ht="15">
+    <row r="550" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A550" s="4" t="s">
         <v>9</v>
       </c>
@@ -14219,7 +14196,7 @@
         <v>962.17147</v>
       </c>
     </row>
-    <row r="551" ht="15">
+    <row r="551" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A551" s="4" t="s">
         <v>9</v>
       </c>
@@ -14239,10 +14216,10 @@
         <v>16</v>
       </c>
       <c r="G551" s="5">
-        <v>1153.275526</v>
-      </c>
-    </row>
-    <row r="552" ht="15">
+        <v>1153.2755259999999</v>
+      </c>
+    </row>
+    <row r="552" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A552" s="4" t="s">
         <v>9</v>
       </c>
@@ -14265,7 +14242,7 @@
         <v>1358.2</v>
       </c>
     </row>
-    <row r="553" ht="15">
+    <row r="553" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A553" s="4" t="s">
         <v>9</v>
       </c>
@@ -14288,7 +14265,7 @@
         <v>1483.888807</v>
       </c>
     </row>
-    <row r="554" ht="15">
+    <row r="554" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A554" s="4" t="s">
         <v>9</v>
       </c>
@@ -14311,7 +14288,7 @@
         <v>1574.513733</v>
       </c>
     </row>
-    <row r="555" ht="15">
+    <row r="555" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A555" s="4" t="s">
         <v>9</v>
       </c>
@@ -14331,10 +14308,10 @@
         <v>28</v>
       </c>
       <c r="G555" s="5">
-        <v>1980.194758</v>
-      </c>
-    </row>
-    <row r="556" ht="15">
+        <v>1980.1947580000001</v>
+      </c>
+    </row>
+    <row r="556" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A556" s="4" t="s">
         <v>9</v>
       </c>
@@ -14354,10 +14331,10 @@
         <v>31</v>
       </c>
       <c r="G556" s="5">
-        <v>2478.350255</v>
-      </c>
-    </row>
-    <row r="557" ht="15">
+        <v>2478.3502549999998</v>
+      </c>
+    </row>
+    <row r="557" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A557" s="4" t="s">
         <v>9</v>
       </c>
@@ -14377,10 +14354,10 @@
         <v>34</v>
       </c>
       <c r="G557" s="5">
-        <v>3037.936153</v>
-      </c>
-    </row>
-    <row r="558" ht="15">
+        <v>3037.9361530000001</v>
+      </c>
+    </row>
+    <row r="558" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A558" s="4" t="s">
         <v>9</v>
       </c>
@@ -14400,10 +14377,10 @@
         <v>37</v>
       </c>
       <c r="G558" s="5">
-        <v>3905.78662</v>
-      </c>
-    </row>
-    <row r="559" ht="15">
+        <v>3905.7866199999999</v>
+      </c>
+    </row>
+    <row r="559" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A559" s="4" t="s">
         <v>9</v>
       </c>
@@ -14423,10 +14400,10 @@
         <v>40</v>
       </c>
       <c r="G559" s="5">
-        <v>4649.970492</v>
-      </c>
-    </row>
-    <row r="560" ht="15">
+        <v>4649.9704920000004</v>
+      </c>
+    </row>
+    <row r="560" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A560" s="4" t="s">
         <v>9</v>
       </c>
@@ -14446,10 +14423,10 @@
         <v>328</v>
       </c>
       <c r="G560" s="5">
-        <v>4585.097246</v>
-      </c>
-    </row>
-    <row r="561" ht="15">
+        <v>4585.0972460000003</v>
+      </c>
+    </row>
+    <row r="561" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A561" s="4" t="s">
         <v>9</v>
       </c>
@@ -14469,10 +14446,10 @@
         <v>283</v>
       </c>
       <c r="G561" s="5">
-        <v>4453.263299</v>
-      </c>
-    </row>
-    <row r="562" ht="15">
+        <v>4453.2632990000002</v>
+      </c>
+    </row>
+    <row r="562" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A562" s="4" t="s">
         <v>9</v>
       </c>
@@ -14492,10 +14469,10 @@
         <v>49</v>
       </c>
       <c r="G562" s="5">
-        <v>3012.233895</v>
-      </c>
-    </row>
-    <row r="563" ht="15">
+        <v>3012.2338949999998</v>
+      </c>
+    </row>
+    <row r="563" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A563" s="4" t="s">
         <v>9</v>
       </c>
@@ -14515,10 +14492,10 @@
         <v>250</v>
       </c>
       <c r="G563" s="5">
-        <v>838.082097</v>
-      </c>
-    </row>
-    <row r="564" ht="15">
+        <v>838.08209699999998</v>
+      </c>
+    </row>
+    <row r="564" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A564" s="4" t="s">
         <v>9</v>
       </c>
@@ -14538,10 +14515,10 @@
         <v>13</v>
       </c>
       <c r="G564" s="5">
-        <v>1281.21841</v>
-      </c>
-    </row>
-    <row r="565" ht="15">
+        <v>1281.2184099999999</v>
+      </c>
+    </row>
+    <row r="565" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A565" s="4" t="s">
         <v>9</v>
       </c>
@@ -14564,7 +14541,7 @@
         <v>1354.467805</v>
       </c>
     </row>
-    <row r="566" ht="15">
+    <row r="566" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A566" s="4" t="s">
         <v>9</v>
       </c>
@@ -14584,10 +14561,10 @@
         <v>19</v>
       </c>
       <c r="G566" s="5">
-        <v>1730.736037</v>
-      </c>
-    </row>
-    <row r="567" ht="15">
+        <v>1730.7360369999999</v>
+      </c>
+    </row>
+    <row r="567" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A567" s="4" t="s">
         <v>9</v>
       </c>
@@ -14607,10 +14584,10 @@
         <v>22</v>
       </c>
       <c r="G567" s="5">
-        <v>1866.034202</v>
-      </c>
-    </row>
-    <row r="568" ht="15">
+        <v>1866.0342020000001</v>
+      </c>
+    </row>
+    <row r="568" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A568" s="4" t="s">
         <v>9</v>
       </c>
@@ -14630,10 +14607,10 @@
         <v>25</v>
       </c>
       <c r="G568" s="5">
-        <v>1728.581752</v>
-      </c>
-    </row>
-    <row r="569" ht="15">
+        <v>1728.5817520000001</v>
+      </c>
+    </row>
+    <row r="569" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A569" s="4" t="s">
         <v>9</v>
       </c>
@@ -14653,10 +14630,10 @@
         <v>28</v>
       </c>
       <c r="G569" s="5">
-        <v>2184.425769</v>
-      </c>
-    </row>
-    <row r="570" ht="15">
+        <v>2184.4257689999999</v>
+      </c>
+    </row>
+    <row r="570" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A570" s="4" t="s">
         <v>9</v>
       </c>
@@ -14676,10 +14653,10 @@
         <v>31</v>
       </c>
       <c r="G570" s="5">
-        <v>2563.64083</v>
-      </c>
-    </row>
-    <row r="571" ht="15">
+        <v>2563.6408299999998</v>
+      </c>
+    </row>
+    <row r="571" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A571" s="4" t="s">
         <v>9</v>
       </c>
@@ -14699,10 +14676,10 @@
         <v>34</v>
       </c>
       <c r="G571" s="5">
-        <v>3272.617708</v>
-      </c>
-    </row>
-    <row r="572" ht="15">
+        <v>3272.6177080000002</v>
+      </c>
+    </row>
+    <row r="572" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A572" s="4" t="s">
         <v>9</v>
       </c>
@@ -14722,10 +14699,10 @@
         <v>37</v>
       </c>
       <c r="G572" s="5">
-        <v>3895.669767</v>
-      </c>
-    </row>
-    <row r="573" ht="15">
+        <v>3895.6697669999999</v>
+      </c>
+    </row>
+    <row r="573" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A573" s="4" t="s">
         <v>9</v>
       </c>
@@ -14745,10 +14722,10 @@
         <v>40</v>
       </c>
       <c r="G573" s="5">
-        <v>4371.595391</v>
-      </c>
-    </row>
-    <row r="574" ht="15">
+        <v>4371.5953909999998</v>
+      </c>
+    </row>
+    <row r="574" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A574" s="4" t="s">
         <v>9</v>
       </c>
@@ -14768,10 +14745,10 @@
         <v>328</v>
       </c>
       <c r="G574" s="5">
-        <v>4639.926782</v>
-      </c>
-    </row>
-    <row r="575" ht="15">
+        <v>4639.9267819999995</v>
+      </c>
+    </row>
+    <row r="575" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A575" s="4" t="s">
         <v>9</v>
       </c>
@@ -14791,10 +14768,10 @@
         <v>283</v>
       </c>
       <c r="G575" s="5">
-        <v>4484.458467</v>
-      </c>
-    </row>
-    <row r="576" ht="15">
+        <v>4484.4584670000004</v>
+      </c>
+    </row>
+    <row r="576" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A576" s="4" t="s">
         <v>9</v>
       </c>
@@ -14814,10 +14791,10 @@
         <v>49</v>
       </c>
       <c r="G576" s="5">
-        <v>2734.544674</v>
-      </c>
-    </row>
-    <row r="577" ht="15">
+        <v>2734.5446740000002</v>
+      </c>
+    </row>
+    <row r="577" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A577" s="4" t="s">
         <v>9</v>
       </c>
@@ -14837,11 +14814,17 @@
         <v>381</v>
       </c>
       <c r="G577" s="5">
-        <v>951.731414</v>
+        <v>951.73141399999997</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="portrait"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{defa4170-0d19-0005-0004-bc88714345d2}" enabled="1" method="Standard" siteId="{0191da82-c548-4ad3-b19b-c1efdbf81bd0}" removed="0"/>
+</clbl:labelList>
 </file>
--- a/Programmes Seguimiento LE_2.xlsx
+++ b/Programmes Seguimiento LE_2.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429">
   <si>
     <t/>
   </si>
@@ -1261,6 +1261,48 @@
   </si>
   <si>
     <t>22:29:47</t>
+  </si>
+  <si>
+    <t>08:00:05</t>
+  </si>
+  <si>
+    <t>08:00:06</t>
+  </si>
+  <si>
+    <t>08:59:46</t>
+  </si>
+  <si>
+    <t>08:59:47</t>
+  </si>
+  <si>
+    <t>11:59:45</t>
+  </si>
+  <si>
+    <t>11:59:46</t>
+  </si>
+  <si>
+    <t>13:29:45</t>
+  </si>
+  <si>
+    <t>13:29:46</t>
+  </si>
+  <si>
+    <t>14:29:45</t>
+  </si>
+  <si>
+    <t>14:29:46</t>
+  </si>
+  <si>
+    <t>15:29:44</t>
+  </si>
+  <si>
+    <t>15:29:45</t>
+  </si>
+  <si>
+    <t>23:07:17</t>
+  </si>
+  <si>
+    <t>24:07:10</t>
   </si>
 </sst>
 </file>
@@ -1686,7 +1728,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:H563"/>
+  <dimension ref="A2:H577"/>
   <sheetData>
     <row r="2" ht="15">
       <c r="A2" s="1" t="s">
@@ -14617,8 +14659,330 @@
         <v>1009.58037</v>
       </c>
     </row>
+    <row r="564" ht="15">
+      <c r="A564" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B564" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C564" s="2">
+        <v>46069</v>
+      </c>
+      <c r="D564" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="E564" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="F564" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G564" s="5">
+        <v>1211.874644</v>
+      </c>
+    </row>
+    <row r="565" ht="15">
+      <c r="A565" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B565" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C565" s="2">
+        <v>46069</v>
+      </c>
+      <c r="D565" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="E565" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="F565" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G565" s="5">
+        <v>1135.685312</v>
+      </c>
+    </row>
+    <row r="566" ht="15">
+      <c r="A566" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B566" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C566" s="2">
+        <v>46069</v>
+      </c>
+      <c r="D566" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="E566" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="F566" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G566" s="5">
+        <v>1556.839711</v>
+      </c>
+    </row>
+    <row r="567" ht="15">
+      <c r="A567" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B567" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C567" s="2">
+        <v>46069</v>
+      </c>
+      <c r="D567" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="E567" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="F567" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G567" s="5">
+        <v>1506.804886</v>
+      </c>
+    </row>
+    <row r="568" ht="15">
+      <c r="A568" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B568" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C568" s="2">
+        <v>46069</v>
+      </c>
+      <c r="D568" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="E568" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="F568" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G568" s="5">
+        <v>1484.354852</v>
+      </c>
+    </row>
+    <row r="569" ht="15">
+      <c r="A569" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B569" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C569" s="2">
+        <v>46069</v>
+      </c>
+      <c r="D569" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="E569" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="F569" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G569" s="5">
+        <v>2202.382371</v>
+      </c>
+    </row>
+    <row r="570" ht="15">
+      <c r="A570" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B570" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C570" s="2">
+        <v>46069</v>
+      </c>
+      <c r="D570" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="E570" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F570" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G570" s="5">
+        <v>2446.268567</v>
+      </c>
+    </row>
+    <row r="571" ht="15">
+      <c r="A571" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B571" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C571" s="2">
+        <v>46069</v>
+      </c>
+      <c r="D571" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E571" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F571" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G571" s="5">
+        <v>3379.271963</v>
+      </c>
+    </row>
+    <row r="572" ht="15">
+      <c r="A572" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B572" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C572" s="2">
+        <v>46069</v>
+      </c>
+      <c r="D572" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E572" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="F572" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G572" s="5">
+        <v>4061.797943</v>
+      </c>
+    </row>
+    <row r="573" ht="15">
+      <c r="A573" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B573" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C573" s="2">
+        <v>46069</v>
+      </c>
+      <c r="D573" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="E573" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="F573" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G573" s="5">
+        <v>4853.346185</v>
+      </c>
+    </row>
+    <row r="574" ht="15">
+      <c r="A574" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B574" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C574" s="2">
+        <v>46069</v>
+      </c>
+      <c r="D574" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="E574" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="F574" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="G574" s="5">
+        <v>4336.800037</v>
+      </c>
+    </row>
+    <row r="575" ht="15">
+      <c r="A575" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B575" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C575" s="2">
+        <v>46069</v>
+      </c>
+      <c r="D575" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="E575" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F575" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="G575" s="5">
+        <v>4497.067733</v>
+      </c>
+    </row>
+    <row r="576" ht="15">
+      <c r="A576" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B576" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C576" s="2">
+        <v>46069</v>
+      </c>
+      <c r="D576" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E576" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F576" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G576" s="5">
+        <v>3102.176952</v>
+      </c>
+    </row>
+    <row r="577" ht="15">
+      <c r="A577" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B577" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C577" s="2">
+        <v>46069</v>
+      </c>
+      <c r="D577" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="E577" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="F577" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="G577" s="5">
+        <v>782.537258</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="5" fitToHeight="0" orientation="portrait"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait"/>
 </worksheet>
 </file>
--- a/Programmes Seguimiento LE_2.xlsx
+++ b/Programmes Seguimiento LE_2.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421">
   <si>
     <t/>
   </si>
@@ -1270,6 +1270,15 @@
   </si>
   <si>
     <t>24:06:35</t>
+  </si>
+  <si>
+    <t>19:29:49</t>
+  </si>
+  <si>
+    <t>23:07:00</t>
+  </si>
+  <si>
+    <t>24:04:31</t>
   </si>
 </sst>
 </file>
@@ -1695,7 +1704,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:H563"/>
+  <dimension ref="A2:H576"/>
   <sheetData>
     <row r="2" ht="15">
       <c r="A2" s="1" t="s">
@@ -14624,6 +14633,305 @@
       </c>
       <c r="G563" s="5">
         <v>1155.783385</v>
+      </c>
+    </row>
+    <row r="564" ht="15">
+      <c r="A564" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B564" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C564" s="2">
+        <v>46076</v>
+      </c>
+      <c r="D564" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="E564" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="F564" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G564" s="5">
+        <v>1282.511238</v>
+      </c>
+    </row>
+    <row r="565" ht="15">
+      <c r="A565" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B565" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C565" s="2">
+        <v>46076</v>
+      </c>
+      <c r="D565" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="E565" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="F565" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G565" s="5">
+        <v>1714.593709</v>
+      </c>
+    </row>
+    <row r="566" ht="15">
+      <c r="A566" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B566" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C566" s="2">
+        <v>46076</v>
+      </c>
+      <c r="D566" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E566" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="F566" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G566" s="5">
+        <v>1603.759728</v>
+      </c>
+    </row>
+    <row r="567" ht="15">
+      <c r="A567" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B567" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C567" s="2">
+        <v>46076</v>
+      </c>
+      <c r="D567" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E567" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F567" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G567" s="5">
+        <v>1726.368329</v>
+      </c>
+    </row>
+    <row r="568" ht="15">
+      <c r="A568" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B568" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C568" s="2">
+        <v>46076</v>
+      </c>
+      <c r="D568" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E568" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F568" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G568" s="5">
+        <v>2262.678001</v>
+      </c>
+    </row>
+    <row r="569" ht="15">
+      <c r="A569" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B569" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C569" s="2">
+        <v>46076</v>
+      </c>
+      <c r="D569" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E569" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F569" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G569" s="5">
+        <v>2827.519961</v>
+      </c>
+    </row>
+    <row r="570" ht="15">
+      <c r="A570" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B570" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C570" s="2">
+        <v>46076</v>
+      </c>
+      <c r="D570" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E570" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="F570" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G570" s="5">
+        <v>3068.906298</v>
+      </c>
+    </row>
+    <row r="571" ht="15">
+      <c r="A571" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B571" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C571" s="2">
+        <v>46076</v>
+      </c>
+      <c r="D571" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E571" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="F571" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G571" s="5">
+        <v>4168.699245</v>
+      </c>
+    </row>
+    <row r="572" ht="15">
+      <c r="A572" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B572" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C572" s="2">
+        <v>46076</v>
+      </c>
+      <c r="D572" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="E572" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="F572" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G572" s="5">
+        <v>4930.338373</v>
+      </c>
+    </row>
+    <row r="573" ht="15">
+      <c r="A573" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B573" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C573" s="2">
+        <v>46076</v>
+      </c>
+      <c r="D573" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="E573" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="F573" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G573" s="5">
+        <v>4868.081299</v>
+      </c>
+    </row>
+    <row r="574" ht="15">
+      <c r="A574" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B574" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C574" s="2">
+        <v>46076</v>
+      </c>
+      <c r="D574" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="E574" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F574" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G574" s="5">
+        <v>4481.129791</v>
+      </c>
+    </row>
+    <row r="575" ht="15">
+      <c r="A575" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B575" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C575" s="2">
+        <v>46076</v>
+      </c>
+      <c r="D575" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E575" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="F575" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G575" s="5">
+        <v>3178.623351</v>
+      </c>
+    </row>
+    <row r="576" ht="15">
+      <c r="A576" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B576" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C576" s="2">
+        <v>46076</v>
+      </c>
+      <c r="D576" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="E576" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="F576" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="G576" s="5">
+        <v>1078.128713</v>
       </c>
     </row>
   </sheetData>

--- a/Programmes Seguimiento LE_2.xlsx
+++ b/Programmes Seguimiento LE_2.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359">
   <si>
     <t/>
   </si>
@@ -1087,6 +1087,12 @@
   </si>
   <si>
     <t>09:00:17</t>
+  </si>
+  <si>
+    <t>06:56:53</t>
+  </si>
+  <si>
+    <t>24:07:28</t>
   </si>
 </sst>
 </file>
@@ -1512,7 +1518,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:H572"/>
+  <dimension ref="A2:H587"/>
   <sheetData>
     <row r="2" ht="15">
       <c r="A2" s="1" t="s">
@@ -14650,8 +14656,353 @@
         <v>884.764498</v>
       </c>
     </row>
+    <row r="573" ht="15">
+      <c r="A573" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B573" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C573" s="2">
+        <v>46135</v>
+      </c>
+      <c r="D573" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="E573" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="F573" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G573" s="5">
+        <v>1091.467123</v>
+      </c>
+    </row>
+    <row r="574" ht="15">
+      <c r="A574" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B574" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C574" s="2">
+        <v>46135</v>
+      </c>
+      <c r="D574" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="E574" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F574" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G574" s="5">
+        <v>1210.406712</v>
+      </c>
+    </row>
+    <row r="575" ht="15">
+      <c r="A575" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B575" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C575" s="2">
+        <v>46135</v>
+      </c>
+      <c r="D575" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E575" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F575" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G575" s="5">
+        <v>1405.267456</v>
+      </c>
+    </row>
+    <row r="576" ht="15">
+      <c r="A576" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B576" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C576" s="2">
+        <v>46135</v>
+      </c>
+      <c r="D576" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E576" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F576" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G576" s="5">
+        <v>1451.374467</v>
+      </c>
+    </row>
+    <row r="577" ht="15">
+      <c r="A577" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B577" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C577" s="2">
+        <v>46135</v>
+      </c>
+      <c r="D577" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E577" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F577" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G577" s="5">
+        <v>1566.749904</v>
+      </c>
+    </row>
+    <row r="578" ht="15">
+      <c r="A578" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B578" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C578" s="2">
+        <v>46135</v>
+      </c>
+      <c r="D578" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E578" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F578" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G578" s="5">
+        <v>2124.443002</v>
+      </c>
+    </row>
+    <row r="579" ht="15">
+      <c r="A579" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B579" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C579" s="2">
+        <v>46135</v>
+      </c>
+      <c r="D579" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E579" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F579" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G579" s="5">
+        <v>2445.677506</v>
+      </c>
+    </row>
+    <row r="580" ht="15">
+      <c r="A580" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B580" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C580" s="2">
+        <v>46135</v>
+      </c>
+      <c r="D580" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E580" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="F580" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G580" s="5">
+        <v>2921.657951</v>
+      </c>
+    </row>
+    <row r="581" ht="15">
+      <c r="A581" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B581" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C581" s="2">
+        <v>46135</v>
+      </c>
+      <c r="D581" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="E581" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F581" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="G581" s="5">
+        <v>3642.246231</v>
+      </c>
+    </row>
+    <row r="582" ht="15">
+      <c r="A582" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B582" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C582" s="2">
+        <v>46135</v>
+      </c>
+      <c r="D582" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E582" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F582" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G582" s="5">
+        <v>3888.297768</v>
+      </c>
+    </row>
+    <row r="583" ht="15">
+      <c r="A583" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B583" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C583" s="2">
+        <v>46135</v>
+      </c>
+      <c r="D583" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E583" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="F583" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G583" s="5">
+        <v>4566.948666</v>
+      </c>
+    </row>
+    <row r="584" ht="15">
+      <c r="A584" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B584" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C584" s="2">
+        <v>46135</v>
+      </c>
+      <c r="D584" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="E584" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="F584" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G584" s="5">
+        <v>4366.581751</v>
+      </c>
+    </row>
+    <row r="585" ht="15">
+      <c r="A585" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B585" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C585" s="2">
+        <v>46135</v>
+      </c>
+      <c r="D585" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="E585" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F585" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="G585" s="5">
+        <v>4111.706625</v>
+      </c>
+    </row>
+    <row r="586" ht="15">
+      <c r="A586" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B586" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C586" s="2">
+        <v>46135</v>
+      </c>
+      <c r="D586" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E586" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="F586" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G586" s="5">
+        <v>2639.980585</v>
+      </c>
+    </row>
+    <row r="587" ht="15">
+      <c r="A587" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B587" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C587" s="2">
+        <v>46135</v>
+      </c>
+      <c r="D587" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="E587" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="F587" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G587" s="5">
+        <v>1174.807646</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait"/>
+  <pageSetup paperSize="5" fitToHeight="0" orientation="portrait"/>
 </worksheet>
 </file>
--- a/Programmes Seguimiento LE_2.xlsx
+++ b/Programmes Seguimiento LE_2.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364">
   <si>
     <t/>
   </si>
@@ -1099,6 +1099,15 @@
   </si>
   <si>
     <t>24:06:09</t>
+  </si>
+  <si>
+    <t>07:59:24</t>
+  </si>
+  <si>
+    <t>07:59:25</t>
+  </si>
+  <si>
+    <t>24:07:08</t>
   </si>
 </sst>
 </file>
@@ -1524,7 +1533,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:H602"/>
+  <dimension ref="A2:H616"/>
   <sheetData>
     <row r="2" ht="15">
       <c r="A2" s="1" t="s">
@@ -15352,8 +15361,330 @@
         <v>840.397614</v>
       </c>
     </row>
+    <row r="603" ht="15">
+      <c r="A603" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B603" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C603" s="2">
+        <v>46140</v>
+      </c>
+      <c r="D603" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="E603" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="F603" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G603" s="5">
+        <v>952.984297</v>
+      </c>
+    </row>
+    <row r="604" ht="15">
+      <c r="A604" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B604" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C604" s="2">
+        <v>46140</v>
+      </c>
+      <c r="D604" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="E604" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F604" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G604" s="5">
+        <v>1086.521685</v>
+      </c>
+    </row>
+    <row r="605" ht="15">
+      <c r="A605" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B605" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C605" s="2">
+        <v>46140</v>
+      </c>
+      <c r="D605" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E605" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F605" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G605" s="5">
+        <v>1416.291135</v>
+      </c>
+    </row>
+    <row r="606" ht="15">
+      <c r="A606" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B606" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C606" s="2">
+        <v>46140</v>
+      </c>
+      <c r="D606" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E606" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F606" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G606" s="5">
+        <v>1643.989937</v>
+      </c>
+    </row>
+    <row r="607" ht="15">
+      <c r="A607" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B607" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C607" s="2">
+        <v>46140</v>
+      </c>
+      <c r="D607" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E607" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F607" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G607" s="5">
+        <v>1623.748738</v>
+      </c>
+    </row>
+    <row r="608" ht="15">
+      <c r="A608" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B608" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C608" s="2">
+        <v>46140</v>
+      </c>
+      <c r="D608" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E608" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F608" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G608" s="5">
+        <v>2329.139386</v>
+      </c>
+    </row>
+    <row r="609" ht="15">
+      <c r="A609" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B609" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C609" s="2">
+        <v>46140</v>
+      </c>
+      <c r="D609" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E609" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F609" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="G609" s="5">
+        <v>2668.204947</v>
+      </c>
+    </row>
+    <row r="610" ht="15">
+      <c r="A610" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B610" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C610" s="2">
+        <v>46140</v>
+      </c>
+      <c r="D610" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E610" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F610" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="G610" s="5">
+        <v>3180.595386</v>
+      </c>
+    </row>
+    <row r="611" ht="15">
+      <c r="A611" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B611" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C611" s="2">
+        <v>46140</v>
+      </c>
+      <c r="D611" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E611" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F611" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G611" s="5">
+        <v>3714.159851</v>
+      </c>
+    </row>
+    <row r="612" ht="15">
+      <c r="A612" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B612" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C612" s="2">
+        <v>46140</v>
+      </c>
+      <c r="D612" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="E612" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F612" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G612" s="5">
+        <v>4248.682222</v>
+      </c>
+    </row>
+    <row r="613" ht="15">
+      <c r="A613" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B613" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C613" s="2">
+        <v>46140</v>
+      </c>
+      <c r="D613" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E613" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="F613" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G613" s="5">
+        <v>4408.283647</v>
+      </c>
+    </row>
+    <row r="614" ht="15">
+      <c r="A614" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B614" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C614" s="2">
+        <v>46140</v>
+      </c>
+      <c r="D614" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="E614" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F614" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="G614" s="5">
+        <v>4163.167099</v>
+      </c>
+    </row>
+    <row r="615" ht="15">
+      <c r="A615" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B615" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C615" s="2">
+        <v>46140</v>
+      </c>
+      <c r="D615" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E615" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="F615" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G615" s="5">
+        <v>2694.397996</v>
+      </c>
+    </row>
+    <row r="616" ht="15">
+      <c r="A616" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B616" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C616" s="2">
+        <v>46140</v>
+      </c>
+      <c r="D616" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="E616" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="F616" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="G616" s="5">
+        <v>846.910185</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="5" fitToHeight="0" orientation="portrait"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait"/>
 </worksheet>
 </file>
--- a/Programmes Seguimiento LE_2.xlsx
+++ b/Programmes Seguimiento LE_2.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355">
   <si>
     <t/>
   </si>
@@ -778,6 +778,309 @@
   </si>
   <si>
     <t>24:08:06</t>
+  </si>
+  <si>
+    <t>06:57:28</t>
+  </si>
+  <si>
+    <t>08:00:06</t>
+  </si>
+  <si>
+    <t>08:00:07</t>
+  </si>
+  <si>
+    <t>14:29:57</t>
+  </si>
+  <si>
+    <t>18:30:05</t>
+  </si>
+  <si>
+    <t>19:29:56</t>
+  </si>
+  <si>
+    <t>19:29:57</t>
+  </si>
+  <si>
+    <t>20:30:04</t>
+  </si>
+  <si>
+    <t>20:30:05</t>
+  </si>
+  <si>
+    <t>21:30:04</t>
+  </si>
+  <si>
+    <t>21:30:05</t>
+  </si>
+  <si>
+    <t>23:06:24</t>
+  </si>
+  <si>
+    <t>24:03:35</t>
+  </si>
+  <si>
+    <t>06:57:04</t>
+  </si>
+  <si>
+    <t>07:59:42</t>
+  </si>
+  <si>
+    <t>07:59:43</t>
+  </si>
+  <si>
+    <t>21:29:59</t>
+  </si>
+  <si>
+    <t>24:05:53</t>
+  </si>
+  <si>
+    <t>06:57:12</t>
+  </si>
+  <si>
+    <t>08:00:38</t>
+  </si>
+  <si>
+    <t>08:00:39</t>
+  </si>
+  <si>
+    <t>15:30:05</t>
+  </si>
+  <si>
+    <t>23:07:30</t>
+  </si>
+  <si>
+    <t>23:07:31</t>
+  </si>
+  <si>
+    <t>24:18:54</t>
+  </si>
+  <si>
+    <t>08:00:00</t>
+  </si>
+  <si>
+    <t>08:00:01</t>
+  </si>
+  <si>
+    <t>21:30:02</t>
+  </si>
+  <si>
+    <t>23:07:33</t>
+  </si>
+  <si>
+    <t>24:07:57</t>
+  </si>
+  <si>
+    <t>06:56:58</t>
+  </si>
+  <si>
+    <t>13:30:04</t>
+  </si>
+  <si>
+    <t>21:30:06</t>
+  </si>
+  <si>
+    <t>21:30:07</t>
+  </si>
+  <si>
+    <t>23:06:54</t>
+  </si>
+  <si>
+    <t>23:06:55</t>
+  </si>
+  <si>
+    <t>24:12:05</t>
+  </si>
+  <si>
+    <t>08:01:19</t>
+  </si>
+  <si>
+    <t>08:01:20</t>
+  </si>
+  <si>
+    <t>21:29:58</t>
+  </si>
+  <si>
+    <t>24:05:04</t>
+  </si>
+  <si>
+    <t>08:00:28</t>
+  </si>
+  <si>
+    <t>23:07:10</t>
+  </si>
+  <si>
+    <t>24:07:29</t>
+  </si>
+  <si>
+    <t>06:57:25</t>
+  </si>
+  <si>
+    <t>21:30:03</t>
+  </si>
+  <si>
+    <t>24:15:28</t>
+  </si>
+  <si>
+    <t>06:57:33</t>
+  </si>
+  <si>
+    <t>08:00:56</t>
+  </si>
+  <si>
+    <t>08:00:57</t>
+  </si>
+  <si>
+    <t>24:12:14</t>
+  </si>
+  <si>
+    <t>07:59:57</t>
+  </si>
+  <si>
+    <t>07:59:58</t>
+  </si>
+  <si>
+    <t>18:30:06</t>
+  </si>
+  <si>
+    <t>19:30:06</t>
+  </si>
+  <si>
+    <t>19:30:07</t>
+  </si>
+  <si>
+    <t>23:06:20</t>
+  </si>
+  <si>
+    <t>23:06:21</t>
+  </si>
+  <si>
+    <t>24:10:15</t>
+  </si>
+  <si>
+    <t>06:57:32</t>
+  </si>
+  <si>
+    <t>19:29:53</t>
+  </si>
+  <si>
+    <t>19:29:54</t>
+  </si>
+  <si>
+    <t>MI RIVAL</t>
+  </si>
+  <si>
+    <t>23:06:31</t>
+  </si>
+  <si>
+    <t>23:06:32</t>
+  </si>
+  <si>
+    <t>24:05:08</t>
+  </si>
+  <si>
+    <t>06:57:47</t>
+  </si>
+  <si>
+    <t>08:01:00</t>
+  </si>
+  <si>
+    <t>08:01:01</t>
+  </si>
+  <si>
+    <t>23:07:55</t>
+  </si>
+  <si>
+    <t>23:07:56</t>
+  </si>
+  <si>
+    <t>24:07:44</t>
+  </si>
+  <si>
+    <t>06:57:06</t>
+  </si>
+  <si>
+    <t>08:00:24</t>
+  </si>
+  <si>
+    <t>09:00:16</t>
+  </si>
+  <si>
+    <t>09:00:17</t>
+  </si>
+  <si>
+    <t>06:56:53</t>
+  </si>
+  <si>
+    <t>24:07:28</t>
+  </si>
+  <si>
+    <t>23:06:16</t>
+  </si>
+  <si>
+    <t>23:06:17</t>
+  </si>
+  <si>
+    <t>24:07:05</t>
+  </si>
+  <si>
+    <t>06:57:50</t>
+  </si>
+  <si>
+    <t>08:01:02</t>
+  </si>
+  <si>
+    <t>09:00:20</t>
+  </si>
+  <si>
+    <t>09:00:21</t>
+  </si>
+  <si>
+    <t>24:06:09</t>
+  </si>
+  <si>
+    <t>07:59:24</t>
+  </si>
+  <si>
+    <t>07:59:25</t>
+  </si>
+  <si>
+    <t>24:07:08</t>
+  </si>
+  <si>
+    <t>06:57:16</t>
+  </si>
+  <si>
+    <t>18:30:07</t>
+  </si>
+  <si>
+    <t>24:22:23</t>
+  </si>
+  <si>
+    <t>06:57:19</t>
+  </si>
+  <si>
+    <t>08:02:14</t>
+  </si>
+  <si>
+    <t>08:02:15</t>
+  </si>
+  <si>
+    <t>20:29:46</t>
+  </si>
+  <si>
+    <t>20:29:47</t>
+  </si>
+  <si>
+    <t>24:08:05</t>
+  </si>
+  <si>
+    <t>23:08:26</t>
+  </si>
+  <si>
+    <t>23:08:27</t>
+  </si>
+  <si>
+    <t>24:07:45</t>
   </si>
 </sst>
 </file>
@@ -1203,7 +1506,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:H293"/>
+  <dimension ref="A2:H588"/>
   <sheetData>
     <row r="2" ht="15">
       <c r="A2" s="1" t="s">
@@ -7922,6 +8225,6791 @@
       </c>
       <c r="G293" s="5">
         <v>890.702861</v>
+      </c>
+    </row>
+    <row r="294" ht="15">
+      <c r="A294" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B294" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C294" s="2">
+        <v>46118</v>
+      </c>
+      <c r="D294" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="E294" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="F294" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G294" s="5">
+        <v>862.425475</v>
+      </c>
+    </row>
+    <row r="295" ht="15">
+      <c r="A295" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B295" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C295" s="2">
+        <v>46118</v>
+      </c>
+      <c r="D295" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="E295" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F295" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G295" s="5">
+        <v>1015.584788</v>
+      </c>
+    </row>
+    <row r="296" ht="15">
+      <c r="A296" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B296" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C296" s="2">
+        <v>46118</v>
+      </c>
+      <c r="D296" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="E296" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F296" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G296" s="5">
+        <v>1620.208665</v>
+      </c>
+    </row>
+    <row r="297" ht="15">
+      <c r="A297" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B297" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C297" s="2">
+        <v>46118</v>
+      </c>
+      <c r="D297" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E297" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F297" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G297" s="5">
+        <v>1668.327547</v>
+      </c>
+    </row>
+    <row r="298" ht="15">
+      <c r="A298" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B298" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C298" s="2">
+        <v>46118</v>
+      </c>
+      <c r="D298" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="E298" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="F298" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G298" s="5">
+        <v>1557.122822</v>
+      </c>
+    </row>
+    <row r="299" ht="15">
+      <c r="A299" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B299" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C299" s="2">
+        <v>46118</v>
+      </c>
+      <c r="D299" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E299" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F299" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G299" s="5">
+        <v>2305.189241</v>
+      </c>
+    </row>
+    <row r="300" ht="15">
+      <c r="A300" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B300" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C300" s="2">
+        <v>46118</v>
+      </c>
+      <c r="D300" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E300" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F300" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="G300" s="5">
+        <v>2559.289542</v>
+      </c>
+    </row>
+    <row r="301" ht="15">
+      <c r="A301" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B301" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C301" s="2">
+        <v>46118</v>
+      </c>
+      <c r="D301" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E301" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="F301" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G301" s="5">
+        <v>2853.623062</v>
+      </c>
+    </row>
+    <row r="302" ht="15">
+      <c r="A302" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B302" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C302" s="2">
+        <v>46118</v>
+      </c>
+      <c r="D302" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="E302" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F302" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="G302" s="5">
+        <v>3336.53224</v>
+      </c>
+    </row>
+    <row r="303" ht="15">
+      <c r="A303" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B303" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C303" s="2">
+        <v>46118</v>
+      </c>
+      <c r="D303" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="E303" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="F303" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G303" s="5">
+        <v>3650.147169</v>
+      </c>
+    </row>
+    <row r="304" ht="15">
+      <c r="A304" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B304" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C304" s="2">
+        <v>46118</v>
+      </c>
+      <c r="D304" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="E304" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="F304" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G304" s="5">
+        <v>4424.612458</v>
+      </c>
+    </row>
+    <row r="305" ht="15">
+      <c r="A305" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B305" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C305" s="2">
+        <v>46118</v>
+      </c>
+      <c r="D305" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="E305" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="F305" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G305" s="5">
+        <v>4351.888551</v>
+      </c>
+    </row>
+    <row r="306" ht="15">
+      <c r="A306" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B306" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C306" s="2">
+        <v>46118</v>
+      </c>
+      <c r="D306" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="E306" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F306" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="G306" s="5">
+        <v>4103.91685</v>
+      </c>
+    </row>
+    <row r="307" ht="15">
+      <c r="A307" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B307" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C307" s="2">
+        <v>46118</v>
+      </c>
+      <c r="D307" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E307" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="F307" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G307" s="5">
+        <v>2250.903269</v>
+      </c>
+    </row>
+    <row r="308" ht="15">
+      <c r="A308" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B308" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C308" s="2">
+        <v>46118</v>
+      </c>
+      <c r="D308" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E308" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="F308" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G308" s="5">
+        <v>998.497514</v>
+      </c>
+    </row>
+    <row r="309" ht="15">
+      <c r="A309" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B309" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C309" s="2">
+        <v>46119</v>
+      </c>
+      <c r="D309" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="E309" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="F309" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G309" s="5">
+        <v>823.214294</v>
+      </c>
+    </row>
+    <row r="310" ht="15">
+      <c r="A310" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B310" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C310" s="2">
+        <v>46119</v>
+      </c>
+      <c r="D310" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="E310" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F310" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G310" s="5">
+        <v>1116.355228</v>
+      </c>
+    </row>
+    <row r="311" ht="15">
+      <c r="A311" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B311" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C311" s="2">
+        <v>46119</v>
+      </c>
+      <c r="D311" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="E311" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F311" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G311" s="5">
+        <v>1424.246415</v>
+      </c>
+    </row>
+    <row r="312" ht="15">
+      <c r="A312" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B312" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C312" s="2">
+        <v>46119</v>
+      </c>
+      <c r="D312" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E312" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F312" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G312" s="5">
+        <v>1550.649417</v>
+      </c>
+    </row>
+    <row r="313" ht="15">
+      <c r="A313" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B313" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C313" s="2">
+        <v>46119</v>
+      </c>
+      <c r="D313" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="E313" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F313" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G313" s="5">
+        <v>1716.049833</v>
+      </c>
+    </row>
+    <row r="314" ht="15">
+      <c r="A314" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B314" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C314" s="2">
+        <v>46119</v>
+      </c>
+      <c r="D314" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E314" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F314" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G314" s="5">
+        <v>2054.677492</v>
+      </c>
+    </row>
+    <row r="315" ht="15">
+      <c r="A315" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B315" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C315" s="2">
+        <v>46119</v>
+      </c>
+      <c r="D315" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E315" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F315" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="G315" s="5">
+        <v>2406.767247</v>
+      </c>
+    </row>
+    <row r="316" ht="15">
+      <c r="A316" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B316" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C316" s="2">
+        <v>46119</v>
+      </c>
+      <c r="D316" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="E316" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="F316" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G316" s="5">
+        <v>3067.911048</v>
+      </c>
+    </row>
+    <row r="317" ht="15">
+      <c r="A317" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B317" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C317" s="2">
+        <v>46119</v>
+      </c>
+      <c r="D317" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="E317" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="F317" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="G317" s="5">
+        <v>3127.98789</v>
+      </c>
+    </row>
+    <row r="318" ht="15">
+      <c r="A318" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B318" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C318" s="2">
+        <v>46119</v>
+      </c>
+      <c r="D318" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E318" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F318" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G318" s="5">
+        <v>3895.76118</v>
+      </c>
+    </row>
+    <row r="319" ht="15">
+      <c r="A319" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B319" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C319" s="2">
+        <v>46119</v>
+      </c>
+      <c r="D319" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E319" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F319" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G319" s="5">
+        <v>4463.046402</v>
+      </c>
+    </row>
+    <row r="320" ht="15">
+      <c r="A320" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B320" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C320" s="2">
+        <v>46119</v>
+      </c>
+      <c r="D320" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E320" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="F320" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G320" s="5">
+        <v>4476.896866</v>
+      </c>
+    </row>
+    <row r="321" ht="15">
+      <c r="A321" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B321" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C321" s="2">
+        <v>46119</v>
+      </c>
+      <c r="D321" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="E321" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F321" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="G321" s="5">
+        <v>4066.014106</v>
+      </c>
+    </row>
+    <row r="322" ht="15">
+      <c r="A322" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B322" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C322" s="2">
+        <v>46119</v>
+      </c>
+      <c r="D322" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E322" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="F322" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G322" s="5">
+        <v>2834.990017</v>
+      </c>
+    </row>
+    <row r="323" ht="15">
+      <c r="A323" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B323" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C323" s="2">
+        <v>46119</v>
+      </c>
+      <c r="D323" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="E323" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="F323" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G323" s="5">
+        <v>1167.074187</v>
+      </c>
+    </row>
+    <row r="324" ht="15">
+      <c r="A324" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B324" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C324" s="2">
+        <v>46120</v>
+      </c>
+      <c r="D324" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="E324" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="F324" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G324" s="5">
+        <v>1004.260469</v>
+      </c>
+    </row>
+    <row r="325" ht="15">
+      <c r="A325" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B325" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C325" s="2">
+        <v>46120</v>
+      </c>
+      <c r="D325" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="E325" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F325" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G325" s="5">
+        <v>1136.716206</v>
+      </c>
+    </row>
+    <row r="326" ht="15">
+      <c r="A326" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B326" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C326" s="2">
+        <v>46120</v>
+      </c>
+      <c r="D326" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="E326" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F326" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G326" s="5">
+        <v>1354.04624</v>
+      </c>
+    </row>
+    <row r="327" ht="15">
+      <c r="A327" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B327" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C327" s="2">
+        <v>46120</v>
+      </c>
+      <c r="D327" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E327" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F327" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G327" s="5">
+        <v>1550.314898</v>
+      </c>
+    </row>
+    <row r="328" ht="15">
+      <c r="A328" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B328" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C328" s="2">
+        <v>46120</v>
+      </c>
+      <c r="D328" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="E328" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F328" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G328" s="5">
+        <v>1494.476149</v>
+      </c>
+    </row>
+    <row r="329" ht="15">
+      <c r="A329" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B329" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C329" s="2">
+        <v>46120</v>
+      </c>
+      <c r="D329" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E329" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="F329" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G329" s="5">
+        <v>2041.753069</v>
+      </c>
+    </row>
+    <row r="330" ht="15">
+      <c r="A330" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B330" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C330" s="2">
+        <v>46120</v>
+      </c>
+      <c r="D330" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="E330" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F330" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="G330" s="5">
+        <v>2478.008569</v>
+      </c>
+    </row>
+    <row r="331" ht="15">
+      <c r="A331" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B331" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C331" s="2">
+        <v>46120</v>
+      </c>
+      <c r="D331" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="E331" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="F331" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G331" s="5">
+        <v>2826.828142</v>
+      </c>
+    </row>
+    <row r="332" ht="15">
+      <c r="A332" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B332" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C332" s="2">
+        <v>46120</v>
+      </c>
+      <c r="D332" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="E332" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="F332" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="G332" s="5">
+        <v>2789.359629</v>
+      </c>
+    </row>
+    <row r="333" ht="15">
+      <c r="A333" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B333" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C333" s="2">
+        <v>46120</v>
+      </c>
+      <c r="D333" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E333" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="F333" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G333" s="5">
+        <v>3686.405855</v>
+      </c>
+    </row>
+    <row r="334" ht="15">
+      <c r="A334" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B334" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C334" s="2">
+        <v>46120</v>
+      </c>
+      <c r="D334" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="E334" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F334" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G334" s="5">
+        <v>4617.855326</v>
+      </c>
+    </row>
+    <row r="335" ht="15">
+      <c r="A335" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B335" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C335" s="2">
+        <v>46120</v>
+      </c>
+      <c r="D335" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E335" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="F335" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G335" s="5">
+        <v>4684.138218</v>
+      </c>
+    </row>
+    <row r="336" ht="15">
+      <c r="A336" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B336" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C336" s="2">
+        <v>46120</v>
+      </c>
+      <c r="D336" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="E336" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="F336" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="G336" s="5">
+        <v>4011.61459</v>
+      </c>
+    </row>
+    <row r="337" ht="15">
+      <c r="A337" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B337" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C337" s="2">
+        <v>46120</v>
+      </c>
+      <c r="D337" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E337" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="F337" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G337" s="5">
+        <v>2697.635233</v>
+      </c>
+    </row>
+    <row r="338" ht="15">
+      <c r="A338" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B338" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C338" s="2">
+        <v>46120</v>
+      </c>
+      <c r="D338" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="E338" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="F338" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="G338" s="5">
+        <v>787.462766</v>
+      </c>
+    </row>
+    <row r="339" ht="15">
+      <c r="A339" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B339" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C339" s="2">
+        <v>46121</v>
+      </c>
+      <c r="D339" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E339" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="F339" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G339" s="5">
+        <v>836.371756</v>
+      </c>
+    </row>
+    <row r="340" ht="15">
+      <c r="A340" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B340" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C340" s="2">
+        <v>46121</v>
+      </c>
+      <c r="D340" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="E340" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F340" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G340" s="5">
+        <v>1086.962241</v>
+      </c>
+    </row>
+    <row r="341" ht="15">
+      <c r="A341" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B341" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C341" s="2">
+        <v>46121</v>
+      </c>
+      <c r="D341" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E341" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F341" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G341" s="5">
+        <v>1504.381946</v>
+      </c>
+    </row>
+    <row r="342" ht="15">
+      <c r="A342" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B342" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C342" s="2">
+        <v>46121</v>
+      </c>
+      <c r="D342" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E342" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F342" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G342" s="5">
+        <v>1420.273789</v>
+      </c>
+    </row>
+    <row r="343" ht="15">
+      <c r="A343" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B343" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C343" s="2">
+        <v>46121</v>
+      </c>
+      <c r="D343" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="E343" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F343" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G343" s="5">
+        <v>1361.9626</v>
+      </c>
+    </row>
+    <row r="344" ht="15">
+      <c r="A344" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B344" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C344" s="2">
+        <v>46121</v>
+      </c>
+      <c r="D344" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E344" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F344" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G344" s="5">
+        <v>1936.703559</v>
+      </c>
+    </row>
+    <row r="345" ht="15">
+      <c r="A345" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B345" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C345" s="2">
+        <v>46121</v>
+      </c>
+      <c r="D345" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E345" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F345" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="G345" s="5">
+        <v>2371.203835</v>
+      </c>
+    </row>
+    <row r="346" ht="15">
+      <c r="A346" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B346" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C346" s="2">
+        <v>46121</v>
+      </c>
+      <c r="D346" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E346" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="F346" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G346" s="5">
+        <v>2898.266428</v>
+      </c>
+    </row>
+    <row r="347" ht="15">
+      <c r="A347" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B347" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C347" s="2">
+        <v>46121</v>
+      </c>
+      <c r="D347" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="E347" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F347" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="G347" s="5">
+        <v>3354.855672</v>
+      </c>
+    </row>
+    <row r="348" ht="15">
+      <c r="A348" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B348" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C348" s="2">
+        <v>46121</v>
+      </c>
+      <c r="D348" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E348" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F348" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G348" s="5">
+        <v>3651.396128</v>
+      </c>
+    </row>
+    <row r="349" ht="15">
+      <c r="A349" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B349" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C349" s="2">
+        <v>46121</v>
+      </c>
+      <c r="D349" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E349" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F349" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G349" s="5">
+        <v>4380.072994</v>
+      </c>
+    </row>
+    <row r="350" ht="15">
+      <c r="A350" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B350" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C350" s="2">
+        <v>46121</v>
+      </c>
+      <c r="D350" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E350" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="F350" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G350" s="5">
+        <v>4090.557281</v>
+      </c>
+    </row>
+    <row r="351" ht="15">
+      <c r="A351" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B351" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C351" s="2">
+        <v>46121</v>
+      </c>
+      <c r="D351" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="E351" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F351" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="G351" s="5">
+        <v>3784.339731</v>
+      </c>
+    </row>
+    <row r="352" ht="15">
+      <c r="A352" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B352" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C352" s="2">
+        <v>46121</v>
+      </c>
+      <c r="D352" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E352" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="F352" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G352" s="5">
+        <v>2555.547908</v>
+      </c>
+    </row>
+    <row r="353" ht="15">
+      <c r="A353" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B353" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C353" s="2">
+        <v>46121</v>
+      </c>
+      <c r="D353" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E353" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="F353" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G353" s="5">
+        <v>1046.961942</v>
+      </c>
+    </row>
+    <row r="354" ht="15">
+      <c r="A354" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B354" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C354" s="2">
+        <v>46122</v>
+      </c>
+      <c r="D354" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="E354" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F354" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G354" s="5">
+        <v>762.617401</v>
+      </c>
+    </row>
+    <row r="355" ht="15">
+      <c r="A355" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B355" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C355" s="2">
+        <v>46122</v>
+      </c>
+      <c r="D355" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E355" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F355" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G355" s="5">
+        <v>1137.689863</v>
+      </c>
+    </row>
+    <row r="356" ht="15">
+      <c r="A356" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B356" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C356" s="2">
+        <v>46122</v>
+      </c>
+      <c r="D356" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E356" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F356" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G356" s="5">
+        <v>1505.873397</v>
+      </c>
+    </row>
+    <row r="357" ht="15">
+      <c r="A357" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B357" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C357" s="2">
+        <v>46122</v>
+      </c>
+      <c r="D357" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E357" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="F357" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G357" s="5">
+        <v>1486.458236</v>
+      </c>
+    </row>
+    <row r="358" ht="15">
+      <c r="A358" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B358" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C358" s="2">
+        <v>46122</v>
+      </c>
+      <c r="D358" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="E358" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F358" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G358" s="5">
+        <v>1611.324959</v>
+      </c>
+    </row>
+    <row r="359" ht="15">
+      <c r="A359" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B359" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C359" s="2">
+        <v>46122</v>
+      </c>
+      <c r="D359" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E359" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F359" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G359" s="5">
+        <v>2118.028004</v>
+      </c>
+    </row>
+    <row r="360" ht="15">
+      <c r="A360" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B360" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C360" s="2">
+        <v>46122</v>
+      </c>
+      <c r="D360" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E360" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="F360" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="G360" s="5">
+        <v>2714.516453</v>
+      </c>
+    </row>
+    <row r="361" ht="15">
+      <c r="A361" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B361" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C361" s="2">
+        <v>46122</v>
+      </c>
+      <c r="D361" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E361" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="F361" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G361" s="5">
+        <v>3315.478525</v>
+      </c>
+    </row>
+    <row r="362" ht="15">
+      <c r="A362" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B362" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C362" s="2">
+        <v>46122</v>
+      </c>
+      <c r="D362" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="E362" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="F362" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="G362" s="5">
+        <v>3206.405243</v>
+      </c>
+    </row>
+    <row r="363" ht="15">
+      <c r="A363" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B363" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C363" s="2">
+        <v>46122</v>
+      </c>
+      <c r="D363" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E363" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F363" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G363" s="5">
+        <v>3904.764419</v>
+      </c>
+    </row>
+    <row r="364" ht="15">
+      <c r="A364" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B364" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C364" s="2">
+        <v>46122</v>
+      </c>
+      <c r="D364" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E364" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="F364" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G364" s="5">
+        <v>4437.221962</v>
+      </c>
+    </row>
+    <row r="365" ht="15">
+      <c r="A365" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B365" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C365" s="2">
+        <v>46122</v>
+      </c>
+      <c r="D365" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="E365" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="F365" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G365" s="5">
+        <v>4293.446587</v>
+      </c>
+    </row>
+    <row r="366" ht="15">
+      <c r="A366" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B366" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C366" s="2">
+        <v>46122</v>
+      </c>
+      <c r="D366" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="E366" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="F366" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="G366" s="5">
+        <v>3761.372339</v>
+      </c>
+    </row>
+    <row r="367" ht="15">
+      <c r="A367" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B367" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C367" s="2">
+        <v>46122</v>
+      </c>
+      <c r="D367" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E367" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="F367" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G367" s="5">
+        <v>2426.455627</v>
+      </c>
+    </row>
+    <row r="368" ht="15">
+      <c r="A368" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B368" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C368" s="2">
+        <v>46122</v>
+      </c>
+      <c r="D368" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="E368" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="F368" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G368" s="5">
+        <v>1093.054214</v>
+      </c>
+    </row>
+    <row r="369" ht="15">
+      <c r="A369" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B369" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C369" s="2">
+        <v>46125</v>
+      </c>
+      <c r="D369" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="E369" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="F369" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G369" s="5">
+        <v>1061.564348</v>
+      </c>
+    </row>
+    <row r="370" ht="15">
+      <c r="A370" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B370" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C370" s="2">
+        <v>46125</v>
+      </c>
+      <c r="D370" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="E370" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F370" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G370" s="5">
+        <v>1054.554684</v>
+      </c>
+    </row>
+    <row r="371" ht="15">
+      <c r="A371" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B371" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C371" s="2">
+        <v>46125</v>
+      </c>
+      <c r="D371" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E371" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F371" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G371" s="5">
+        <v>1551.339498</v>
+      </c>
+    </row>
+    <row r="372" ht="15">
+      <c r="A372" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B372" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C372" s="2">
+        <v>46125</v>
+      </c>
+      <c r="D372" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E372" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F372" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G372" s="5">
+        <v>1405.328648</v>
+      </c>
+    </row>
+    <row r="373" ht="15">
+      <c r="A373" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B373" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C373" s="2">
+        <v>46125</v>
+      </c>
+      <c r="D373" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E373" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F373" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G373" s="5">
+        <v>1533.669266</v>
+      </c>
+    </row>
+    <row r="374" ht="15">
+      <c r="A374" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B374" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C374" s="2">
+        <v>46125</v>
+      </c>
+      <c r="D374" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E374" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F374" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G374" s="5">
+        <v>1848.441963</v>
+      </c>
+    </row>
+    <row r="375" ht="15">
+      <c r="A375" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B375" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C375" s="2">
+        <v>46125</v>
+      </c>
+      <c r="D375" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="E375" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="F375" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="G375" s="5">
+        <v>2411.819085</v>
+      </c>
+    </row>
+    <row r="376" ht="15">
+      <c r="A376" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B376" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C376" s="2">
+        <v>46125</v>
+      </c>
+      <c r="D376" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E376" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="F376" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G376" s="5">
+        <v>3061.022905</v>
+      </c>
+    </row>
+    <row r="377" ht="15">
+      <c r="A377" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B377" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C377" s="2">
+        <v>46125</v>
+      </c>
+      <c r="D377" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="E377" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F377" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="G377" s="5">
+        <v>3284.398215</v>
+      </c>
+    </row>
+    <row r="378" ht="15">
+      <c r="A378" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B378" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C378" s="2">
+        <v>46125</v>
+      </c>
+      <c r="D378" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E378" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F378" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G378" s="5">
+        <v>3649.501972</v>
+      </c>
+    </row>
+    <row r="379" ht="15">
+      <c r="A379" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B379" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C379" s="2">
+        <v>46125</v>
+      </c>
+      <c r="D379" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E379" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="F379" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G379" s="5">
+        <v>4289.06425</v>
+      </c>
+    </row>
+    <row r="380" ht="15">
+      <c r="A380" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B380" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C380" s="2">
+        <v>46125</v>
+      </c>
+      <c r="D380" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E380" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="F380" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G380" s="5">
+        <v>4189.166916</v>
+      </c>
+    </row>
+    <row r="381" ht="15">
+      <c r="A381" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B381" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C381" s="2">
+        <v>46125</v>
+      </c>
+      <c r="D381" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="E381" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F381" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="G381" s="5">
+        <v>3865.10565</v>
+      </c>
+    </row>
+    <row r="382" ht="15">
+      <c r="A382" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B382" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C382" s="2">
+        <v>46125</v>
+      </c>
+      <c r="D382" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E382" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="F382" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G382" s="5">
+        <v>2738.842112</v>
+      </c>
+    </row>
+    <row r="383" ht="15">
+      <c r="A383" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B383" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C383" s="2">
+        <v>46125</v>
+      </c>
+      <c r="D383" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E383" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="F383" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G383" s="5">
+        <v>1000.138122</v>
+      </c>
+    </row>
+    <row r="384" ht="15">
+      <c r="A384" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B384" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C384" s="2">
+        <v>46126</v>
+      </c>
+      <c r="D384" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="E384" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="F384" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G384" s="5">
+        <v>1055.066527</v>
+      </c>
+    </row>
+    <row r="385" ht="15">
+      <c r="A385" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B385" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C385" s="2">
+        <v>46126</v>
+      </c>
+      <c r="D385" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="E385" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="F385" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G385" s="5">
+        <v>1280.267844</v>
+      </c>
+    </row>
+    <row r="386" ht="15">
+      <c r="A386" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B386" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C386" s="2">
+        <v>46126</v>
+      </c>
+      <c r="D386" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="E386" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F386" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G386" s="5">
+        <v>1429.580868</v>
+      </c>
+    </row>
+    <row r="387" ht="15">
+      <c r="A387" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B387" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C387" s="2">
+        <v>46126</v>
+      </c>
+      <c r="D387" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E387" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F387" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G387" s="5">
+        <v>1520.641879</v>
+      </c>
+    </row>
+    <row r="388" ht="15">
+      <c r="A388" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B388" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C388" s="2">
+        <v>46126</v>
+      </c>
+      <c r="D388" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E388" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F388" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G388" s="5">
+        <v>1659.13913</v>
+      </c>
+    </row>
+    <row r="389" ht="15">
+      <c r="A389" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B389" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C389" s="2">
+        <v>46126</v>
+      </c>
+      <c r="D389" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E389" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="F389" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G389" s="5">
+        <v>2016.479538</v>
+      </c>
+    </row>
+    <row r="390" ht="15">
+      <c r="A390" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B390" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C390" s="2">
+        <v>46126</v>
+      </c>
+      <c r="D390" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E390" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="F390" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="G390" s="5">
+        <v>2616.03545</v>
+      </c>
+    </row>
+    <row r="391" ht="15">
+      <c r="A391" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B391" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C391" s="2">
+        <v>46126</v>
+      </c>
+      <c r="D391" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E391" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="F391" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G391" s="5">
+        <v>3087.345034</v>
+      </c>
+    </row>
+    <row r="392" ht="15">
+      <c r="A392" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B392" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C392" s="2">
+        <v>46126</v>
+      </c>
+      <c r="D392" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="E392" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F392" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="G392" s="5">
+        <v>3263.672736</v>
+      </c>
+    </row>
+    <row r="393" ht="15">
+      <c r="A393" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B393" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C393" s="2">
+        <v>46126</v>
+      </c>
+      <c r="D393" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E393" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F393" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G393" s="5">
+        <v>3433.109308</v>
+      </c>
+    </row>
+    <row r="394" ht="15">
+      <c r="A394" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B394" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C394" s="2">
+        <v>46126</v>
+      </c>
+      <c r="D394" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E394" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F394" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G394" s="5">
+        <v>4285.299432</v>
+      </c>
+    </row>
+    <row r="395" ht="15">
+      <c r="A395" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B395" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C395" s="2">
+        <v>46126</v>
+      </c>
+      <c r="D395" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="E395" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="F395" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G395" s="5">
+        <v>4359.411689</v>
+      </c>
+    </row>
+    <row r="396" ht="15">
+      <c r="A396" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B396" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C396" s="2">
+        <v>46126</v>
+      </c>
+      <c r="D396" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="E396" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F396" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="G396" s="5">
+        <v>4036.827223</v>
+      </c>
+    </row>
+    <row r="397" ht="15">
+      <c r="A397" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B397" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C397" s="2">
+        <v>46126</v>
+      </c>
+      <c r="D397" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="E397" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="F397" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G397" s="5">
+        <v>2573.673984</v>
+      </c>
+    </row>
+    <row r="398" ht="15">
+      <c r="A398" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B398" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C398" s="2">
+        <v>46126</v>
+      </c>
+      <c r="D398" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="E398" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="F398" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G398" s="5">
+        <v>892.780767</v>
+      </c>
+    </row>
+    <row r="399" ht="15">
+      <c r="A399" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B399" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C399" s="2">
+        <v>46127</v>
+      </c>
+      <c r="D399" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="E399" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="F399" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G399" s="5">
+        <v>967.554533</v>
+      </c>
+    </row>
+    <row r="400" ht="15">
+      <c r="A400" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B400" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C400" s="2">
+        <v>46127</v>
+      </c>
+      <c r="D400" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="E400" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F400" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G400" s="5">
+        <v>1128.989588</v>
+      </c>
+    </row>
+    <row r="401" ht="15">
+      <c r="A401" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B401" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C401" s="2">
+        <v>46127</v>
+      </c>
+      <c r="D401" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="E401" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F401" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G401" s="5">
+        <v>1453.36893</v>
+      </c>
+    </row>
+    <row r="402" ht="15">
+      <c r="A402" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B402" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C402" s="2">
+        <v>46127</v>
+      </c>
+      <c r="D402" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E402" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F402" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G402" s="5">
+        <v>1479.179238</v>
+      </c>
+    </row>
+    <row r="403" ht="15">
+      <c r="A403" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B403" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C403" s="2">
+        <v>46127</v>
+      </c>
+      <c r="D403" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E403" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F403" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G403" s="5">
+        <v>1725.84791</v>
+      </c>
+    </row>
+    <row r="404" ht="15">
+      <c r="A404" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B404" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C404" s="2">
+        <v>46127</v>
+      </c>
+      <c r="D404" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E404" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F404" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G404" s="5">
+        <v>2366.913391</v>
+      </c>
+    </row>
+    <row r="405" ht="15">
+      <c r="A405" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B405" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C405" s="2">
+        <v>46127</v>
+      </c>
+      <c r="D405" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E405" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="F405" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="G405" s="5">
+        <v>2786.677595</v>
+      </c>
+    </row>
+    <row r="406" ht="15">
+      <c r="A406" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B406" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C406" s="2">
+        <v>46127</v>
+      </c>
+      <c r="D406" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E406" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="F406" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G406" s="5">
+        <v>3105.934128</v>
+      </c>
+    </row>
+    <row r="407" ht="15">
+      <c r="A407" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B407" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C407" s="2">
+        <v>46127</v>
+      </c>
+      <c r="D407" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="E407" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F407" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="G407" s="5">
+        <v>3408.148646</v>
+      </c>
+    </row>
+    <row r="408" ht="15">
+      <c r="A408" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B408" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C408" s="2">
+        <v>46127</v>
+      </c>
+      <c r="D408" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="E408" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F408" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G408" s="5">
+        <v>3986.078693</v>
+      </c>
+    </row>
+    <row r="409" ht="15">
+      <c r="A409" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B409" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C409" s="2">
+        <v>46127</v>
+      </c>
+      <c r="D409" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E409" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="F409" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G409" s="5">
+        <v>4395.598192</v>
+      </c>
+    </row>
+    <row r="410" ht="15">
+      <c r="A410" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B410" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C410" s="2">
+        <v>46127</v>
+      </c>
+      <c r="D410" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E410" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="F410" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G410" s="5">
+        <v>4261.451456</v>
+      </c>
+    </row>
+    <row r="411" ht="15">
+      <c r="A411" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B411" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C411" s="2">
+        <v>46127</v>
+      </c>
+      <c r="D411" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="E411" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F411" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="G411" s="5">
+        <v>3736.421404</v>
+      </c>
+    </row>
+    <row r="412" ht="15">
+      <c r="A412" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B412" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C412" s="2">
+        <v>46127</v>
+      </c>
+      <c r="D412" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E412" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="F412" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G412" s="5">
+        <v>2388.177173</v>
+      </c>
+    </row>
+    <row r="413" ht="15">
+      <c r="A413" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B413" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C413" s="2">
+        <v>46127</v>
+      </c>
+      <c r="D413" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="E413" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="F413" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="G413" s="5">
+        <v>769.035352</v>
+      </c>
+    </row>
+    <row r="414" ht="15">
+      <c r="A414" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B414" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C414" s="2">
+        <v>46128</v>
+      </c>
+      <c r="D414" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="E414" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="F414" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G414" s="5">
+        <v>1121.834488</v>
+      </c>
+    </row>
+    <row r="415" ht="15">
+      <c r="A415" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B415" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C415" s="2">
+        <v>46128</v>
+      </c>
+      <c r="D415" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="E415" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F415" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G415" s="5">
+        <v>1344.848906</v>
+      </c>
+    </row>
+    <row r="416" ht="15">
+      <c r="A416" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B416" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C416" s="2">
+        <v>46128</v>
+      </c>
+      <c r="D416" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E416" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F416" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G416" s="5">
+        <v>1600.497669</v>
+      </c>
+    </row>
+    <row r="417" ht="15">
+      <c r="A417" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B417" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C417" s="2">
+        <v>46128</v>
+      </c>
+      <c r="D417" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E417" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F417" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G417" s="5">
+        <v>1638.773693</v>
+      </c>
+    </row>
+    <row r="418" ht="15">
+      <c r="A418" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B418" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C418" s="2">
+        <v>46128</v>
+      </c>
+      <c r="D418" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="E418" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F418" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G418" s="5">
+        <v>1731.344293</v>
+      </c>
+    </row>
+    <row r="419" ht="15">
+      <c r="A419" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B419" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C419" s="2">
+        <v>46128</v>
+      </c>
+      <c r="D419" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E419" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F419" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G419" s="5">
+        <v>2078.739841</v>
+      </c>
+    </row>
+    <row r="420" ht="15">
+      <c r="A420" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B420" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C420" s="2">
+        <v>46128</v>
+      </c>
+      <c r="D420" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E420" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F420" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="G420" s="5">
+        <v>2416.54358</v>
+      </c>
+    </row>
+    <row r="421" ht="15">
+      <c r="A421" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B421" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C421" s="2">
+        <v>46128</v>
+      </c>
+      <c r="D421" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E421" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="F421" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G421" s="5">
+        <v>2769.597399</v>
+      </c>
+    </row>
+    <row r="422" ht="15">
+      <c r="A422" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B422" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C422" s="2">
+        <v>46128</v>
+      </c>
+      <c r="D422" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="E422" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F422" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="G422" s="5">
+        <v>3153.054021</v>
+      </c>
+    </row>
+    <row r="423" ht="15">
+      <c r="A423" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B423" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C423" s="2">
+        <v>46128</v>
+      </c>
+      <c r="D423" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E423" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F423" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G423" s="5">
+        <v>3607.347714</v>
+      </c>
+    </row>
+    <row r="424" ht="15">
+      <c r="A424" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B424" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C424" s="2">
+        <v>46128</v>
+      </c>
+      <c r="D424" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E424" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="F424" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G424" s="5">
+        <v>4188.932358</v>
+      </c>
+    </row>
+    <row r="425" ht="15">
+      <c r="A425" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B425" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C425" s="2">
+        <v>46128</v>
+      </c>
+      <c r="D425" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E425" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="F425" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G425" s="5">
+        <v>4343.157942</v>
+      </c>
+    </row>
+    <row r="426" ht="15">
+      <c r="A426" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B426" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C426" s="2">
+        <v>46128</v>
+      </c>
+      <c r="D426" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="E426" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="F426" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="G426" s="5">
+        <v>4046.525257</v>
+      </c>
+    </row>
+    <row r="427" ht="15">
+      <c r="A427" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B427" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C427" s="2">
+        <v>46128</v>
+      </c>
+      <c r="D427" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E427" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="F427" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G427" s="5">
+        <v>2509.708226</v>
+      </c>
+    </row>
+    <row r="428" ht="15">
+      <c r="A428" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B428" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C428" s="2">
+        <v>46128</v>
+      </c>
+      <c r="D428" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E428" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="F428" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G428" s="5">
+        <v>818.859818</v>
+      </c>
+    </row>
+    <row r="429" ht="15">
+      <c r="A429" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B429" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C429" s="2">
+        <v>46129</v>
+      </c>
+      <c r="D429" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="E429" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="F429" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G429" s="5">
+        <v>1053.716292</v>
+      </c>
+    </row>
+    <row r="430" ht="15">
+      <c r="A430" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B430" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C430" s="2">
+        <v>46129</v>
+      </c>
+      <c r="D430" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="E430" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F430" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G430" s="5">
+        <v>1157.76415</v>
+      </c>
+    </row>
+    <row r="431" ht="15">
+      <c r="A431" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B431" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C431" s="2">
+        <v>46129</v>
+      </c>
+      <c r="D431" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E431" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F431" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G431" s="5">
+        <v>1488.768978</v>
+      </c>
+    </row>
+    <row r="432" ht="15">
+      <c r="A432" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B432" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C432" s="2">
+        <v>46129</v>
+      </c>
+      <c r="D432" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E432" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F432" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G432" s="5">
+        <v>1545.259634</v>
+      </c>
+    </row>
+    <row r="433" ht="15">
+      <c r="A433" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B433" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C433" s="2">
+        <v>46129</v>
+      </c>
+      <c r="D433" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E433" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F433" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G433" s="5">
+        <v>1749.116249</v>
+      </c>
+    </row>
+    <row r="434" ht="15">
+      <c r="A434" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B434" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C434" s="2">
+        <v>46129</v>
+      </c>
+      <c r="D434" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E434" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F434" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G434" s="5">
+        <v>2036.345938</v>
+      </c>
+    </row>
+    <row r="435" ht="15">
+      <c r="A435" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B435" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C435" s="2">
+        <v>46129</v>
+      </c>
+      <c r="D435" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E435" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F435" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="G435" s="5">
+        <v>2542.14951</v>
+      </c>
+    </row>
+    <row r="436" ht="15">
+      <c r="A436" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B436" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C436" s="2">
+        <v>46129</v>
+      </c>
+      <c r="D436" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E436" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="F436" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G436" s="5">
+        <v>3036.832831</v>
+      </c>
+    </row>
+    <row r="437" ht="15">
+      <c r="A437" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B437" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C437" s="2">
+        <v>46129</v>
+      </c>
+      <c r="D437" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="E437" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="F437" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="G437" s="5">
+        <v>3283.207058</v>
+      </c>
+    </row>
+    <row r="438" ht="15">
+      <c r="A438" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B438" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C438" s="2">
+        <v>46129</v>
+      </c>
+      <c r="D438" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="E438" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="F438" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G438" s="5">
+        <v>3810.465843</v>
+      </c>
+    </row>
+    <row r="439" ht="15">
+      <c r="A439" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B439" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C439" s="2">
+        <v>46129</v>
+      </c>
+      <c r="D439" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="E439" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F439" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G439" s="5">
+        <v>4126.785863</v>
+      </c>
+    </row>
+    <row r="440" ht="15">
+      <c r="A440" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B440" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C440" s="2">
+        <v>46129</v>
+      </c>
+      <c r="D440" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="E440" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="F440" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G440" s="5">
+        <v>4285.945604</v>
+      </c>
+    </row>
+    <row r="441" ht="15">
+      <c r="A441" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B441" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C441" s="2">
+        <v>46129</v>
+      </c>
+      <c r="D441" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="E441" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F441" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="G441" s="5">
+        <v>3943.408517</v>
+      </c>
+    </row>
+    <row r="442" ht="15">
+      <c r="A442" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B442" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C442" s="2">
+        <v>46129</v>
+      </c>
+      <c r="D442" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E442" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="F442" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G442" s="5">
+        <v>2290.407317</v>
+      </c>
+    </row>
+    <row r="443" ht="15">
+      <c r="A443" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B443" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C443" s="2">
+        <v>46129</v>
+      </c>
+      <c r="D443" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="E443" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="F443" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G443" s="5">
+        <v>862.536435</v>
+      </c>
+    </row>
+    <row r="444" ht="15">
+      <c r="A444" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B444" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C444" s="2">
+        <v>46132</v>
+      </c>
+      <c r="D444" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="E444" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="F444" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G444" s="5">
+        <v>972.519936</v>
+      </c>
+    </row>
+    <row r="445" ht="15">
+      <c r="A445" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B445" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C445" s="2">
+        <v>46132</v>
+      </c>
+      <c r="D445" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="E445" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="F445" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G445" s="5">
+        <v>1265.276781</v>
+      </c>
+    </row>
+    <row r="446" ht="15">
+      <c r="A446" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B446" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C446" s="2">
+        <v>46132</v>
+      </c>
+      <c r="D446" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="E446" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F446" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G446" s="5">
+        <v>1563.698672</v>
+      </c>
+    </row>
+    <row r="447" ht="15">
+      <c r="A447" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B447" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C447" s="2">
+        <v>46132</v>
+      </c>
+      <c r="D447" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E447" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F447" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G447" s="5">
+        <v>1561.473634</v>
+      </c>
+    </row>
+    <row r="448" ht="15">
+      <c r="A448" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B448" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C448" s="2">
+        <v>46132</v>
+      </c>
+      <c r="D448" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E448" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F448" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G448" s="5">
+        <v>1766.909534</v>
+      </c>
+    </row>
+    <row r="449" ht="15">
+      <c r="A449" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B449" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C449" s="2">
+        <v>46132</v>
+      </c>
+      <c r="D449" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E449" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F449" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G449" s="5">
+        <v>2301.060325</v>
+      </c>
+    </row>
+    <row r="450" ht="15">
+      <c r="A450" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B450" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C450" s="2">
+        <v>46132</v>
+      </c>
+      <c r="D450" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E450" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F450" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="G450" s="5">
+        <v>2739.542332</v>
+      </c>
+    </row>
+    <row r="451" ht="15">
+      <c r="A451" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B451" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C451" s="2">
+        <v>46132</v>
+      </c>
+      <c r="D451" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E451" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="F451" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G451" s="5">
+        <v>3206.194537</v>
+      </c>
+    </row>
+    <row r="452" ht="15">
+      <c r="A452" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B452" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C452" s="2">
+        <v>46132</v>
+      </c>
+      <c r="D452" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="E452" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F452" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="G452" s="5">
+        <v>3414.985688</v>
+      </c>
+    </row>
+    <row r="453" ht="15">
+      <c r="A453" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B453" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C453" s="2">
+        <v>46132</v>
+      </c>
+      <c r="D453" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E453" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="F453" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G453" s="5">
+        <v>3750.750148</v>
+      </c>
+    </row>
+    <row r="454" ht="15">
+      <c r="A454" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B454" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C454" s="2">
+        <v>46132</v>
+      </c>
+      <c r="D454" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="E454" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F454" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G454" s="5">
+        <v>4432.814431</v>
+      </c>
+    </row>
+    <row r="455" ht="15">
+      <c r="A455" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B455" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C455" s="2">
+        <v>46132</v>
+      </c>
+      <c r="D455" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E455" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="F455" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G455" s="5">
+        <v>4287.73305</v>
+      </c>
+    </row>
+    <row r="456" ht="15">
+      <c r="A456" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B456" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C456" s="2">
+        <v>46132</v>
+      </c>
+      <c r="D456" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="E456" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="F456" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="G456" s="5">
+        <v>4532.940344</v>
+      </c>
+    </row>
+    <row r="457" ht="15">
+      <c r="A457" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B457" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C457" s="2">
+        <v>46132</v>
+      </c>
+      <c r="D457" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E457" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="F457" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G457" s="5">
+        <v>2473.58709</v>
+      </c>
+    </row>
+    <row r="458" ht="15">
+      <c r="A458" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B458" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C458" s="2">
+        <v>46132</v>
+      </c>
+      <c r="D458" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="E458" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="F458" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G458" s="5">
+        <v>779.642569</v>
+      </c>
+    </row>
+    <row r="459" ht="15">
+      <c r="A459" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B459" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C459" s="2">
+        <v>46133</v>
+      </c>
+      <c r="D459" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E459" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="F459" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G459" s="5">
+        <v>1120.253315</v>
+      </c>
+    </row>
+    <row r="460" ht="15">
+      <c r="A460" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B460" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C460" s="2">
+        <v>46133</v>
+      </c>
+      <c r="D460" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="E460" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F460" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G460" s="5">
+        <v>1334.823302</v>
+      </c>
+    </row>
+    <row r="461" ht="15">
+      <c r="A461" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B461" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C461" s="2">
+        <v>46133</v>
+      </c>
+      <c r="D461" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E461" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F461" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G461" s="5">
+        <v>1762.071305</v>
+      </c>
+    </row>
+    <row r="462" ht="15">
+      <c r="A462" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B462" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C462" s="2">
+        <v>46133</v>
+      </c>
+      <c r="D462" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E462" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F462" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G462" s="5">
+        <v>1758.690457</v>
+      </c>
+    </row>
+    <row r="463" ht="15">
+      <c r="A463" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B463" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C463" s="2">
+        <v>46133</v>
+      </c>
+      <c r="D463" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E463" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="F463" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G463" s="5">
+        <v>1805.943085</v>
+      </c>
+    </row>
+    <row r="464" ht="15">
+      <c r="A464" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B464" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C464" s="2">
+        <v>46133</v>
+      </c>
+      <c r="D464" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E464" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F464" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G464" s="5">
+        <v>2162.902835</v>
+      </c>
+    </row>
+    <row r="465" ht="15">
+      <c r="A465" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B465" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C465" s="2">
+        <v>46133</v>
+      </c>
+      <c r="D465" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E465" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F465" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="G465" s="5">
+        <v>2655.977144</v>
+      </c>
+    </row>
+    <row r="466" ht="15">
+      <c r="A466" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B466" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C466" s="2">
+        <v>46133</v>
+      </c>
+      <c r="D466" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E466" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="F466" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G466" s="5">
+        <v>3193.391115</v>
+      </c>
+    </row>
+    <row r="467" ht="15">
+      <c r="A467" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B467" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C467" s="2">
+        <v>46133</v>
+      </c>
+      <c r="D467" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="E467" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F467" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="G467" s="5">
+        <v>3697.718529</v>
+      </c>
+    </row>
+    <row r="468" ht="15">
+      <c r="A468" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B468" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C468" s="2">
+        <v>46133</v>
+      </c>
+      <c r="D468" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E468" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F468" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G468" s="5">
+        <v>4085.008705</v>
+      </c>
+    </row>
+    <row r="469" ht="15">
+      <c r="A469" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B469" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C469" s="2">
+        <v>46133</v>
+      </c>
+      <c r="D469" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E469" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F469" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G469" s="5">
+        <v>4653.05845</v>
+      </c>
+    </row>
+    <row r="470" ht="15">
+      <c r="A470" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B470" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C470" s="2">
+        <v>46133</v>
+      </c>
+      <c r="D470" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="E470" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="F470" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G470" s="5">
+        <v>4153.401419</v>
+      </c>
+    </row>
+    <row r="471" ht="15">
+      <c r="A471" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B471" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C471" s="2">
+        <v>46133</v>
+      </c>
+      <c r="D471" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="E471" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="F471" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="G471" s="5">
+        <v>4249.140766</v>
+      </c>
+    </row>
+    <row r="472" ht="15">
+      <c r="A472" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B472" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C472" s="2">
+        <v>46133</v>
+      </c>
+      <c r="D472" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E472" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="F472" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G472" s="5">
+        <v>2521.891607</v>
+      </c>
+    </row>
+    <row r="473" ht="15">
+      <c r="A473" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B473" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C473" s="2">
+        <v>46133</v>
+      </c>
+      <c r="D473" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="E473" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="F473" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G473" s="5">
+        <v>886.835407</v>
+      </c>
+    </row>
+    <row r="474" ht="15">
+      <c r="A474" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B474" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C474" s="2">
+        <v>46134</v>
+      </c>
+      <c r="D474" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="E474" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F474" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G474" s="5">
+        <v>870.752637</v>
+      </c>
+    </row>
+    <row r="475" ht="15">
+      <c r="A475" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B475" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C475" s="2">
+        <v>46134</v>
+      </c>
+      <c r="D475" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="E475" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="F475" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G475" s="5">
+        <v>999.803793</v>
+      </c>
+    </row>
+    <row r="476" ht="15">
+      <c r="A476" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B476" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C476" s="2">
+        <v>46134</v>
+      </c>
+      <c r="D476" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="E476" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F476" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G476" s="5">
+        <v>1383.930079</v>
+      </c>
+    </row>
+    <row r="477" ht="15">
+      <c r="A477" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B477" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C477" s="2">
+        <v>46134</v>
+      </c>
+      <c r="D477" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E477" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F477" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G477" s="5">
+        <v>1412.13256</v>
+      </c>
+    </row>
+    <row r="478" ht="15">
+      <c r="A478" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B478" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C478" s="2">
+        <v>46134</v>
+      </c>
+      <c r="D478" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E478" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="F478" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G478" s="5">
+        <v>1525.872661</v>
+      </c>
+    </row>
+    <row r="479" ht="15">
+      <c r="A479" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B479" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C479" s="2">
+        <v>46134</v>
+      </c>
+      <c r="D479" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E479" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F479" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G479" s="5">
+        <v>2098.437437</v>
+      </c>
+    </row>
+    <row r="480" ht="15">
+      <c r="A480" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B480" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C480" s="2">
+        <v>46134</v>
+      </c>
+      <c r="D480" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E480" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="F480" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="G480" s="5">
+        <v>2647.042206</v>
+      </c>
+    </row>
+    <row r="481" ht="15">
+      <c r="A481" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B481" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C481" s="2">
+        <v>46134</v>
+      </c>
+      <c r="D481" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E481" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="F481" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G481" s="5">
+        <v>3044.390959</v>
+      </c>
+    </row>
+    <row r="482" ht="15">
+      <c r="A482" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B482" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C482" s="2">
+        <v>46134</v>
+      </c>
+      <c r="D482" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E482" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F482" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="G482" s="5">
+        <v>3222.5011</v>
+      </c>
+    </row>
+    <row r="483" ht="15">
+      <c r="A483" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B483" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C483" s="2">
+        <v>46134</v>
+      </c>
+      <c r="D483" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E483" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F483" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G483" s="5">
+        <v>3518.146211</v>
+      </c>
+    </row>
+    <row r="484" ht="15">
+      <c r="A484" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B484" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C484" s="2">
+        <v>46134</v>
+      </c>
+      <c r="D484" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E484" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F484" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G484" s="5">
+        <v>4540.955838</v>
+      </c>
+    </row>
+    <row r="485" ht="15">
+      <c r="A485" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B485" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C485" s="2">
+        <v>46134</v>
+      </c>
+      <c r="D485" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="E485" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="F485" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G485" s="5">
+        <v>4607.101438</v>
+      </c>
+    </row>
+    <row r="486" ht="15">
+      <c r="A486" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B486" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C486" s="2">
+        <v>46134</v>
+      </c>
+      <c r="D486" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="E486" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F486" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="G486" s="5">
+        <v>4023.743118</v>
+      </c>
+    </row>
+    <row r="487" ht="15">
+      <c r="A487" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B487" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C487" s="2">
+        <v>46134</v>
+      </c>
+      <c r="D487" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E487" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F487" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G487" s="5">
+        <v>2501.371893</v>
+      </c>
+    </row>
+    <row r="488" ht="15">
+      <c r="A488" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B488" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C488" s="2">
+        <v>46134</v>
+      </c>
+      <c r="D488" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="E488" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="F488" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="G488" s="5">
+        <v>884.764498</v>
+      </c>
+    </row>
+    <row r="489" ht="15">
+      <c r="A489" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B489" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C489" s="2">
+        <v>46135</v>
+      </c>
+      <c r="D489" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="E489" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F489" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G489" s="5">
+        <v>1091.467123</v>
+      </c>
+    </row>
+    <row r="490" ht="15">
+      <c r="A490" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B490" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C490" s="2">
+        <v>46135</v>
+      </c>
+      <c r="D490" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E490" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F490" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G490" s="5">
+        <v>1210.406712</v>
+      </c>
+    </row>
+    <row r="491" ht="15">
+      <c r="A491" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B491" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C491" s="2">
+        <v>46135</v>
+      </c>
+      <c r="D491" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E491" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F491" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G491" s="5">
+        <v>1405.267456</v>
+      </c>
+    </row>
+    <row r="492" ht="15">
+      <c r="A492" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B492" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C492" s="2">
+        <v>46135</v>
+      </c>
+      <c r="D492" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E492" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F492" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G492" s="5">
+        <v>1451.374467</v>
+      </c>
+    </row>
+    <row r="493" ht="15">
+      <c r="A493" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B493" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C493" s="2">
+        <v>46135</v>
+      </c>
+      <c r="D493" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E493" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="F493" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G493" s="5">
+        <v>1566.749904</v>
+      </c>
+    </row>
+    <row r="494" ht="15">
+      <c r="A494" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B494" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C494" s="2">
+        <v>46135</v>
+      </c>
+      <c r="D494" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E494" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F494" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G494" s="5">
+        <v>2124.443002</v>
+      </c>
+    </row>
+    <row r="495" ht="15">
+      <c r="A495" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B495" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C495" s="2">
+        <v>46135</v>
+      </c>
+      <c r="D495" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E495" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F495" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="G495" s="5">
+        <v>2445.677506</v>
+      </c>
+    </row>
+    <row r="496" ht="15">
+      <c r="A496" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B496" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C496" s="2">
+        <v>46135</v>
+      </c>
+      <c r="D496" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E496" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="F496" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G496" s="5">
+        <v>2921.657951</v>
+      </c>
+    </row>
+    <row r="497" ht="15">
+      <c r="A497" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B497" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C497" s="2">
+        <v>46135</v>
+      </c>
+      <c r="D497" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="E497" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F497" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="G497" s="5">
+        <v>3642.246231</v>
+      </c>
+    </row>
+    <row r="498" ht="15">
+      <c r="A498" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B498" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C498" s="2">
+        <v>46135</v>
+      </c>
+      <c r="D498" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E498" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F498" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G498" s="5">
+        <v>3888.297768</v>
+      </c>
+    </row>
+    <row r="499" ht="15">
+      <c r="A499" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B499" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C499" s="2">
+        <v>46135</v>
+      </c>
+      <c r="D499" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E499" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="F499" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G499" s="5">
+        <v>4566.948666</v>
+      </c>
+    </row>
+    <row r="500" ht="15">
+      <c r="A500" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B500" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C500" s="2">
+        <v>46135</v>
+      </c>
+      <c r="D500" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E500" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="F500" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G500" s="5">
+        <v>4366.581751</v>
+      </c>
+    </row>
+    <row r="501" ht="15">
+      <c r="A501" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B501" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C501" s="2">
+        <v>46135</v>
+      </c>
+      <c r="D501" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="E501" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F501" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="G501" s="5">
+        <v>4111.706625</v>
+      </c>
+    </row>
+    <row r="502" ht="15">
+      <c r="A502" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B502" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C502" s="2">
+        <v>46135</v>
+      </c>
+      <c r="D502" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E502" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="F502" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G502" s="5">
+        <v>2639.980585</v>
+      </c>
+    </row>
+    <row r="503" ht="15">
+      <c r="A503" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B503" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C503" s="2">
+        <v>46135</v>
+      </c>
+      <c r="D503" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="E503" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="F503" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G503" s="5">
+        <v>1174.807646</v>
+      </c>
+    </row>
+    <row r="504" ht="15">
+      <c r="A504" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B504" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C504" s="2">
+        <v>46136</v>
+      </c>
+      <c r="D504" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="E504" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="F504" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G504" s="5">
+        <v>1116.836436</v>
+      </c>
+    </row>
+    <row r="505" ht="15">
+      <c r="A505" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B505" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C505" s="2">
+        <v>46136</v>
+      </c>
+      <c r="D505" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="E505" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="F505" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G505" s="5">
+        <v>1013.35905</v>
+      </c>
+    </row>
+    <row r="506" ht="15">
+      <c r="A506" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B506" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C506" s="2">
+        <v>46136</v>
+      </c>
+      <c r="D506" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E506" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F506" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G506" s="5">
+        <v>1474.733023</v>
+      </c>
+    </row>
+    <row r="507" ht="15">
+      <c r="A507" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B507" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C507" s="2">
+        <v>46136</v>
+      </c>
+      <c r="D507" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E507" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F507" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G507" s="5">
+        <v>1499.888552</v>
+      </c>
+    </row>
+    <row r="508" ht="15">
+      <c r="A508" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B508" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C508" s="2">
+        <v>46136</v>
+      </c>
+      <c r="D508" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E508" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="F508" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G508" s="5">
+        <v>1595.91602</v>
+      </c>
+    </row>
+    <row r="509" ht="15">
+      <c r="A509" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B509" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C509" s="2">
+        <v>46136</v>
+      </c>
+      <c r="D509" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E509" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F509" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G509" s="5">
+        <v>1959.95209</v>
+      </c>
+    </row>
+    <row r="510" ht="15">
+      <c r="A510" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B510" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C510" s="2">
+        <v>46136</v>
+      </c>
+      <c r="D510" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E510" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F510" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="G510" s="5">
+        <v>2537.701832</v>
+      </c>
+    </row>
+    <row r="511" ht="15">
+      <c r="A511" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B511" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C511" s="2">
+        <v>46136</v>
+      </c>
+      <c r="D511" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E511" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="F511" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G511" s="5">
+        <v>3076.723827</v>
+      </c>
+    </row>
+    <row r="512" ht="15">
+      <c r="A512" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B512" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C512" s="2">
+        <v>46136</v>
+      </c>
+      <c r="D512" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="E512" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F512" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="G512" s="5">
+        <v>3215.259112</v>
+      </c>
+    </row>
+    <row r="513" ht="15">
+      <c r="A513" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B513" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C513" s="2">
+        <v>46136</v>
+      </c>
+      <c r="D513" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E513" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F513" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G513" s="5">
+        <v>3555.40786</v>
+      </c>
+    </row>
+    <row r="514" ht="15">
+      <c r="A514" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B514" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C514" s="2">
+        <v>46136</v>
+      </c>
+      <c r="D514" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E514" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F514" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G514" s="5">
+        <v>4207.941339</v>
+      </c>
+    </row>
+    <row r="515" ht="15">
+      <c r="A515" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B515" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C515" s="2">
+        <v>46136</v>
+      </c>
+      <c r="D515" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="E515" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="F515" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G515" s="5">
+        <v>4225.16123</v>
+      </c>
+    </row>
+    <row r="516" ht="15">
+      <c r="A516" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B516" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C516" s="2">
+        <v>46136</v>
+      </c>
+      <c r="D516" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="E516" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F516" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="G516" s="5">
+        <v>3714.124378</v>
+      </c>
+    </row>
+    <row r="517" ht="15">
+      <c r="A517" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B517" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C517" s="2">
+        <v>46136</v>
+      </c>
+      <c r="D517" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E517" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="F517" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G517" s="5">
+        <v>2300.665314</v>
+      </c>
+    </row>
+    <row r="518" ht="15">
+      <c r="A518" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B518" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C518" s="2">
+        <v>46136</v>
+      </c>
+      <c r="D518" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="E518" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="F518" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G518" s="5">
+        <v>906.93388</v>
+      </c>
+    </row>
+    <row r="519" ht="15">
+      <c r="A519" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B519" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C519" s="2">
+        <v>46139</v>
+      </c>
+      <c r="D519" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="E519" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="F519" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G519" s="5">
+        <v>895.652739</v>
+      </c>
+    </row>
+    <row r="520" ht="15">
+      <c r="A520" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B520" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C520" s="2">
+        <v>46139</v>
+      </c>
+      <c r="D520" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="E520" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="F520" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G520" s="5">
+        <v>1097.346062</v>
+      </c>
+    </row>
+    <row r="521" ht="15">
+      <c r="A521" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B521" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C521" s="2">
+        <v>46139</v>
+      </c>
+      <c r="D521" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="E521" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F521" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G521" s="5">
+        <v>1468.891578</v>
+      </c>
+    </row>
+    <row r="522" ht="15">
+      <c r="A522" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B522" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C522" s="2">
+        <v>46139</v>
+      </c>
+      <c r="D522" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E522" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F522" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G522" s="5">
+        <v>1609.588629</v>
+      </c>
+    </row>
+    <row r="523" ht="15">
+      <c r="A523" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B523" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C523" s="2">
+        <v>46139</v>
+      </c>
+      <c r="D523" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E523" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="F523" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G523" s="5">
+        <v>1794.433416</v>
+      </c>
+    </row>
+    <row r="524" ht="15">
+      <c r="A524" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B524" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C524" s="2">
+        <v>46139</v>
+      </c>
+      <c r="D524" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E524" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F524" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G524" s="5">
+        <v>1980.080986</v>
+      </c>
+    </row>
+    <row r="525" ht="15">
+      <c r="A525" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B525" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C525" s="2">
+        <v>46139</v>
+      </c>
+      <c r="D525" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E525" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F525" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="G525" s="5">
+        <v>2215.671955</v>
+      </c>
+    </row>
+    <row r="526" ht="15">
+      <c r="A526" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B526" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C526" s="2">
+        <v>46139</v>
+      </c>
+      <c r="D526" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="E526" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F526" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="G526" s="5">
+        <v>2893.7053</v>
+      </c>
+    </row>
+    <row r="527" ht="15">
+      <c r="A527" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B527" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C527" s="2">
+        <v>46139</v>
+      </c>
+      <c r="D527" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E527" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F527" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G527" s="5">
+        <v>3565.453371</v>
+      </c>
+    </row>
+    <row r="528" ht="15">
+      <c r="A528" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B528" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C528" s="2">
+        <v>46139</v>
+      </c>
+      <c r="D528" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E528" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F528" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G528" s="5">
+        <v>3885.07481</v>
+      </c>
+    </row>
+    <row r="529" ht="15">
+      <c r="A529" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B529" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C529" s="2">
+        <v>46139</v>
+      </c>
+      <c r="D529" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E529" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="F529" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G529" s="5">
+        <v>3780.155199</v>
+      </c>
+    </row>
+    <row r="530" ht="15">
+      <c r="A530" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B530" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C530" s="2">
+        <v>46139</v>
+      </c>
+      <c r="D530" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="E530" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F530" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="G530" s="5">
+        <v>3584.043056</v>
+      </c>
+    </row>
+    <row r="531" ht="15">
+      <c r="A531" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B531" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C531" s="2">
+        <v>46139</v>
+      </c>
+      <c r="D531" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E531" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="F531" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G531" s="5">
+        <v>2287.468436</v>
+      </c>
+    </row>
+    <row r="532" ht="15">
+      <c r="A532" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B532" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C532" s="2">
+        <v>46139</v>
+      </c>
+      <c r="D532" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="E532" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="F532" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G532" s="5">
+        <v>840.397614</v>
+      </c>
+    </row>
+    <row r="533" ht="15">
+      <c r="A533" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B533" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C533" s="2">
+        <v>46140</v>
+      </c>
+      <c r="D533" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E533" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="F533" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G533" s="5">
+        <v>952.984297</v>
+      </c>
+    </row>
+    <row r="534" ht="15">
+      <c r="A534" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B534" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C534" s="2">
+        <v>46140</v>
+      </c>
+      <c r="D534" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="E534" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F534" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G534" s="5">
+        <v>1086.521685</v>
+      </c>
+    </row>
+    <row r="535" ht="15">
+      <c r="A535" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B535" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C535" s="2">
+        <v>46140</v>
+      </c>
+      <c r="D535" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E535" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F535" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G535" s="5">
+        <v>1416.291135</v>
+      </c>
+    </row>
+    <row r="536" ht="15">
+      <c r="A536" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B536" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C536" s="2">
+        <v>46140</v>
+      </c>
+      <c r="D536" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E536" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F536" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G536" s="5">
+        <v>1643.989937</v>
+      </c>
+    </row>
+    <row r="537" ht="15">
+      <c r="A537" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B537" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C537" s="2">
+        <v>46140</v>
+      </c>
+      <c r="D537" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E537" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="F537" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G537" s="5">
+        <v>1623.748738</v>
+      </c>
+    </row>
+    <row r="538" ht="15">
+      <c r="A538" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B538" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C538" s="2">
+        <v>46140</v>
+      </c>
+      <c r="D538" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E538" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F538" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G538" s="5">
+        <v>2329.139386</v>
+      </c>
+    </row>
+    <row r="539" ht="15">
+      <c r="A539" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B539" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C539" s="2">
+        <v>46140</v>
+      </c>
+      <c r="D539" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E539" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F539" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="G539" s="5">
+        <v>2668.204947</v>
+      </c>
+    </row>
+    <row r="540" ht="15">
+      <c r="A540" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B540" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C540" s="2">
+        <v>46140</v>
+      </c>
+      <c r="D540" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E540" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F540" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="G540" s="5">
+        <v>3180.595386</v>
+      </c>
+    </row>
+    <row r="541" ht="15">
+      <c r="A541" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B541" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C541" s="2">
+        <v>46140</v>
+      </c>
+      <c r="D541" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E541" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F541" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G541" s="5">
+        <v>3714.159851</v>
+      </c>
+    </row>
+    <row r="542" ht="15">
+      <c r="A542" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B542" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C542" s="2">
+        <v>46140</v>
+      </c>
+      <c r="D542" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E542" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="F542" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G542" s="5">
+        <v>4248.682222</v>
+      </c>
+    </row>
+    <row r="543" ht="15">
+      <c r="A543" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B543" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C543" s="2">
+        <v>46140</v>
+      </c>
+      <c r="D543" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E543" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="F543" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G543" s="5">
+        <v>4408.283647</v>
+      </c>
+    </row>
+    <row r="544" ht="15">
+      <c r="A544" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B544" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C544" s="2">
+        <v>46140</v>
+      </c>
+      <c r="D544" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="E544" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F544" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="G544" s="5">
+        <v>4163.167099</v>
+      </c>
+    </row>
+    <row r="545" ht="15">
+      <c r="A545" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B545" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C545" s="2">
+        <v>46140</v>
+      </c>
+      <c r="D545" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E545" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="F545" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G545" s="5">
+        <v>2694.397996</v>
+      </c>
+    </row>
+    <row r="546" ht="15">
+      <c r="A546" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B546" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C546" s="2">
+        <v>46140</v>
+      </c>
+      <c r="D546" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="E546" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="F546" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G546" s="5">
+        <v>846.910185</v>
+      </c>
+    </row>
+    <row r="547" ht="15">
+      <c r="A547" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B547" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C547" s="2">
+        <v>46141</v>
+      </c>
+      <c r="D547" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="E547" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="F547" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G547" s="5">
+        <v>1024.820377</v>
+      </c>
+    </row>
+    <row r="548" ht="15">
+      <c r="A548" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B548" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C548" s="2">
+        <v>46141</v>
+      </c>
+      <c r="D548" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="E548" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F548" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G548" s="5">
+        <v>1112.425477</v>
+      </c>
+    </row>
+    <row r="549" ht="15">
+      <c r="A549" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B549" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C549" s="2">
+        <v>46141</v>
+      </c>
+      <c r="D549" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="E549" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F549" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G549" s="5">
+        <v>1370.42998</v>
+      </c>
+    </row>
+    <row r="550" ht="15">
+      <c r="A550" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B550" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C550" s="2">
+        <v>46141</v>
+      </c>
+      <c r="D550" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E550" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F550" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G550" s="5">
+        <v>1283.116405</v>
+      </c>
+    </row>
+    <row r="551" ht="15">
+      <c r="A551" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B551" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C551" s="2">
+        <v>46141</v>
+      </c>
+      <c r="D551" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E551" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F551" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G551" s="5">
+        <v>1410.64548</v>
+      </c>
+    </row>
+    <row r="552" ht="15">
+      <c r="A552" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B552" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C552" s="2">
+        <v>46141</v>
+      </c>
+      <c r="D552" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E552" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F552" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G552" s="5">
+        <v>1930.443125</v>
+      </c>
+    </row>
+    <row r="553" ht="15">
+      <c r="A553" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B553" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C553" s="2">
+        <v>46141</v>
+      </c>
+      <c r="D553" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E553" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F553" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="G553" s="5">
+        <v>2278.379537</v>
+      </c>
+    </row>
+    <row r="554" ht="15">
+      <c r="A554" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B554" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C554" s="2">
+        <v>46141</v>
+      </c>
+      <c r="D554" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E554" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="F554" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="G554" s="5">
+        <v>2861.386742</v>
+      </c>
+    </row>
+    <row r="555" ht="15">
+      <c r="A555" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B555" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C555" s="2">
+        <v>46141</v>
+      </c>
+      <c r="D555" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="E555" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F555" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G555" s="5">
+        <v>3479.491246</v>
+      </c>
+    </row>
+    <row r="556" ht="15">
+      <c r="A556" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B556" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C556" s="2">
+        <v>46141</v>
+      </c>
+      <c r="D556" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E556" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F556" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G556" s="5">
+        <v>4438.057676</v>
+      </c>
+    </row>
+    <row r="557" ht="15">
+      <c r="A557" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B557" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C557" s="2">
+        <v>46141</v>
+      </c>
+      <c r="D557" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="E557" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="F557" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G557" s="5">
+        <v>4056.608074</v>
+      </c>
+    </row>
+    <row r="558" ht="15">
+      <c r="A558" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B558" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C558" s="2">
+        <v>46141</v>
+      </c>
+      <c r="D558" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="E558" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F558" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="G558" s="5">
+        <v>3742.660769</v>
+      </c>
+    </row>
+    <row r="559" ht="15">
+      <c r="A559" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B559" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C559" s="2">
+        <v>46141</v>
+      </c>
+      <c r="D559" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E559" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F559" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G559" s="5">
+        <v>2138.63983</v>
+      </c>
+    </row>
+    <row r="560" ht="15">
+      <c r="A560" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B560" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C560" s="2">
+        <v>46141</v>
+      </c>
+      <c r="D560" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="E560" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="F560" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="G560" s="5">
+        <v>677.519286</v>
+      </c>
+    </row>
+    <row r="561" ht="15">
+      <c r="A561" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B561" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C561" s="2">
+        <v>46142</v>
+      </c>
+      <c r="D561" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="E561" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="F561" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G561" s="5">
+        <v>945.287786</v>
+      </c>
+    </row>
+    <row r="562" ht="15">
+      <c r="A562" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B562" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C562" s="2">
+        <v>46142</v>
+      </c>
+      <c r="D562" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="E562" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F562" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G562" s="5">
+        <v>1189.835248</v>
+      </c>
+    </row>
+    <row r="563" ht="15">
+      <c r="A563" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B563" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C563" s="2">
+        <v>46142</v>
+      </c>
+      <c r="D563" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E563" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F563" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G563" s="5">
+        <v>1585.211411</v>
+      </c>
+    </row>
+    <row r="564" ht="15">
+      <c r="A564" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B564" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C564" s="2">
+        <v>46142</v>
+      </c>
+      <c r="D564" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E564" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F564" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G564" s="5">
+        <v>1546.898765</v>
+      </c>
+    </row>
+    <row r="565" ht="15">
+      <c r="A565" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B565" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C565" s="2">
+        <v>46142</v>
+      </c>
+      <c r="D565" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E565" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F565" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G565" s="5">
+        <v>1478.568478</v>
+      </c>
+    </row>
+    <row r="566" ht="15">
+      <c r="A566" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B566" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C566" s="2">
+        <v>46142</v>
+      </c>
+      <c r="D566" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E566" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="F566" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G566" s="5">
+        <v>1913.011344</v>
+      </c>
+    </row>
+    <row r="567" ht="15">
+      <c r="A567" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B567" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C567" s="2">
+        <v>46142</v>
+      </c>
+      <c r="D567" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E567" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F567" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="G567" s="5">
+        <v>2321.734638</v>
+      </c>
+    </row>
+    <row r="568" ht="15">
+      <c r="A568" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B568" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C568" s="2">
+        <v>46142</v>
+      </c>
+      <c r="D568" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="E568" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="F568" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="G568" s="5">
+        <v>3200.792246</v>
+      </c>
+    </row>
+    <row r="569" ht="15">
+      <c r="A569" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B569" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C569" s="2">
+        <v>46142</v>
+      </c>
+      <c r="D569" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E569" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F569" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G569" s="5">
+        <v>3427.151019</v>
+      </c>
+    </row>
+    <row r="570" ht="15">
+      <c r="A570" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B570" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C570" s="2">
+        <v>46142</v>
+      </c>
+      <c r="D570" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E570" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="F570" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G570" s="5">
+        <v>3934.782316</v>
+      </c>
+    </row>
+    <row r="571" ht="15">
+      <c r="A571" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B571" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C571" s="2">
+        <v>46142</v>
+      </c>
+      <c r="D571" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="E571" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="F571" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G571" s="5">
+        <v>3739.801547</v>
+      </c>
+    </row>
+    <row r="572" ht="15">
+      <c r="A572" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B572" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C572" s="2">
+        <v>46142</v>
+      </c>
+      <c r="D572" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="E572" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F572" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="G572" s="5">
+        <v>3531.506392</v>
+      </c>
+    </row>
+    <row r="573" ht="15">
+      <c r="A573" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B573" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C573" s="2">
+        <v>46142</v>
+      </c>
+      <c r="D573" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E573" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="F573" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G573" s="5">
+        <v>2571.9573</v>
+      </c>
+    </row>
+    <row r="574" ht="15">
+      <c r="A574" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B574" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C574" s="2">
+        <v>46142</v>
+      </c>
+      <c r="D574" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="E574" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="F574" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G574" s="5">
+        <v>1019.691048</v>
+      </c>
+    </row>
+    <row r="575" ht="15">
+      <c r="A575" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B575" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C575" s="2">
+        <v>46143</v>
+      </c>
+      <c r="D575" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="E575" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F575" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G575" s="5">
+        <v>618.219383</v>
+      </c>
+    </row>
+    <row r="576" ht="15">
+      <c r="A576" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B576" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C576" s="2">
+        <v>46143</v>
+      </c>
+      <c r="D576" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="E576" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F576" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G576" s="5">
+        <v>930.294761</v>
+      </c>
+    </row>
+    <row r="577" ht="15">
+      <c r="A577" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B577" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C577" s="2">
+        <v>46143</v>
+      </c>
+      <c r="D577" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E577" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F577" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G577" s="5">
+        <v>1416.898443</v>
+      </c>
+    </row>
+    <row r="578" ht="15">
+      <c r="A578" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B578" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C578" s="2">
+        <v>46143</v>
+      </c>
+      <c r="D578" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E578" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F578" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G578" s="5">
+        <v>1750.713956</v>
+      </c>
+    </row>
+    <row r="579" ht="15">
+      <c r="A579" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B579" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C579" s="2">
+        <v>46143</v>
+      </c>
+      <c r="D579" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="E579" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F579" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G579" s="5">
+        <v>1839.532216</v>
+      </c>
+    </row>
+    <row r="580" ht="15">
+      <c r="A580" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B580" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C580" s="2">
+        <v>46143</v>
+      </c>
+      <c r="D580" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E580" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F580" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G580" s="5">
+        <v>2257.552983</v>
+      </c>
+    </row>
+    <row r="581" ht="15">
+      <c r="A581" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B581" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C581" s="2">
+        <v>46143</v>
+      </c>
+      <c r="D581" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E581" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F581" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="G581" s="5">
+        <v>2457.192388</v>
+      </c>
+    </row>
+    <row r="582" ht="15">
+      <c r="A582" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B582" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C582" s="2">
+        <v>46143</v>
+      </c>
+      <c r="D582" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E582" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="F582" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="G582" s="5">
+        <v>3045.274466</v>
+      </c>
+    </row>
+    <row r="583" ht="15">
+      <c r="A583" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B583" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C583" s="2">
+        <v>46143</v>
+      </c>
+      <c r="D583" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E583" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F583" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G583" s="5">
+        <v>3395.31346</v>
+      </c>
+    </row>
+    <row r="584" ht="15">
+      <c r="A584" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B584" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C584" s="2">
+        <v>46143</v>
+      </c>
+      <c r="D584" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E584" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="F584" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G584" s="5">
+        <v>3917.226804</v>
+      </c>
+    </row>
+    <row r="585" ht="15">
+      <c r="A585" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B585" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C585" s="2">
+        <v>46143</v>
+      </c>
+      <c r="D585" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E585" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="F585" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G585" s="5">
+        <v>4001.26388</v>
+      </c>
+    </row>
+    <row r="586" ht="15">
+      <c r="A586" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B586" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C586" s="2">
+        <v>46143</v>
+      </c>
+      <c r="D586" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="E586" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F586" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="G586" s="5">
+        <v>4120.736709</v>
+      </c>
+    </row>
+    <row r="587" ht="15">
+      <c r="A587" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B587" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C587" s="2">
+        <v>46143</v>
+      </c>
+      <c r="D587" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E587" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="F587" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G587" s="5">
+        <v>2462.757862</v>
+      </c>
+    </row>
+    <row r="588" ht="15">
+      <c r="A588" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B588" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C588" s="2">
+        <v>46143</v>
+      </c>
+      <c r="D588" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="E588" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="F588" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G588" s="5">
+        <v>1214.021156</v>
       </c>
     </row>
   </sheetData>

--- a/Programmes Seguimiento LE_2.xlsx
+++ b/Programmes Seguimiento LE_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Seguimiento-LE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F722260F-E693-4B27-965A-73DD2D4EE26B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC12DA7A-673A-4F72-BD70-B0178B69318D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1836" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1878" uniqueCount="69">
   <si>
     <t>Targets</t>
   </si>
@@ -170,7 +170,7 @@
     <t>Tv Programs</t>
   </si>
   <si>
-    <t>10/04/2026;   13/04/2026 - 17/04/2026;   20/04/2026 - 24/04/2026;   27/04/2026 - 01/05/2026;   04/05/2026 - 08/05/2026;   11/05/2026 - 15/05/2026;   18/05/2026 - 22/05/2026;   25/05/2026 - 29/05/2026;   01/06/2026 - 03/06/2026</t>
+    <t>10/04/2026;   13/04/2026 - 17/04/2026;   20/04/2026 - 24/04/2026;   27/04/2026 - 01/05/2026;   04/05/2026 - 08/05/2026;   11/05/2026 - 15/05/2026;   18/05/2026 - 22/05/2026;   25/05/2026 - 29/05/2026;   01/06/2026 - 04/06/2026</t>
   </si>
   <si>
     <t>National</t>
@@ -221,13 +221,13 @@
     <t xml:space="preserve">	For Target [P.2+] ...</t>
   </si>
   <si>
-    <t xml:space="preserve">	 For Region [National] Universe 78427.2; Sample 6882 ( 100.00% )</t>
+    <t xml:space="preserve">	 For Region [National] Universe 78427.2; Sample 6883 ( 100.00% )</t>
   </si>
   <si>
     <t xml:space="preserve">	For Target [Universe] ...</t>
   </si>
   <si>
-    <t xml:space="preserve">	 For Region [National] Universe 78427.2; Sample 6828 ( 100.00% )</t>
+    <t xml:space="preserve">	 For Region [National] Universe 78427.2; Sample 6829 ( 100.00% )</t>
   </si>
 </sst>
 </file>
@@ -769,7 +769,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H597"/>
+  <dimension ref="A1:H611"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -16301,6 +16301,370 @@
       </c>
       <c r="H597" s="5">
         <v>739.74610499999994</v>
+      </c>
+    </row>
+    <row r="598" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A598" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B598" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C598" s="3">
+        <v>46177</v>
+      </c>
+      <c r="D598" s="4">
+        <v>0.24456018518518499</v>
+      </c>
+      <c r="E598" s="4">
+        <v>0.29012731481481502</v>
+      </c>
+      <c r="F598" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G598" s="2">
+        <v>1</v>
+      </c>
+      <c r="H598" s="5">
+        <v>459.20778200000001</v>
+      </c>
+    </row>
+    <row r="599" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A599" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B599" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C599" s="3">
+        <v>46177</v>
+      </c>
+      <c r="D599" s="4">
+        <v>0.29012731481481502</v>
+      </c>
+      <c r="E599" s="4">
+        <v>0.37502314814814802</v>
+      </c>
+      <c r="F599" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G599" s="2">
+        <v>1</v>
+      </c>
+      <c r="H599" s="5">
+        <v>867.59927700000003</v>
+      </c>
+    </row>
+    <row r="600" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A600" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B600" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C600" s="3">
+        <v>46177</v>
+      </c>
+      <c r="D600" s="4">
+        <v>0.37502314814814802</v>
+      </c>
+      <c r="E600" s="4">
+        <v>0.50002314814814797</v>
+      </c>
+      <c r="F600" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G600" s="2">
+        <v>1</v>
+      </c>
+      <c r="H600" s="5">
+        <v>1441.304954</v>
+      </c>
+    </row>
+    <row r="601" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A601" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B601" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C601" s="3">
+        <v>46177</v>
+      </c>
+      <c r="D601" s="4">
+        <v>0.50002314814814797</v>
+      </c>
+      <c r="E601" s="4">
+        <v>0.56252314814814797</v>
+      </c>
+      <c r="F601" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G601" s="2">
+        <v>1</v>
+      </c>
+      <c r="H601" s="5">
+        <v>1599.847925</v>
+      </c>
+    </row>
+    <row r="602" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A602" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B602" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C602" s="3">
+        <v>46177</v>
+      </c>
+      <c r="D602" s="4">
+        <v>0.56252314814814797</v>
+      </c>
+      <c r="E602" s="4">
+        <v>0.60418981481481504</v>
+      </c>
+      <c r="F602" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G602" s="2">
+        <v>1</v>
+      </c>
+      <c r="H602" s="5">
+        <v>1487.415493</v>
+      </c>
+    </row>
+    <row r="603" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A603" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B603" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C603" s="3">
+        <v>46177</v>
+      </c>
+      <c r="D603" s="4">
+        <v>0.60418981481481504</v>
+      </c>
+      <c r="E603" s="4">
+        <v>0.64583333333333304</v>
+      </c>
+      <c r="F603" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G603" s="2">
+        <v>1</v>
+      </c>
+      <c r="H603" s="5">
+        <v>1984.2137090000001</v>
+      </c>
+    </row>
+    <row r="604" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A604" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B604" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C604" s="3">
+        <v>46177</v>
+      </c>
+      <c r="D604" s="4">
+        <v>0.64583333333333304</v>
+      </c>
+      <c r="E604" s="4">
+        <v>0.68753472222222201</v>
+      </c>
+      <c r="F604" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G604" s="2">
+        <v>1</v>
+      </c>
+      <c r="H604" s="5">
+        <v>2337.093969</v>
+      </c>
+    </row>
+    <row r="605" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A605" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B605" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C605" s="3">
+        <v>46177</v>
+      </c>
+      <c r="D605" s="4">
+        <v>0.68753472222222201</v>
+      </c>
+      <c r="E605" s="4">
+        <v>0.770821759259259</v>
+      </c>
+      <c r="F605" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G605" s="2">
+        <v>1</v>
+      </c>
+      <c r="H605" s="5">
+        <v>2935.1661989999998</v>
+      </c>
+    </row>
+    <row r="606" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A606" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B606" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C606" s="3">
+        <v>46177</v>
+      </c>
+      <c r="D606" s="4">
+        <v>0.770821759259259</v>
+      </c>
+      <c r="E606" s="4">
+        <v>0.81251157407407404</v>
+      </c>
+      <c r="F606" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G606" s="2">
+        <v>1</v>
+      </c>
+      <c r="H606" s="5">
+        <v>3398.039988</v>
+      </c>
+    </row>
+    <row r="607" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A607" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B607" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C607" s="3">
+        <v>46177</v>
+      </c>
+      <c r="D607" s="4">
+        <v>0.81251157407407404</v>
+      </c>
+      <c r="E607" s="4">
+        <v>0.85421296296296301</v>
+      </c>
+      <c r="F607" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G607" s="2">
+        <v>1</v>
+      </c>
+      <c r="H607" s="5">
+        <v>3941.4985710000001</v>
+      </c>
+    </row>
+    <row r="608" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A608" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B608" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C608" s="3">
+        <v>46177</v>
+      </c>
+      <c r="D608" s="4">
+        <v>0.85421296296296301</v>
+      </c>
+      <c r="E608" s="4">
+        <v>0.89586805555555604</v>
+      </c>
+      <c r="F608" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G608" s="2">
+        <v>1</v>
+      </c>
+      <c r="H608" s="5">
+        <v>3854.8877149999998</v>
+      </c>
+    </row>
+    <row r="609" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A609" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B609" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C609" s="3">
+        <v>46177</v>
+      </c>
+      <c r="D609" s="4">
+        <v>0.89586805555555604</v>
+      </c>
+      <c r="E609" s="4">
+        <v>0.93754629629629604</v>
+      </c>
+      <c r="F609" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G609" s="2">
+        <v>1</v>
+      </c>
+      <c r="H609" s="5">
+        <v>3780.1327999999999</v>
+      </c>
+    </row>
+    <row r="610" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A610" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B610" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C610" s="3">
+        <v>46177</v>
+      </c>
+      <c r="D610" s="4">
+        <v>0.93754629629629604</v>
+      </c>
+      <c r="E610" s="4">
+        <v>0.963321759259259</v>
+      </c>
+      <c r="F610" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G610" s="2">
+        <v>1</v>
+      </c>
+      <c r="H610" s="5">
+        <v>2656.725719</v>
+      </c>
+    </row>
+    <row r="611" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A611" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B611" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C611" s="3">
+        <v>46177</v>
+      </c>
+      <c r="D611" s="4">
+        <v>0.963321759259259</v>
+      </c>
+      <c r="E611" s="4">
+        <v>1.0053125000000001</v>
+      </c>
+      <c r="F611" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G611" s="2">
+        <v>1</v>
+      </c>
+      <c r="H611" s="5">
+        <v>961.78833899999995</v>
       </c>
     </row>
   </sheetData>

--- a/Programmes Seguimiento LE_2.xlsx
+++ b/Programmes Seguimiento LE_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Seguimiento-LE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E105C355-DDF8-4BA9-A588-1B6CB6E6E6EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49814366-2DD2-42B3-8038-326E44BD50D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,12 +16,15 @@
     <sheet name="CON-Las Estrellas" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="1" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CON-Las Estrellas'!$A$1:$H$608</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1869" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1869" uniqueCount="69">
   <si>
     <t>Targets</t>
   </si>
@@ -105,9 +108,6 @@
   </si>
   <si>
     <t>TAN CERCA DE TI NACE EL AMOR</t>
-  </si>
-  <si>
-    <t>HOY CELEBREMOS</t>
   </si>
   <si>
     <t>Rows</t>
@@ -772,6 +772,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:H608"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -804,13 +805,13 @@
         <v>7</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -836,7 +837,7 @@
         <v>513.11862699999995</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -862,7 +863,7 @@
         <v>967.55453499999999</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -914,7 +915,7 @@
         <v>1453.368931</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
@@ -940,7 +941,7 @@
         <v>1479.1792370000001</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>1</v>
       </c>
@@ -966,7 +967,7 @@
         <v>1725.84791</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>1</v>
       </c>
@@ -992,7 +993,7 @@
         <v>2366.9133889999998</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>1</v>
       </c>
@@ -1018,7 +1019,7 @@
         <v>2786.6775929999999</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>1</v>
       </c>
@@ -1044,7 +1045,7 @@
         <v>3105.9341279999999</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>1</v>
       </c>
@@ -1070,7 +1071,7 @@
         <v>3408.1486490000002</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>1</v>
       </c>
@@ -1096,7 +1097,7 @@
         <v>3986.0786969999999</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>1</v>
       </c>
@@ -1122,7 +1123,7 @@
         <v>4395.5981920000004</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>1</v>
       </c>
@@ -1148,7 +1149,7 @@
         <v>4261.451454</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>1</v>
       </c>
@@ -1174,7 +1175,7 @@
         <v>3736.4214029999998</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>1</v>
       </c>
@@ -1200,7 +1201,7 @@
         <v>2388.1771739999999</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>1</v>
       </c>
@@ -1226,7 +1227,7 @@
         <v>769.03535299999999</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>1</v>
       </c>
@@ -1252,7 +1253,7 @@
         <v>446.74877199999997</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>1</v>
       </c>
@@ -1278,7 +1279,7 @@
         <v>1121.834488</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>1</v>
       </c>
@@ -1330,7 +1331,7 @@
         <v>1600.497664</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>1</v>
       </c>
@@ -1356,7 +1357,7 @@
         <v>1638.773688</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>1</v>
       </c>
@@ -1382,7 +1383,7 @@
         <v>1731.3442889999999</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>1</v>
       </c>
@@ -1408,7 +1409,7 @@
         <v>2078.7398389999998</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>1</v>
       </c>
@@ -1434,7 +1435,7 @@
         <v>2416.54358</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>1</v>
       </c>
@@ -1460,7 +1461,7 @@
         <v>2769.597401</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>1</v>
       </c>
@@ -1486,7 +1487,7 @@
         <v>3153.0540209999999</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>1</v>
       </c>
@@ -1512,7 +1513,7 @@
         <v>3607.3477090000001</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>1</v>
       </c>
@@ -1538,7 +1539,7 @@
         <v>4188.9323549999999</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>1</v>
       </c>
@@ -1564,7 +1565,7 @@
         <v>4343.1579369999999</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>1</v>
       </c>
@@ -1590,7 +1591,7 @@
         <v>4046.5252529999998</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>1</v>
       </c>
@@ -1616,7 +1617,7 @@
         <v>2509.7082220000002</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>1</v>
       </c>
@@ -1642,7 +1643,7 @@
         <v>818.85981500000003</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>1</v>
       </c>
@@ -1668,7 +1669,7 @@
         <v>574.13904400000001</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>1</v>
       </c>
@@ -1694,7 +1695,7 @@
         <v>1053.7162900000001</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>1</v>
       </c>
@@ -1746,7 +1747,7 @@
         <v>1488.768984</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>1</v>
       </c>
@@ -1772,7 +1773,7 @@
         <v>1545.25964</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>1</v>
       </c>
@@ -1798,7 +1799,7 @@
         <v>1749.11625</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>1</v>
       </c>
@@ -1824,7 +1825,7 @@
         <v>2036.345945</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>1</v>
       </c>
@@ -1850,7 +1851,7 @@
         <v>2542.1495129999998</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>1</v>
       </c>
@@ -1876,7 +1877,7 @@
         <v>3036.8328320000001</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>1</v>
       </c>
@@ -1902,7 +1903,7 @@
         <v>3283.207058</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>1</v>
       </c>
@@ -1928,7 +1929,7 @@
         <v>3810.4658469999999</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
         <v>1</v>
       </c>
@@ -1954,7 +1955,7 @@
         <v>4126.7858740000001</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>1</v>
       </c>
@@ -1980,7 +1981,7 @@
         <v>4285.9456039999995</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>1</v>
       </c>
@@ -2006,7 +2007,7 @@
         <v>3943.4085110000001</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
         <v>1</v>
       </c>
@@ -2032,7 +2033,7 @@
         <v>2290.4073199999998</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
         <v>1</v>
       </c>
@@ -2058,7 +2059,7 @@
         <v>862.53643499999998</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
         <v>1</v>
       </c>
@@ -2084,7 +2085,7 @@
         <v>350.51629100000002</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
         <v>1</v>
       </c>
@@ -2110,7 +2111,7 @@
         <v>972.51993600000003</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
         <v>1</v>
       </c>
@@ -2162,7 +2163,7 @@
         <v>1563.6986690000001</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
         <v>1</v>
       </c>
@@ -2188,7 +2189,7 @@
         <v>1561.4736290000001</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
         <v>1</v>
       </c>
@@ -2214,7 +2215,7 @@
         <v>1766.909531</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
         <v>1</v>
       </c>
@@ -2240,7 +2241,7 @@
         <v>2301.0603219999998</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
         <v>1</v>
       </c>
@@ -2266,7 +2267,7 @@
         <v>2739.542324</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
         <v>1</v>
       </c>
@@ -2292,7 +2293,7 @@
         <v>3206.1945289999999</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
         <v>1</v>
       </c>
@@ -2318,7 +2319,7 @@
         <v>3414.9856810000001</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
         <v>1</v>
       </c>
@@ -2344,7 +2345,7 @@
         <v>3750.7501430000002</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
         <v>1</v>
       </c>
@@ -2370,7 +2371,7 @@
         <v>4432.8144309999998</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
         <v>1</v>
       </c>
@@ -2396,7 +2397,7 @@
         <v>4287.7330439999996</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
         <v>1</v>
       </c>
@@ -2422,7 +2423,7 @@
         <v>4532.9403400000001</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
         <v>1</v>
       </c>
@@ -2448,7 +2449,7 @@
         <v>2473.5870890000001</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
         <v>1</v>
       </c>
@@ -2474,7 +2475,7 @@
         <v>779.64256899999998</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
         <v>1</v>
       </c>
@@ -2500,7 +2501,7 @@
         <v>445.61400400000002</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
         <v>1</v>
       </c>
@@ -2526,7 +2527,7 @@
         <v>1120.2533149999999</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
         <v>1</v>
       </c>
@@ -2578,7 +2579,7 @@
         <v>1762.071306</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
         <v>1</v>
       </c>
@@ -2604,7 +2605,7 @@
         <v>1758.6904549999999</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
         <v>1</v>
       </c>
@@ -2630,7 +2631,7 @@
         <v>1805.9430809999999</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
         <v>1</v>
       </c>
@@ -2656,7 +2657,7 @@
         <v>2162.9028309999999</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
         <v>1</v>
       </c>
@@ -2682,7 +2683,7 @@
         <v>2655.977144</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>1</v>
       </c>
@@ -2708,7 +2709,7 @@
         <v>3193.3911189999999</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
         <v>1</v>
       </c>
@@ -2734,7 +2735,7 @@
         <v>3697.7185330000002</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
         <v>1</v>
       </c>
@@ -2760,7 +2761,7 @@
         <v>4085.0087109999999</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
         <v>1</v>
       </c>
@@ -2786,7 +2787,7 @@
         <v>4653.0584509999999</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
         <v>1</v>
       </c>
@@ -2812,7 +2813,7 @@
         <v>4153.4014189999998</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
         <v>1</v>
       </c>
@@ -2838,7 +2839,7 @@
         <v>4249.1407639999998</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
         <v>1</v>
       </c>
@@ -2864,7 +2865,7 @@
         <v>2521.8916089999998</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
         <v>1</v>
       </c>
@@ -2890,7 +2891,7 @@
         <v>886.83540300000004</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
         <v>1</v>
       </c>
@@ -2916,7 +2917,7 @@
         <v>447.58211</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
         <v>1</v>
       </c>
@@ -2942,7 +2943,7 @@
         <v>870.75262999999995</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
         <v>1</v>
       </c>
@@ -2994,7 +2995,7 @@
         <v>1383.9300740000001</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
         <v>1</v>
       </c>
@@ -3020,7 +3021,7 @@
         <v>1412.1325609999999</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
         <v>1</v>
       </c>
@@ -3046,7 +3047,7 @@
         <v>1525.872664</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>1</v>
       </c>
@@ -3072,7 +3073,7 @@
         <v>2098.4374320000002</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
         <v>1</v>
       </c>
@@ -3098,7 +3099,7 @@
         <v>2647.0421980000001</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
         <v>1</v>
       </c>
@@ -3124,7 +3125,7 @@
         <v>3044.3909509999999</v>
       </c>
     </row>
-    <row r="91" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
         <v>1</v>
       </c>
@@ -3150,7 +3151,7 @@
         <v>3222.501092</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
         <v>1</v>
       </c>
@@ -3176,7 +3177,7 @@
         <v>3518.1461989999998</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
         <v>1</v>
       </c>
@@ -3202,7 +3203,7 @@
         <v>4540.955825</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
         <v>1</v>
       </c>
@@ -3228,7 +3229,7 @@
         <v>4607.1014100000002</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
         <v>1</v>
       </c>
@@ -3254,7 +3255,7 @@
         <v>4023.7430939999999</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
         <v>1</v>
       </c>
@@ -3280,7 +3281,7 @@
         <v>2501.3718749999998</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
         <v>1</v>
       </c>
@@ -3306,7 +3307,7 @@
         <v>884.76449100000002</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
         <v>1</v>
       </c>
@@ -3332,7 +3333,7 @@
         <v>581.99064599999997</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
         <v>1</v>
       </c>
@@ -3358,7 +3359,7 @@
         <v>1091.467124</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
         <v>1</v>
       </c>
@@ -3410,7 +3411,7 @@
         <v>1405.2674589999999</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
         <v>1</v>
       </c>
@@ -3436,7 +3437,7 @@
         <v>1451.374466</v>
       </c>
     </row>
-    <row r="103" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
         <v>1</v>
       </c>
@@ -3462,7 +3463,7 @@
         <v>1566.7499069999999</v>
       </c>
     </row>
-    <row r="104" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
         <v>1</v>
       </c>
@@ -3488,7 +3489,7 @@
         <v>2124.4430069999999</v>
       </c>
     </row>
-    <row r="105" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
         <v>1</v>
       </c>
@@ -3514,7 +3515,7 @@
         <v>2445.67751</v>
       </c>
     </row>
-    <row r="106" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
         <v>1</v>
       </c>
@@ -3540,7 +3541,7 @@
         <v>2921.65796</v>
       </c>
     </row>
-    <row r="107" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
         <v>1</v>
       </c>
@@ -3566,7 +3567,7 @@
         <v>3642.2462399999999</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
         <v>1</v>
       </c>
@@ -3592,7 +3593,7 @@
         <v>3888.2977780000001</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
         <v>1</v>
       </c>
@@ -3618,7 +3619,7 @@
         <v>4566.9486820000002</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
         <v>1</v>
       </c>
@@ -3644,7 +3645,7 @@
         <v>4366.581768</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
         <v>1</v>
       </c>
@@ -3670,7 +3671,7 @@
         <v>4111.706639</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
         <v>1</v>
       </c>
@@ -3696,7 +3697,7 @@
         <v>2639.9805889999998</v>
       </c>
     </row>
-    <row r="113" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
         <v>1</v>
       </c>
@@ -3722,7 +3723,7 @@
         <v>1174.8076450000001</v>
       </c>
     </row>
-    <row r="114" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
         <v>1</v>
       </c>
@@ -3748,7 +3749,7 @@
         <v>551.23432100000002</v>
       </c>
     </row>
-    <row r="115" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
         <v>1</v>
       </c>
@@ -3774,7 +3775,7 @@
         <v>1116.8364329999999</v>
       </c>
     </row>
-    <row r="116" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
         <v>1</v>
       </c>
@@ -3826,7 +3827,7 @@
         <v>1474.7330219999999</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
         <v>1</v>
       </c>
@@ -3852,7 +3853,7 @@
         <v>1499.8885499999999</v>
       </c>
     </row>
-    <row r="119" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
         <v>1</v>
       </c>
@@ -3878,7 +3879,7 @@
         <v>1595.916017</v>
       </c>
     </row>
-    <row r="120" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>1</v>
       </c>
@@ -3904,7 +3905,7 @@
         <v>1959.9520849999999</v>
       </c>
     </row>
-    <row r="121" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
         <v>1</v>
       </c>
@@ -3930,7 +3931,7 @@
         <v>2537.701826</v>
       </c>
     </row>
-    <row r="122" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
         <v>1</v>
       </c>
@@ -3956,7 +3957,7 @@
         <v>3076.7238170000001</v>
       </c>
     </row>
-    <row r="123" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="2" t="s">
         <v>1</v>
       </c>
@@ -3982,7 +3983,7 @@
         <v>3215.2591069999999</v>
       </c>
     </row>
-    <row r="124" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
         <v>1</v>
       </c>
@@ -4008,7 +4009,7 @@
         <v>3555.4078559999998</v>
       </c>
     </row>
-    <row r="125" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="2" t="s">
         <v>1</v>
       </c>
@@ -4034,7 +4035,7 @@
         <v>4207.9413439999998</v>
       </c>
     </row>
-    <row r="126" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
         <v>1</v>
       </c>
@@ -4060,7 +4061,7 @@
         <v>4225.1612359999999</v>
       </c>
     </row>
-    <row r="127" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="2" t="s">
         <v>1</v>
       </c>
@@ -4086,7 +4087,7 @@
         <v>3714.1243840000002</v>
       </c>
     </row>
-    <row r="128" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="2" t="s">
         <v>1</v>
       </c>
@@ -4112,7 +4113,7 @@
         <v>2300.665317</v>
       </c>
     </row>
-    <row r="129" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="2" t="s">
         <v>1</v>
       </c>
@@ -4138,7 +4139,7 @@
         <v>906.93387800000005</v>
       </c>
     </row>
-    <row r="130" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="2" t="s">
         <v>1</v>
       </c>
@@ -4164,7 +4165,7 @@
         <v>343.72257100000002</v>
       </c>
     </row>
-    <row r="131" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="2" t="s">
         <v>1</v>
       </c>
@@ -4190,7 +4191,7 @@
         <v>895.65274199999999</v>
       </c>
     </row>
-    <row r="132" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
         <v>1</v>
       </c>
@@ -4242,7 +4243,7 @@
         <v>1468.8915830000001</v>
       </c>
     </row>
-    <row r="134" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="2" t="s">
         <v>1</v>
       </c>
@@ -4268,7 +4269,7 @@
         <v>1609.5886390000001</v>
       </c>
     </row>
-    <row r="135" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="2" t="s">
         <v>1</v>
       </c>
@@ -4294,7 +4295,7 @@
         <v>1794.4334249999999</v>
       </c>
     </row>
-    <row r="136" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
         <v>1</v>
       </c>
@@ -4320,7 +4321,7 @@
         <v>1980.080993</v>
       </c>
     </row>
-    <row r="137" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="2" t="s">
         <v>1</v>
       </c>
@@ -4346,7 +4347,7 @@
         <v>2215.6719629999998</v>
       </c>
     </row>
-    <row r="138" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
         <v>1</v>
       </c>
@@ -4372,7 +4373,7 @@
         <v>2893.7053089999999</v>
       </c>
     </row>
-    <row r="139" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="2" t="s">
         <v>1</v>
       </c>
@@ -4398,7 +4399,7 @@
         <v>3565.453379</v>
       </c>
     </row>
-    <row r="140" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="2" t="s">
         <v>1</v>
       </c>
@@ -4424,7 +4425,7 @@
         <v>3885.0748239999998</v>
       </c>
     </row>
-    <row r="141" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="2" t="s">
         <v>1</v>
       </c>
@@ -4450,7 +4451,7 @@
         <v>3780.155205</v>
       </c>
     </row>
-    <row r="142" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="2" t="s">
         <v>1</v>
       </c>
@@ -4476,7 +4477,7 @@
         <v>3584.0430569999999</v>
       </c>
     </row>
-    <row r="143" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="2" t="s">
         <v>1</v>
       </c>
@@ -4502,7 +4503,7 @@
         <v>2287.468437</v>
       </c>
     </row>
-    <row r="144" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
         <v>1</v>
       </c>
@@ -4528,7 +4529,7 @@
         <v>840.39761299999998</v>
       </c>
     </row>
-    <row r="145" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="2" t="s">
         <v>1</v>
       </c>
@@ -4554,7 +4555,7 @@
         <v>514.28511900000001</v>
       </c>
     </row>
-    <row r="146" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
         <v>1</v>
       </c>
@@ -4580,7 +4581,7 @@
         <v>952.98429799999997</v>
       </c>
     </row>
-    <row r="147" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="2" t="s">
         <v>1</v>
       </c>
@@ -4632,7 +4633,7 @@
         <v>1416.2911369999999</v>
       </c>
     </row>
-    <row r="149" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="2" t="s">
         <v>1</v>
       </c>
@@ -4658,7 +4659,7 @@
         <v>1643.9899419999999</v>
       </c>
     </row>
-    <row r="150" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
         <v>1</v>
       </c>
@@ -4684,7 +4685,7 @@
         <v>1623.7487430000001</v>
       </c>
     </row>
-    <row r="151" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="2" t="s">
         <v>1</v>
       </c>
@@ -4710,7 +4711,7 @@
         <v>2329.1393929999999</v>
       </c>
     </row>
-    <row r="152" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="2" t="s">
         <v>1</v>
       </c>
@@ -4736,7 +4737,7 @@
         <v>2668.2049510000002</v>
       </c>
     </row>
-    <row r="153" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="2" t="s">
         <v>1</v>
       </c>
@@ -4762,7 +4763,7 @@
         <v>3180.5953920000002</v>
       </c>
     </row>
-    <row r="154" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="2" t="s">
         <v>1</v>
       </c>
@@ -4788,7 +4789,7 @@
         <v>3714.1598549999999</v>
       </c>
     </row>
-    <row r="155" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="2" t="s">
         <v>1</v>
       </c>
@@ -4814,7 +4815,7 @@
         <v>4248.6822229999998</v>
       </c>
     </row>
-    <row r="156" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="2" t="s">
         <v>1</v>
       </c>
@@ -4840,7 +4841,7 @@
         <v>4408.2836530000004</v>
       </c>
     </row>
-    <row r="157" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="2" t="s">
         <v>1</v>
       </c>
@@ -4866,7 +4867,7 @@
         <v>4163.167109</v>
       </c>
     </row>
-    <row r="158" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
         <v>1</v>
       </c>
@@ -4892,7 +4893,7 @@
         <v>2694.398001</v>
       </c>
     </row>
-    <row r="159" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="2" t="s">
         <v>1</v>
       </c>
@@ -4918,7 +4919,7 @@
         <v>846.91018499999996</v>
       </c>
     </row>
-    <row r="160" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="2" t="s">
         <v>1</v>
       </c>
@@ -4944,7 +4945,7 @@
         <v>479.34187900000001</v>
       </c>
     </row>
-    <row r="161" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="2" t="s">
         <v>1</v>
       </c>
@@ -4970,7 +4971,7 @@
         <v>1024.820375</v>
       </c>
     </row>
-    <row r="162" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="2" t="s">
         <v>1</v>
       </c>
@@ -5022,7 +5023,7 @@
         <v>1370.4299799999999</v>
       </c>
     </row>
-    <row r="164" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="2" t="s">
         <v>1</v>
       </c>
@@ -5048,7 +5049,7 @@
         <v>1283.116405</v>
       </c>
     </row>
-    <row r="165" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="2" t="s">
         <v>1</v>
       </c>
@@ -5074,7 +5075,7 @@
         <v>1410.645475</v>
       </c>
     </row>
-    <row r="166" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="2" t="s">
         <v>1</v>
       </c>
@@ -5100,7 +5101,7 @@
         <v>1930.443117</v>
       </c>
     </row>
-    <row r="167" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="2" t="s">
         <v>1</v>
       </c>
@@ -5126,7 +5127,7 @@
         <v>2278.3795279999999</v>
       </c>
     </row>
-    <row r="168" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="2" t="s">
         <v>1</v>
       </c>
@@ -5152,7 +5153,7 @@
         <v>2861.3867279999999</v>
       </c>
     </row>
-    <row r="169" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="2" t="s">
         <v>1</v>
       </c>
@@ -5178,7 +5179,7 @@
         <v>3479.4912359999998</v>
       </c>
     </row>
-    <row r="170" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="2" t="s">
         <v>1</v>
       </c>
@@ -5204,7 +5205,7 @@
         <v>4438.0576639999999</v>
       </c>
     </row>
-    <row r="171" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="2" t="s">
         <v>1</v>
       </c>
@@ -5230,7 +5231,7 @@
         <v>4056.6080619999998</v>
       </c>
     </row>
-    <row r="172" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="2" t="s">
         <v>1</v>
       </c>
@@ -5256,7 +5257,7 @@
         <v>3742.6607640000002</v>
       </c>
     </row>
-    <row r="173" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="2" t="s">
         <v>1</v>
       </c>
@@ -5282,7 +5283,7 @@
         <v>2138.6398260000001</v>
       </c>
     </row>
-    <row r="174" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="2" t="s">
         <v>1</v>
       </c>
@@ -5308,7 +5309,7 @@
         <v>677.51928599999997</v>
       </c>
     </row>
-    <row r="175" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="2" t="s">
         <v>1</v>
       </c>
@@ -5334,7 +5335,7 @@
         <v>408.75640800000002</v>
       </c>
     </row>
-    <row r="176" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="2" t="s">
         <v>1</v>
       </c>
@@ -5360,7 +5361,7 @@
         <v>945.28779099999997</v>
       </c>
     </row>
-    <row r="177" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" s="2" t="s">
         <v>1</v>
       </c>
@@ -5412,7 +5413,7 @@
         <v>1585.211411</v>
       </c>
     </row>
-    <row r="179" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="2" t="s">
         <v>1</v>
       </c>
@@ -5438,7 +5439,7 @@
         <v>1546.8987669999999</v>
       </c>
     </row>
-    <row r="180" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
         <v>1</v>
       </c>
@@ -5464,7 +5465,7 @@
         <v>1478.568481</v>
       </c>
     </row>
-    <row r="181" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" s="2" t="s">
         <v>1</v>
       </c>
@@ -5490,7 +5491,7 @@
         <v>1913.0113490000001</v>
       </c>
     </row>
-    <row r="182" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="2" t="s">
         <v>1</v>
       </c>
@@ -5516,7 +5517,7 @@
         <v>2321.734649</v>
       </c>
     </row>
-    <row r="183" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" s="2" t="s">
         <v>1</v>
       </c>
@@ -5542,7 +5543,7 @@
         <v>3200.7922600000002</v>
       </c>
     </row>
-    <row r="184" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="2" t="s">
         <v>1</v>
       </c>
@@ -5568,7 +5569,7 @@
         <v>3427.1510269999999</v>
       </c>
     </row>
-    <row r="185" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" s="2" t="s">
         <v>1</v>
       </c>
@@ -5594,7 +5595,7 @@
         <v>3934.7823159999998</v>
       </c>
     </row>
-    <row r="186" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" s="2" t="s">
         <v>1</v>
       </c>
@@ -5620,7 +5621,7 @@
         <v>3739.801543</v>
       </c>
     </row>
-    <row r="187" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="2" t="s">
         <v>1</v>
       </c>
@@ -5646,7 +5647,7 @@
         <v>3531.5063919999998</v>
       </c>
     </row>
-    <row r="188" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" s="2" t="s">
         <v>1</v>
       </c>
@@ -5672,7 +5673,7 @@
         <v>2571.957304</v>
       </c>
     </row>
-    <row r="189" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" s="2" t="s">
         <v>1</v>
       </c>
@@ -5698,7 +5699,7 @@
         <v>1019.691052</v>
       </c>
     </row>
-    <row r="190" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" s="2" t="s">
         <v>1</v>
       </c>
@@ -5724,7 +5725,7 @@
         <v>242.36804100000001</v>
       </c>
     </row>
-    <row r="191" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="2" t="s">
         <v>1</v>
       </c>
@@ -5750,7 +5751,7 @@
         <v>618.219382</v>
       </c>
     </row>
-    <row r="192" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="2" t="s">
         <v>1</v>
       </c>
@@ -5802,7 +5803,7 @@
         <v>1416.8984399999999</v>
       </c>
     </row>
-    <row r="194" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" s="2" t="s">
         <v>1</v>
       </c>
@@ -5828,7 +5829,7 @@
         <v>1750.7139569999999</v>
       </c>
     </row>
-    <row r="195" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" s="2" t="s">
         <v>1</v>
       </c>
@@ -5854,7 +5855,7 @@
         <v>1839.5322200000001</v>
       </c>
     </row>
-    <row r="196" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" s="2" t="s">
         <v>1</v>
       </c>
@@ -5880,7 +5881,7 @@
         <v>2257.5529889999998</v>
       </c>
     </row>
-    <row r="197" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" s="2" t="s">
         <v>1</v>
       </c>
@@ -5906,7 +5907,7 @@
         <v>2457.1923940000001</v>
       </c>
     </row>
-    <row r="198" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198" s="2" t="s">
         <v>1</v>
       </c>
@@ -5932,7 +5933,7 @@
         <v>3045.274469</v>
       </c>
     </row>
-    <row r="199" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" s="2" t="s">
         <v>1</v>
       </c>
@@ -5958,7 +5959,7 @@
         <v>3395.3134639999998</v>
       </c>
     </row>
-    <row r="200" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" s="2" t="s">
         <v>1</v>
       </c>
@@ -5984,7 +5985,7 @@
         <v>3917.2267999999999</v>
       </c>
     </row>
-    <row r="201" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" s="2" t="s">
         <v>1</v>
       </c>
@@ -6010,7 +6011,7 @@
         <v>4001.2638780000002</v>
       </c>
     </row>
-    <row r="202" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202" s="2" t="s">
         <v>1</v>
       </c>
@@ -6036,7 +6037,7 @@
         <v>4120.7367050000003</v>
       </c>
     </row>
-    <row r="203" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203" s="2" t="s">
         <v>1</v>
       </c>
@@ -6062,7 +6063,7 @@
         <v>2462.757861</v>
       </c>
     </row>
-    <row r="204" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204" s="2" t="s">
         <v>1</v>
       </c>
@@ -6088,7 +6089,7 @@
         <v>1214.0211569999999</v>
       </c>
     </row>
-    <row r="205" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A205" s="2" t="s">
         <v>1</v>
       </c>
@@ -6114,7 +6115,7 @@
         <v>377.24842000000001</v>
       </c>
     </row>
-    <row r="206" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A206" s="2" t="s">
         <v>1</v>
       </c>
@@ -6140,7 +6141,7 @@
         <v>661.29326600000002</v>
       </c>
     </row>
-    <row r="207" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A207" s="2" t="s">
         <v>1</v>
       </c>
@@ -6192,7 +6193,7 @@
         <v>1387.4629</v>
       </c>
     </row>
-    <row r="209" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A209" s="2" t="s">
         <v>1</v>
       </c>
@@ -6218,7 +6219,7 @@
         <v>1402.9269690000001</v>
       </c>
     </row>
-    <row r="210" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A210" s="2" t="s">
         <v>1</v>
       </c>
@@ -6244,7 +6245,7 @@
         <v>1298.310763</v>
       </c>
     </row>
-    <row r="211" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A211" s="2" t="s">
         <v>1</v>
       </c>
@@ -6270,7 +6271,7 @@
         <v>1884.83377</v>
       </c>
     </row>
-    <row r="212" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A212" s="2" t="s">
         <v>1</v>
       </c>
@@ -6296,7 +6297,7 @@
         <v>2424.1899600000002</v>
       </c>
     </row>
-    <row r="213" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A213" s="2" t="s">
         <v>1</v>
       </c>
@@ -6322,7 +6323,7 @@
         <v>2894.764021</v>
       </c>
     </row>
-    <row r="214" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A214" s="2" t="s">
         <v>1</v>
       </c>
@@ -6348,7 +6349,7 @@
         <v>3664.9933030000002</v>
       </c>
     </row>
-    <row r="215" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A215" s="2" t="s">
         <v>1</v>
       </c>
@@ -6374,7 +6375,7 @@
         <v>4321.2774589999999</v>
       </c>
     </row>
-    <row r="216" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A216" s="2" t="s">
         <v>1</v>
       </c>
@@ -6400,7 +6401,7 @@
         <v>4425.4977870000002</v>
       </c>
     </row>
-    <row r="217" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A217" s="2" t="s">
         <v>1</v>
       </c>
@@ -6426,7 +6427,7 @@
         <v>3916.2979190000001</v>
       </c>
     </row>
-    <row r="218" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A218" s="2" t="s">
         <v>1</v>
       </c>
@@ -6452,7 +6453,7 @@
         <v>2281.678222</v>
       </c>
     </row>
-    <row r="219" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A219" s="2" t="s">
         <v>1</v>
       </c>
@@ -6478,7 +6479,7 @@
         <v>932.21952999999996</v>
       </c>
     </row>
-    <row r="220" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A220" s="2" t="s">
         <v>1</v>
       </c>
@@ -6504,7 +6505,7 @@
         <v>305.27260699999999</v>
       </c>
     </row>
-    <row r="221" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A221" s="2" t="s">
         <v>1</v>
       </c>
@@ -6530,7 +6531,7 @@
         <v>784.22994500000004</v>
       </c>
     </row>
-    <row r="222" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A222" s="2" t="s">
         <v>1</v>
       </c>
@@ -6582,7 +6583,7 @@
         <v>1556.2085549999999</v>
       </c>
     </row>
-    <row r="224" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A224" s="2" t="s">
         <v>1</v>
       </c>
@@ -6608,7 +6609,7 @@
         <v>1608.17338</v>
       </c>
     </row>
-    <row r="225" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A225" s="2" t="s">
         <v>1</v>
       </c>
@@ -6634,7 +6635,7 @@
         <v>1582.9089329999999</v>
       </c>
     </row>
-    <row r="226" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A226" s="2" t="s">
         <v>1</v>
       </c>
@@ -6660,7 +6661,7 @@
         <v>2072.7168270000002</v>
       </c>
     </row>
-    <row r="227" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A227" s="2" t="s">
         <v>1</v>
       </c>
@@ -6686,7 +6687,7 @@
         <v>2364.4791610000002</v>
       </c>
     </row>
-    <row r="228" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A228" s="2" t="s">
         <v>1</v>
       </c>
@@ -6712,7 +6713,7 @@
         <v>3168.1837500000001</v>
       </c>
     </row>
-    <row r="229" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A229" s="2" t="s">
         <v>1</v>
       </c>
@@ -6738,7 +6739,7 @@
         <v>3858.0020249999998</v>
       </c>
     </row>
-    <row r="230" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A230" s="2" t="s">
         <v>1</v>
       </c>
@@ -6764,7 +6765,7 @@
         <v>4303.0383309999997</v>
       </c>
     </row>
-    <row r="231" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A231" s="2" t="s">
         <v>1</v>
       </c>
@@ -6790,7 +6791,7 @@
         <v>3972.3816379999998</v>
       </c>
     </row>
-    <row r="232" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A232" s="2" t="s">
         <v>1</v>
       </c>
@@ -6816,7 +6817,7 @@
         <v>3899.610228</v>
       </c>
     </row>
-    <row r="233" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A233" s="2" t="s">
         <v>1</v>
       </c>
@@ -6842,7 +6843,7 @@
         <v>2427.7212300000001</v>
       </c>
     </row>
-    <row r="234" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A234" s="2" t="s">
         <v>1</v>
       </c>
@@ -6868,7 +6869,7 @@
         <v>1046.0439510000001</v>
       </c>
     </row>
-    <row r="235" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A235" s="2" t="s">
         <v>1</v>
       </c>
@@ -6894,7 +6895,7 @@
         <v>394.406837</v>
       </c>
     </row>
-    <row r="236" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A236" s="2" t="s">
         <v>1</v>
       </c>
@@ -6920,7 +6921,7 @@
         <v>956.03068099999996</v>
       </c>
     </row>
-    <row r="237" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A237" s="2" t="s">
         <v>1</v>
       </c>
@@ -6972,7 +6973,7 @@
         <v>1540.070541</v>
       </c>
     </row>
-    <row r="239" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A239" s="2" t="s">
         <v>1</v>
       </c>
@@ -6998,7 +6999,7 @@
         <v>1608.663816</v>
       </c>
     </row>
-    <row r="240" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A240" s="2" t="s">
         <v>1</v>
       </c>
@@ -7024,7 +7025,7 @@
         <v>1708.6623970000001</v>
       </c>
     </row>
-    <row r="241" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A241" s="2" t="s">
         <v>1</v>
       </c>
@@ -7050,7 +7051,7 @@
         <v>2247.7823830000002</v>
       </c>
     </row>
-    <row r="242" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A242" s="2" t="s">
         <v>1</v>
       </c>
@@ -7076,7 +7077,7 @@
         <v>2614.9169879999999</v>
       </c>
     </row>
-    <row r="243" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A243" s="2" t="s">
         <v>1</v>
       </c>
@@ -7102,7 +7103,7 @@
         <v>3700.9143800000002</v>
       </c>
     </row>
-    <row r="244" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A244" s="2" t="s">
         <v>1</v>
       </c>
@@ -7128,7 +7129,7 @@
         <v>4320.9134839999997</v>
       </c>
     </row>
-    <row r="245" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A245" s="2" t="s">
         <v>1</v>
       </c>
@@ -7154,7 +7155,7 @@
         <v>4566.4738360000001</v>
       </c>
     </row>
-    <row r="246" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A246" s="2" t="s">
         <v>1</v>
       </c>
@@ -7180,7 +7181,7 @@
         <v>4422.415841</v>
       </c>
     </row>
-    <row r="247" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A247" s="2" t="s">
         <v>1</v>
       </c>
@@ -7206,7 +7207,7 @@
         <v>3670.9107359999998</v>
       </c>
     </row>
-    <row r="248" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A248" s="2" t="s">
         <v>1</v>
       </c>
@@ -7232,7 +7233,7 @@
         <v>2162.310786</v>
       </c>
     </row>
-    <row r="249" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A249" s="2" t="s">
         <v>1</v>
       </c>
@@ -7258,7 +7259,7 @@
         <v>738.847757</v>
       </c>
     </row>
-    <row r="250" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A250" s="2" t="s">
         <v>1</v>
       </c>
@@ -7284,7 +7285,7 @@
         <v>344.73537399999998</v>
       </c>
     </row>
-    <row r="251" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A251" s="2" t="s">
         <v>1</v>
       </c>
@@ -7310,7 +7311,7 @@
         <v>1007.627396</v>
       </c>
     </row>
-    <row r="252" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A252" s="2" t="s">
         <v>1</v>
       </c>
@@ -7362,7 +7363,7 @@
         <v>1558.469828</v>
       </c>
     </row>
-    <row r="254" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A254" s="2" t="s">
         <v>1</v>
       </c>
@@ -7388,7 +7389,7 @@
         <v>1577.0601979999999</v>
       </c>
     </row>
-    <row r="255" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A255" s="2" t="s">
         <v>1</v>
       </c>
@@ -7414,7 +7415,7 @@
         <v>1579.866374</v>
       </c>
     </row>
-    <row r="256" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A256" s="2" t="s">
         <v>1</v>
       </c>
@@ -7440,7 +7441,7 @@
         <v>2044.721875</v>
       </c>
     </row>
-    <row r="257" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A257" s="2" t="s">
         <v>1</v>
       </c>
@@ -7466,7 +7467,7 @@
         <v>2404.4087399999999</v>
       </c>
     </row>
-    <row r="258" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A258" s="2" t="s">
         <v>1</v>
       </c>
@@ -7492,7 +7493,7 @@
         <v>3034.8436590000001</v>
       </c>
     </row>
-    <row r="259" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A259" s="2" t="s">
         <v>1</v>
       </c>
@@ -7518,7 +7519,7 @@
         <v>3781.0486930000002</v>
       </c>
     </row>
-    <row r="260" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A260" s="2" t="s">
         <v>1</v>
       </c>
@@ -7544,7 +7545,7 @@
         <v>4036.2989950000001</v>
       </c>
     </row>
-    <row r="261" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A261" s="2" t="s">
         <v>1</v>
       </c>
@@ -7570,7 +7571,7 @@
         <v>4084.8014710000002</v>
       </c>
     </row>
-    <row r="262" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A262" s="2" t="s">
         <v>1</v>
       </c>
@@ -7596,7 +7597,7 @@
         <v>4157.1242480000001</v>
       </c>
     </row>
-    <row r="263" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A263" s="2" t="s">
         <v>1</v>
       </c>
@@ -7622,7 +7623,7 @@
         <v>2821.3793340000002</v>
       </c>
     </row>
-    <row r="264" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A264" s="2" t="s">
         <v>1</v>
       </c>
@@ -7648,7 +7649,7 @@
         <v>1070.875057</v>
       </c>
     </row>
-    <row r="265" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A265" s="2" t="s">
         <v>1</v>
       </c>
@@ -7674,7 +7675,7 @@
         <v>284.31872399999997</v>
       </c>
     </row>
-    <row r="266" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A266" s="2" t="s">
         <v>1</v>
       </c>
@@ -7700,7 +7701,7 @@
         <v>830.15711599999997</v>
       </c>
     </row>
-    <row r="267" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A267" s="2" t="s">
         <v>1</v>
       </c>
@@ -7752,7 +7753,7 @@
         <v>1550.7845749999999</v>
       </c>
     </row>
-    <row r="269" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A269" s="2" t="s">
         <v>1</v>
       </c>
@@ -7778,7 +7779,7 @@
         <v>1443.3059490000001</v>
       </c>
     </row>
-    <row r="270" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A270" s="2" t="s">
         <v>1</v>
       </c>
@@ -7804,7 +7805,7 @@
         <v>1509.612811</v>
       </c>
     </row>
-    <row r="271" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A271" s="2" t="s">
         <v>1</v>
       </c>
@@ -7830,7 +7831,7 @@
         <v>2273.896025</v>
       </c>
     </row>
-    <row r="272" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A272" s="2" t="s">
         <v>1</v>
       </c>
@@ -7856,7 +7857,7 @@
         <v>2677.5167299999998</v>
       </c>
     </row>
-    <row r="273" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A273" s="2" t="s">
         <v>1</v>
       </c>
@@ -7882,7 +7883,7 @@
         <v>3201.9476300000001</v>
       </c>
     </row>
-    <row r="274" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A274" s="2" t="s">
         <v>1</v>
       </c>
@@ -7908,7 +7909,7 @@
         <v>3756.7620189999998</v>
       </c>
     </row>
-    <row r="275" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A275" s="2" t="s">
         <v>1</v>
       </c>
@@ -7934,7 +7935,7 @@
         <v>4332.5251070000004</v>
       </c>
     </row>
-    <row r="276" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A276" s="2" t="s">
         <v>1</v>
       </c>
@@ -7960,7 +7961,7 @@
         <v>4178.7576730000001</v>
       </c>
     </row>
-    <row r="277" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A277" s="2" t="s">
         <v>1</v>
       </c>
@@ -7986,7 +7987,7 @@
         <v>3936.191421</v>
       </c>
     </row>
-    <row r="278" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A278" s="2" t="s">
         <v>1</v>
       </c>
@@ -8012,7 +8013,7 @@
         <v>2749.9767069999998</v>
       </c>
     </row>
-    <row r="279" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A279" s="2" t="s">
         <v>1</v>
       </c>
@@ -8038,7 +8039,7 @@
         <v>1132.9599740000001</v>
       </c>
     </row>
-    <row r="280" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A280" s="2" t="s">
         <v>1</v>
       </c>
@@ -8064,7 +8065,7 @@
         <v>487.77528000000001</v>
       </c>
     </row>
-    <row r="281" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A281" s="2" t="s">
         <v>1</v>
       </c>
@@ -8090,7 +8091,7 @@
         <v>837.16062299999999</v>
       </c>
     </row>
-    <row r="282" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A282" s="2" t="s">
         <v>1</v>
       </c>
@@ -8142,7 +8143,7 @@
         <v>1397.9728050000001</v>
       </c>
     </row>
-    <row r="284" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A284" s="2" t="s">
         <v>1</v>
       </c>
@@ -8168,7 +8169,7 @@
         <v>1515.492972</v>
       </c>
     </row>
-    <row r="285" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A285" s="2" t="s">
         <v>1</v>
       </c>
@@ -8194,7 +8195,7 @@
         <v>1705.29035</v>
       </c>
     </row>
-    <row r="286" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A286" s="2" t="s">
         <v>1</v>
       </c>
@@ -8220,7 +8221,7 @@
         <v>2076.5091990000001</v>
       </c>
     </row>
-    <row r="287" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A287" s="2" t="s">
         <v>1</v>
       </c>
@@ -8246,7 +8247,7 @@
         <v>2454.5889219999999</v>
       </c>
     </row>
-    <row r="288" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A288" s="2" t="s">
         <v>1</v>
       </c>
@@ -8272,7 +8273,7 @@
         <v>3106.293979</v>
       </c>
     </row>
-    <row r="289" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A289" s="2" t="s">
         <v>1</v>
       </c>
@@ -8298,7 +8299,7 @@
         <v>3748.649531</v>
       </c>
     </row>
-    <row r="290" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A290" s="2" t="s">
         <v>1</v>
       </c>
@@ -8324,7 +8325,7 @@
         <v>4400.1984869999997</v>
       </c>
     </row>
-    <row r="291" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A291" s="2" t="s">
         <v>1</v>
       </c>
@@ -8350,7 +8351,7 @@
         <v>4335.0955130000002</v>
       </c>
     </row>
-    <row r="292" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A292" s="2" t="s">
         <v>1</v>
       </c>
@@ -8376,7 +8377,7 @@
         <v>3949.6297930000001</v>
       </c>
     </row>
-    <row r="293" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A293" s="2" t="s">
         <v>1</v>
       </c>
@@ -8402,7 +8403,7 @@
         <v>2623.6198549999999</v>
       </c>
     </row>
-    <row r="294" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A294" s="2" t="s">
         <v>1</v>
       </c>
@@ -8428,7 +8429,7 @@
         <v>1065.148285</v>
       </c>
     </row>
-    <row r="295" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A295" s="2" t="s">
         <v>1</v>
       </c>
@@ -8454,7 +8455,7 @@
         <v>399.00652700000001</v>
       </c>
     </row>
-    <row r="296" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A296" s="2" t="s">
         <v>1</v>
       </c>
@@ -8480,7 +8481,7 @@
         <v>969.18797199999995</v>
       </c>
     </row>
-    <row r="297" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A297" s="2" t="s">
         <v>1</v>
       </c>
@@ -8532,7 +8533,7 @@
         <v>1554.4569200000001</v>
       </c>
     </row>
-    <row r="299" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A299" s="2" t="s">
         <v>1</v>
       </c>
@@ -8558,7 +8559,7 @@
         <v>1586.1406979999999</v>
       </c>
     </row>
-    <row r="300" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A300" s="2" t="s">
         <v>1</v>
       </c>
@@ -8584,7 +8585,7 @@
         <v>1743.654544</v>
       </c>
     </row>
-    <row r="301" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A301" s="2" t="s">
         <v>1</v>
       </c>
@@ -8610,7 +8611,7 @@
         <v>2464.119177</v>
       </c>
     </row>
-    <row r="302" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A302" s="2" t="s">
         <v>1</v>
       </c>
@@ -8636,7 +8637,7 @@
         <v>2663.8434430000002</v>
       </c>
     </row>
-    <row r="303" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A303" s="2" t="s">
         <v>1</v>
       </c>
@@ -8662,7 +8663,7 @@
         <v>3383.8120829999998</v>
       </c>
     </row>
-    <row r="304" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A304" s="2" t="s">
         <v>1</v>
       </c>
@@ -8688,7 +8689,7 @@
         <v>3870.8869749999999</v>
       </c>
     </row>
-    <row r="305" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A305" s="2" t="s">
         <v>1</v>
       </c>
@@ -8714,7 +8715,7 @@
         <v>4808.6590329999999</v>
       </c>
     </row>
-    <row r="306" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A306" s="2" t="s">
         <v>1</v>
       </c>
@@ -8740,7 +8741,7 @@
         <v>4303.9243390000001</v>
       </c>
     </row>
-    <row r="307" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A307" s="2" t="s">
         <v>1</v>
       </c>
@@ -8766,7 +8767,7 @@
         <v>3972.9581499999999</v>
       </c>
     </row>
-    <row r="308" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A308" s="2" t="s">
         <v>1</v>
       </c>
@@ -8792,7 +8793,7 @@
         <v>2553.3513389999998</v>
       </c>
     </row>
-    <row r="309" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A309" s="2" t="s">
         <v>1</v>
       </c>
@@ -8818,7 +8819,7 @@
         <v>778.28286700000001</v>
       </c>
     </row>
-    <row r="310" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A310" s="2" t="s">
         <v>1</v>
       </c>
@@ -8844,7 +8845,7 @@
         <v>474.18467299999998</v>
       </c>
     </row>
-    <row r="311" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A311" s="2" t="s">
         <v>1</v>
       </c>
@@ -8870,7 +8871,7 @@
         <v>1055.6471240000001</v>
       </c>
     </row>
-    <row r="312" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A312" s="2" t="s">
         <v>1</v>
       </c>
@@ -8922,7 +8923,7 @@
         <v>1642.4056720000001</v>
       </c>
     </row>
-    <row r="314" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A314" s="2" t="s">
         <v>1</v>
       </c>
@@ -8948,7 +8949,7 @@
         <v>1595.0075730000001</v>
       </c>
     </row>
-    <row r="315" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A315" s="2" t="s">
         <v>1</v>
       </c>
@@ -8974,7 +8975,7 @@
         <v>1670.5622989999999</v>
       </c>
     </row>
-    <row r="316" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A316" s="2" t="s">
         <v>1</v>
       </c>
@@ -9000,7 +9001,7 @@
         <v>2016.387534</v>
       </c>
     </row>
-    <row r="317" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A317" s="2" t="s">
         <v>1</v>
       </c>
@@ -9026,7 +9027,7 @@
         <v>2485.3573390000001</v>
       </c>
     </row>
-    <row r="318" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A318" s="2" t="s">
         <v>1</v>
       </c>
@@ -9052,7 +9053,7 @@
         <v>3095.3428990000002</v>
       </c>
     </row>
-    <row r="319" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A319" s="2" t="s">
         <v>1</v>
       </c>
@@ -9078,7 +9079,7 @@
         <v>3607.4480589999998</v>
       </c>
     </row>
-    <row r="320" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A320" s="2" t="s">
         <v>1</v>
       </c>
@@ -9104,7 +9105,7 @@
         <v>3926.7474929999998</v>
       </c>
     </row>
-    <row r="321" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A321" s="2" t="s">
         <v>1</v>
       </c>
@@ -9130,7 +9131,7 @@
         <v>3907.7432950000002</v>
       </c>
     </row>
-    <row r="322" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A322" s="2" t="s">
         <v>1</v>
       </c>
@@ -9156,7 +9157,7 @@
         <v>3352.9935409999998</v>
       </c>
     </row>
-    <row r="323" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A323" s="2" t="s">
         <v>1</v>
       </c>
@@ -9182,7 +9183,7 @@
         <v>2398.9623419999998</v>
       </c>
     </row>
-    <row r="324" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A324" s="2" t="s">
         <v>1</v>
       </c>
@@ -9208,7 +9209,7 @@
         <v>652.13566600000001</v>
       </c>
     </row>
-    <row r="325" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A325" s="2" t="s">
         <v>1</v>
       </c>
@@ -9234,7 +9235,7 @@
         <v>316.54869300000001</v>
       </c>
     </row>
-    <row r="326" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A326" s="2" t="s">
         <v>1</v>
       </c>
@@ -9260,7 +9261,7 @@
         <v>723.31758300000001</v>
       </c>
     </row>
-    <row r="327" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A327" s="2" t="s">
         <v>1</v>
       </c>
@@ -9312,7 +9313,7 @@
         <v>1472.5453339999999</v>
       </c>
     </row>
-    <row r="329" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A329" s="2" t="s">
         <v>1</v>
       </c>
@@ -9338,7 +9339,7 @@
         <v>1519.516259</v>
       </c>
     </row>
-    <row r="330" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A330" s="2" t="s">
         <v>1</v>
       </c>
@@ -9364,7 +9365,7 @@
         <v>1612.869455</v>
       </c>
     </row>
-    <row r="331" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A331" s="2" t="s">
         <v>1</v>
       </c>
@@ -9390,7 +9391,7 @@
         <v>1827.998902</v>
       </c>
     </row>
-    <row r="332" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A332" s="2" t="s">
         <v>1</v>
       </c>
@@ -9416,7 +9417,7 @@
         <v>2357.1189690000001</v>
       </c>
     </row>
-    <row r="333" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A333" s="2" t="s">
         <v>1</v>
       </c>
@@ -9442,7 +9443,7 @@
         <v>3152.82321</v>
       </c>
     </row>
-    <row r="334" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A334" s="2" t="s">
         <v>1</v>
       </c>
@@ -9468,7 +9469,7 @@
         <v>3376.3958090000001</v>
       </c>
     </row>
-    <row r="335" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A335" s="2" t="s">
         <v>1</v>
       </c>
@@ -9494,7 +9495,7 @@
         <v>3891.7009589999998</v>
       </c>
     </row>
-    <row r="336" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A336" s="2" t="s">
         <v>1</v>
       </c>
@@ -9520,7 +9521,7 @@
         <v>3826.4375949999999</v>
       </c>
     </row>
-    <row r="337" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A337" s="2" t="s">
         <v>1</v>
       </c>
@@ -9546,7 +9547,7 @@
         <v>3803.5983310000001</v>
       </c>
     </row>
-    <row r="338" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A338" s="2" t="s">
         <v>1</v>
       </c>
@@ -9572,7 +9573,7 @@
         <v>2466.3465609999998</v>
       </c>
     </row>
-    <row r="339" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A339" s="2" t="s">
         <v>1</v>
       </c>
@@ -9598,7 +9599,7 @@
         <v>845.97471700000006</v>
       </c>
     </row>
-    <row r="340" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A340" s="2" t="s">
         <v>1</v>
       </c>
@@ -9624,7 +9625,7 @@
         <v>287.14895899999999</v>
       </c>
     </row>
-    <row r="341" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A341" s="2" t="s">
         <v>1</v>
       </c>
@@ -9650,7 +9651,7 @@
         <v>859.73106700000005</v>
       </c>
     </row>
-    <row r="342" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A342" s="2" t="s">
         <v>1</v>
       </c>
@@ -9702,7 +9703,7 @@
         <v>1526.4797100000001</v>
       </c>
     </row>
-    <row r="344" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A344" s="2" t="s">
         <v>1</v>
       </c>
@@ -9728,7 +9729,7 @@
         <v>1582.7345210000001</v>
       </c>
     </row>
-    <row r="345" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A345" s="2" t="s">
         <v>1</v>
       </c>
@@ -9754,7 +9755,7 @@
         <v>1758.2569699999999</v>
       </c>
     </row>
-    <row r="346" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A346" s="2" t="s">
         <v>1</v>
       </c>
@@ -9780,7 +9781,7 @@
         <v>2305.8918090000002</v>
       </c>
     </row>
-    <row r="347" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A347" s="2" t="s">
         <v>1</v>
       </c>
@@ -9806,7 +9807,7 @@
         <v>2480.71164</v>
       </c>
     </row>
-    <row r="348" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A348" s="2" t="s">
         <v>1</v>
       </c>
@@ -9832,7 +9833,7 @@
         <v>3141.8619119999998</v>
       </c>
     </row>
-    <row r="349" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A349" s="2" t="s">
         <v>1</v>
       </c>
@@ -9858,7 +9859,7 @@
         <v>3565.3710649999998</v>
       </c>
     </row>
-    <row r="350" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A350" s="2" t="s">
         <v>1</v>
       </c>
@@ -9884,7 +9885,7 @@
         <v>3984.0854720000002</v>
       </c>
     </row>
-    <row r="351" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A351" s="2" t="s">
         <v>1</v>
       </c>
@@ -9910,7 +9911,7 @@
         <v>4225.1512570000004</v>
       </c>
     </row>
-    <row r="352" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A352" s="2" t="s">
         <v>1</v>
       </c>
@@ -9936,7 +9937,7 @@
         <v>3902.2351899999999</v>
       </c>
     </row>
-    <row r="353" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A353" s="2" t="s">
         <v>1</v>
       </c>
@@ -9962,7 +9963,7 @@
         <v>2524.0925350000002</v>
       </c>
     </row>
-    <row r="354" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A354" s="2" t="s">
         <v>1</v>
       </c>
@@ -9988,7 +9989,7 @@
         <v>1130.6442890000001</v>
       </c>
     </row>
-    <row r="355" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A355" s="2" t="s">
         <v>1</v>
       </c>
@@ -10014,7 +10015,7 @@
         <v>431.009951</v>
       </c>
     </row>
-    <row r="356" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A356" s="2" t="s">
         <v>1</v>
       </c>
@@ -10040,7 +10041,7 @@
         <v>915.71633199999997</v>
       </c>
     </row>
-    <row r="357" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A357" s="2" t="s">
         <v>1</v>
       </c>
@@ -10092,7 +10093,7 @@
         <v>1503.2281350000001</v>
       </c>
     </row>
-    <row r="359" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A359" s="2" t="s">
         <v>1</v>
       </c>
@@ -10118,7 +10119,7 @@
         <v>1484.8924999999999</v>
       </c>
     </row>
-    <row r="360" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A360" s="2" t="s">
         <v>1</v>
       </c>
@@ -10144,7 +10145,7 @@
         <v>1587.2274950000001</v>
       </c>
     </row>
-    <row r="361" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A361" s="2" t="s">
         <v>1</v>
       </c>
@@ -10170,7 +10171,7 @@
         <v>2191.1130010000002</v>
       </c>
     </row>
-    <row r="362" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A362" s="2" t="s">
         <v>1</v>
       </c>
@@ -10196,7 +10197,7 @@
         <v>2468.0986830000002</v>
       </c>
     </row>
-    <row r="363" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A363" s="2" t="s">
         <v>1</v>
       </c>
@@ -10222,7 +10223,7 @@
         <v>3212.0334950000001</v>
       </c>
     </row>
-    <row r="364" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A364" s="2" t="s">
         <v>1</v>
       </c>
@@ -10248,7 +10249,7 @@
         <v>3795.7274440000001</v>
       </c>
     </row>
-    <row r="365" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A365" s="2" t="s">
         <v>1</v>
       </c>
@@ -10274,7 +10275,7 @@
         <v>4415.8087230000001</v>
       </c>
     </row>
-    <row r="366" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A366" s="2" t="s">
         <v>1</v>
       </c>
@@ -10300,7 +10301,7 @@
         <v>4315.4171100000003</v>
       </c>
     </row>
-    <row r="367" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A367" s="2" t="s">
         <v>1</v>
       </c>
@@ -10326,7 +10327,7 @@
         <v>3951.0096629999998</v>
       </c>
     </row>
-    <row r="368" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A368" s="2" t="s">
         <v>1</v>
       </c>
@@ -10352,7 +10353,7 @@
         <v>2535.4839809999999</v>
       </c>
     </row>
-    <row r="369" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A369" s="2" t="s">
         <v>1</v>
       </c>
@@ -10378,7 +10379,7 @@
         <v>908.95164999999997</v>
       </c>
     </row>
-    <row r="370" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A370" s="2" t="s">
         <v>1</v>
       </c>
@@ -10404,7 +10405,7 @@
         <v>378.52808199999998</v>
       </c>
     </row>
-    <row r="371" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A371" s="2" t="s">
         <v>1</v>
       </c>
@@ -10430,7 +10431,7 @@
         <v>959.211412</v>
       </c>
     </row>
-    <row r="372" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A372" s="2" t="s">
         <v>1</v>
       </c>
@@ -10482,7 +10483,7 @@
         <v>1472.090432</v>
       </c>
     </row>
-    <row r="374" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A374" s="2" t="s">
         <v>1</v>
       </c>
@@ -10508,7 +10509,7 @@
         <v>1616.0917999999999</v>
       </c>
     </row>
-    <row r="375" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A375" s="2" t="s">
         <v>1</v>
       </c>
@@ -10534,7 +10535,7 @@
         <v>1696.8972610000001</v>
       </c>
     </row>
-    <row r="376" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A376" s="2" t="s">
         <v>1</v>
       </c>
@@ -10560,7 +10561,7 @@
         <v>2209.8484509999998</v>
       </c>
     </row>
-    <row r="377" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A377" s="2" t="s">
         <v>1</v>
       </c>
@@ -10586,7 +10587,7 @@
         <v>2669.3757449999998</v>
       </c>
     </row>
-    <row r="378" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A378" s="2" t="s">
         <v>1</v>
       </c>
@@ -10612,7 +10613,7 @@
         <v>3440.403812</v>
       </c>
     </row>
-    <row r="379" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A379" s="2" t="s">
         <v>1</v>
       </c>
@@ -10638,7 +10639,7 @@
         <v>3802.8783469999998</v>
       </c>
     </row>
-    <row r="380" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A380" s="2" t="s">
         <v>1</v>
       </c>
@@ -10664,7 +10665,7 @@
         <v>4514.5574640000004</v>
       </c>
     </row>
-    <row r="381" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A381" s="2" t="s">
         <v>1</v>
       </c>
@@ -10690,7 +10691,7 @@
         <v>4485.4404560000003</v>
       </c>
     </row>
-    <row r="382" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A382" s="2" t="s">
         <v>1</v>
       </c>
@@ -10716,7 +10717,7 @@
         <v>3814.5754000000002</v>
       </c>
     </row>
-    <row r="383" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A383" s="2" t="s">
         <v>1</v>
       </c>
@@ -10742,7 +10743,7 @@
         <v>2356.9418580000001</v>
       </c>
     </row>
-    <row r="384" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A384" s="2" t="s">
         <v>1</v>
       </c>
@@ -10768,7 +10769,7 @@
         <v>968.79826500000001</v>
       </c>
     </row>
-    <row r="385" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A385" s="2" t="s">
         <v>1</v>
       </c>
@@ -10794,7 +10795,7 @@
         <v>385.872544</v>
       </c>
     </row>
-    <row r="386" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A386" s="2" t="s">
         <v>1</v>
       </c>
@@ -10820,7 +10821,7 @@
         <v>982.998152</v>
       </c>
     </row>
-    <row r="387" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A387" s="2" t="s">
         <v>1</v>
       </c>
@@ -10872,7 +10873,7 @@
         <v>1545.4451610000001</v>
       </c>
     </row>
-    <row r="389" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A389" s="2" t="s">
         <v>1</v>
       </c>
@@ -10898,7 +10899,7 @@
         <v>1440.7573279999999</v>
       </c>
     </row>
-    <row r="390" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A390" s="2" t="s">
         <v>1</v>
       </c>
@@ -10924,7 +10925,7 @@
         <v>1867.474412</v>
       </c>
     </row>
-    <row r="391" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A391" s="2" t="s">
         <v>1</v>
       </c>
@@ -10950,7 +10951,7 @@
         <v>2334.0456760000002</v>
       </c>
     </row>
-    <row r="392" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A392" s="2" t="s">
         <v>1</v>
       </c>
@@ -10976,7 +10977,7 @@
         <v>2512.7856200000001</v>
       </c>
     </row>
-    <row r="393" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A393" s="2" t="s">
         <v>1</v>
       </c>
@@ -11002,7 +11003,7 @@
         <v>3137.4727269999998</v>
       </c>
     </row>
-    <row r="394" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A394" s="2" t="s">
         <v>1</v>
       </c>
@@ -11028,7 +11029,7 @@
         <v>3832.2948179999999</v>
       </c>
     </row>
-    <row r="395" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A395" s="2" t="s">
         <v>1</v>
       </c>
@@ -11054,7 +11055,7 @@
         <v>4208.3900270000004</v>
       </c>
     </row>
-    <row r="396" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A396" s="2" t="s">
         <v>1</v>
       </c>
@@ -11080,7 +11081,7 @@
         <v>4144.8292760000004</v>
       </c>
     </row>
-    <row r="397" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A397" s="2" t="s">
         <v>1</v>
       </c>
@@ -11106,7 +11107,7 @@
         <v>3709.3870820000002</v>
       </c>
     </row>
-    <row r="398" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A398" s="2" t="s">
         <v>1</v>
       </c>
@@ -11132,7 +11133,7 @@
         <v>2302.303406</v>
       </c>
     </row>
-    <row r="399" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A399" s="2" t="s">
         <v>1</v>
       </c>
@@ -11158,7 +11159,7 @@
         <v>833.621126</v>
       </c>
     </row>
-    <row r="400" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A400" s="2" t="s">
         <v>1</v>
       </c>
@@ -11184,7 +11185,7 @@
         <v>450.68197400000003</v>
       </c>
     </row>
-    <row r="401" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A401" s="2" t="s">
         <v>1</v>
       </c>
@@ -11210,7 +11211,7 @@
         <v>1043.7207989999999</v>
       </c>
     </row>
-    <row r="402" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A402" s="2" t="s">
         <v>1</v>
       </c>
@@ -11262,7 +11263,7 @@
         <v>1452.3960830000001</v>
       </c>
     </row>
-    <row r="404" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A404" s="2" t="s">
         <v>1</v>
       </c>
@@ -11288,7 +11289,7 @@
         <v>1441.149461</v>
       </c>
     </row>
-    <row r="405" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A405" s="2" t="s">
         <v>1</v>
       </c>
@@ -11314,7 +11315,7 @@
         <v>1472.2091969999999</v>
       </c>
     </row>
-    <row r="406" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A406" s="2" t="s">
         <v>1</v>
       </c>
@@ -11340,7 +11341,7 @@
         <v>2038.106043</v>
       </c>
     </row>
-    <row r="407" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A407" s="2" t="s">
         <v>1</v>
       </c>
@@ -11366,7 +11367,7 @@
         <v>2423.735635</v>
       </c>
     </row>
-    <row r="408" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A408" s="2" t="s">
         <v>1</v>
       </c>
@@ -11392,7 +11393,7 @@
         <v>3140.9392039999998</v>
       </c>
     </row>
-    <row r="409" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A409" s="2" t="s">
         <v>1</v>
       </c>
@@ -11418,7 +11419,7 @@
         <v>3880.742655</v>
       </c>
     </row>
-    <row r="410" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A410" s="2" t="s">
         <v>1</v>
       </c>
@@ -11444,7 +11445,7 @@
         <v>4172.9899800000003</v>
       </c>
     </row>
-    <row r="411" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A411" s="2" t="s">
         <v>1</v>
       </c>
@@ -11470,7 +11471,7 @@
         <v>4037.0822229999999</v>
       </c>
     </row>
-    <row r="412" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A412" s="2" t="s">
         <v>1</v>
       </c>
@@ -11496,7 +11497,7 @@
         <v>3603.601682</v>
       </c>
     </row>
-    <row r="413" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A413" s="2" t="s">
         <v>1</v>
       </c>
@@ -11522,7 +11523,7 @@
         <v>2545.5960340000001</v>
       </c>
     </row>
-    <row r="414" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A414" s="2" t="s">
         <v>1</v>
       </c>
@@ -11548,7 +11549,7 @@
         <v>705.83279800000003</v>
       </c>
     </row>
-    <row r="415" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A415" s="2" t="s">
         <v>1</v>
       </c>
@@ -11574,7 +11575,7 @@
         <v>520.83662200000003</v>
       </c>
     </row>
-    <row r="416" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A416" s="2" t="s">
         <v>1</v>
       </c>
@@ -11600,7 +11601,7 @@
         <v>997.50297899999998</v>
       </c>
     </row>
-    <row r="417" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A417" s="2" t="s">
         <v>1</v>
       </c>
@@ -11652,7 +11653,7 @@
         <v>1484.2561479999999</v>
       </c>
     </row>
-    <row r="419" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A419" s="2" t="s">
         <v>1</v>
       </c>
@@ -11678,7 +11679,7 @@
         <v>1662.150545</v>
       </c>
     </row>
-    <row r="420" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A420" s="2" t="s">
         <v>1</v>
       </c>
@@ -11704,7 +11705,7 @@
         <v>1869.1279850000001</v>
       </c>
     </row>
-    <row r="421" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A421" s="2" t="s">
         <v>1</v>
       </c>
@@ -11730,7 +11731,7 @@
         <v>2325.5938120000001</v>
       </c>
     </row>
-    <row r="422" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A422" s="2" t="s">
         <v>1</v>
       </c>
@@ -11756,7 +11757,7 @@
         <v>2700.4607339999998</v>
       </c>
     </row>
-    <row r="423" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A423" s="2" t="s">
         <v>1</v>
       </c>
@@ -11782,7 +11783,7 @@
         <v>3391.8293789999998</v>
       </c>
     </row>
-    <row r="424" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A424" s="2" t="s">
         <v>1</v>
       </c>
@@ -11808,7 +11809,7 @@
         <v>3801.5943649999999</v>
       </c>
     </row>
-    <row r="425" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A425" s="2" t="s">
         <v>1</v>
       </c>
@@ -11834,7 +11835,7 @@
         <v>4301.9646869999997</v>
       </c>
     </row>
-    <row r="426" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A426" s="2" t="s">
         <v>1</v>
       </c>
@@ -11860,7 +11861,7 @@
         <v>4485.3198350000002</v>
       </c>
     </row>
-    <row r="427" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A427" s="2" t="s">
         <v>1</v>
       </c>
@@ -11886,7 +11887,7 @@
         <v>3667.9937770000001</v>
       </c>
     </row>
-    <row r="428" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A428" s="2" t="s">
         <v>1</v>
       </c>
@@ -11912,7 +11913,7 @@
         <v>2561.0361870000002</v>
       </c>
     </row>
-    <row r="429" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A429" s="2" t="s">
         <v>1</v>
       </c>
@@ -11938,7 +11939,7 @@
         <v>896.96177399999999</v>
       </c>
     </row>
-    <row r="430" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A430" s="2" t="s">
         <v>1</v>
       </c>
@@ -11964,7 +11965,7 @@
         <v>461.63094000000001</v>
       </c>
     </row>
-    <row r="431" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A431" s="2" t="s">
         <v>1</v>
       </c>
@@ -11990,7 +11991,7 @@
         <v>943.13041099999998</v>
       </c>
     </row>
-    <row r="432" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A432" s="2" t="s">
         <v>1</v>
       </c>
@@ -12042,7 +12043,7 @@
         <v>1419.4265230000001</v>
       </c>
     </row>
-    <row r="434" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A434" s="2" t="s">
         <v>1</v>
       </c>
@@ -12068,7 +12069,7 @@
         <v>1417.7720569999999</v>
       </c>
     </row>
-    <row r="435" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A435" s="2" t="s">
         <v>1</v>
       </c>
@@ -12094,7 +12095,7 @@
         <v>1785.208854</v>
       </c>
     </row>
-    <row r="436" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A436" s="2" t="s">
         <v>1</v>
       </c>
@@ -12120,7 +12121,7 @@
         <v>2122.945475</v>
       </c>
     </row>
-    <row r="437" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A437" s="2" t="s">
         <v>1</v>
       </c>
@@ -12146,7 +12147,7 @@
         <v>2495.5076979999999</v>
       </c>
     </row>
-    <row r="438" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A438" s="2" t="s">
         <v>1</v>
       </c>
@@ -12172,7 +12173,7 @@
         <v>3197.3863120000001</v>
       </c>
     </row>
-    <row r="439" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A439" s="2" t="s">
         <v>1</v>
       </c>
@@ -12198,7 +12199,7 @@
         <v>3527.412257</v>
       </c>
     </row>
-    <row r="440" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A440" s="2" t="s">
         <v>1</v>
       </c>
@@ -12224,7 +12225,7 @@
         <v>3944.0123050000002</v>
       </c>
     </row>
-    <row r="441" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A441" s="2" t="s">
         <v>1</v>
       </c>
@@ -12250,7 +12251,7 @@
         <v>4238.5901889999996</v>
       </c>
     </row>
-    <row r="442" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A442" s="2" t="s">
         <v>1</v>
       </c>
@@ -12276,7 +12277,7 @@
         <v>3709.7188919999999</v>
       </c>
     </row>
-    <row r="443" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A443" s="2" t="s">
         <v>1</v>
       </c>
@@ -12302,7 +12303,7 @@
         <v>2066.9811319999999</v>
       </c>
     </row>
-    <row r="444" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A444" s="2" t="s">
         <v>1</v>
       </c>
@@ -12328,7 +12329,7 @@
         <v>753.64399300000002</v>
       </c>
     </row>
-    <row r="445" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A445" s="2" t="s">
         <v>1</v>
       </c>
@@ -12354,7 +12355,7 @@
         <v>437.23364299999997</v>
       </c>
     </row>
-    <row r="446" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A446" s="2" t="s">
         <v>1</v>
       </c>
@@ -12380,7 +12381,7 @@
         <v>977.90123100000005</v>
       </c>
     </row>
-    <row r="447" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A447" s="2" t="s">
         <v>1</v>
       </c>
@@ -12432,7 +12433,7 @@
         <v>1489.956126</v>
       </c>
     </row>
-    <row r="449" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A449" s="2" t="s">
         <v>1</v>
       </c>
@@ -12458,7 +12459,7 @@
         <v>1335.8036970000001</v>
       </c>
     </row>
-    <row r="450" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A450" s="2" t="s">
         <v>1</v>
       </c>
@@ -12484,7 +12485,7 @@
         <v>1580.4329069999999</v>
       </c>
     </row>
-    <row r="451" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A451" s="2" t="s">
         <v>1</v>
       </c>
@@ -12510,7 +12511,7 @@
         <v>2136.3993909999999</v>
       </c>
     </row>
-    <row r="452" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A452" s="2" t="s">
         <v>1</v>
       </c>
@@ -12536,7 +12537,7 @@
         <v>2496.188791</v>
       </c>
     </row>
-    <row r="453" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A453" s="2" t="s">
         <v>1</v>
       </c>
@@ -12562,7 +12563,7 @@
         <v>3645.109633</v>
       </c>
     </row>
-    <row r="454" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A454" s="2" t="s">
         <v>1</v>
       </c>
@@ -12588,7 +12589,7 @@
         <v>3909.8605120000002</v>
       </c>
     </row>
-    <row r="455" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A455" s="2" t="s">
         <v>1</v>
       </c>
@@ -12614,7 +12615,7 @@
         <v>4654.6172390000002</v>
       </c>
     </row>
-    <row r="456" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A456" s="2" t="s">
         <v>1</v>
       </c>
@@ -12640,7 +12641,7 @@
         <v>4530.8892260000002</v>
       </c>
     </row>
-    <row r="457" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A457" s="2" t="s">
         <v>1</v>
       </c>
@@ -12666,7 +12667,7 @@
         <v>3967.5030240000001</v>
       </c>
     </row>
-    <row r="458" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A458" s="2" t="s">
         <v>1</v>
       </c>
@@ -12692,7 +12693,7 @@
         <v>2567.4790119999998</v>
       </c>
     </row>
-    <row r="459" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A459" s="2" t="s">
         <v>1</v>
       </c>
@@ -12718,7 +12719,7 @@
         <v>992.65407600000003</v>
       </c>
     </row>
-    <row r="460" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A460" s="2" t="s">
         <v>1</v>
       </c>
@@ -12744,7 +12745,7 @@
         <v>483.20663000000002</v>
       </c>
     </row>
-    <row r="461" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A461" s="2" t="s">
         <v>1</v>
       </c>
@@ -12770,7 +12771,7 @@
         <v>971.27779799999996</v>
       </c>
     </row>
-    <row r="462" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A462" s="2" t="s">
         <v>1</v>
       </c>
@@ -12822,7 +12823,7 @@
         <v>1601.0309580000001</v>
       </c>
     </row>
-    <row r="464" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A464" s="2" t="s">
         <v>1</v>
       </c>
@@ -12848,7 +12849,7 @@
         <v>1639.8365060000001</v>
       </c>
     </row>
-    <row r="465" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A465" s="2" t="s">
         <v>1</v>
       </c>
@@ -12874,7 +12875,7 @@
         <v>1531.7499419999999</v>
       </c>
     </row>
-    <row r="466" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A466" s="2" t="s">
         <v>1</v>
       </c>
@@ -12900,7 +12901,7 @@
         <v>2043.000536</v>
       </c>
     </row>
-    <row r="467" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A467" s="2" t="s">
         <v>1</v>
       </c>
@@ -12926,7 +12927,7 @@
         <v>2293.6396260000001</v>
       </c>
     </row>
-    <row r="468" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A468" s="2" t="s">
         <v>1</v>
       </c>
@@ -12952,7 +12953,7 @@
         <v>3501.043917</v>
       </c>
     </row>
-    <row r="469" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A469" s="2" t="s">
         <v>1</v>
       </c>
@@ -12978,7 +12979,7 @@
         <v>3756.5668489999998</v>
       </c>
     </row>
-    <row r="470" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A470" s="2" t="s">
         <v>1</v>
       </c>
@@ -13004,7 +13005,7 @@
         <v>4771.7482069999996</v>
       </c>
     </row>
-    <row r="471" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A471" s="2" t="s">
         <v>1</v>
       </c>
@@ -13030,7 +13031,7 @@
         <v>4592.8168290000003</v>
       </c>
     </row>
-    <row r="472" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A472" s="2" t="s">
         <v>1</v>
       </c>
@@ -13056,7 +13057,7 @@
         <v>3917.829209</v>
       </c>
     </row>
-    <row r="473" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A473" s="2" t="s">
         <v>1</v>
       </c>
@@ -13082,7 +13083,7 @@
         <v>2382.3844049999998</v>
       </c>
     </row>
-    <row r="474" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A474" s="2" t="s">
         <v>1</v>
       </c>
@@ -13108,7 +13109,7 @@
         <v>672.16639699999996</v>
       </c>
     </row>
-    <row r="475" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A475" s="2" t="s">
         <v>1</v>
       </c>
@@ -13134,7 +13135,7 @@
         <v>391.29756400000002</v>
       </c>
     </row>
-    <row r="476" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A476" s="2" t="s">
         <v>1</v>
       </c>
@@ -13160,7 +13161,7 @@
         <v>915.29615100000001</v>
       </c>
     </row>
-    <row r="477" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A477" s="2" t="s">
         <v>1</v>
       </c>
@@ -13212,7 +13213,7 @@
         <v>1574.421861</v>
       </c>
     </row>
-    <row r="479" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A479" s="2" t="s">
         <v>1</v>
       </c>
@@ -13238,7 +13239,7 @@
         <v>1527.690965</v>
       </c>
     </row>
-    <row r="480" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A480" s="2" t="s">
         <v>1</v>
       </c>
@@ -13264,7 +13265,7 @@
         <v>1474.607573</v>
       </c>
     </row>
-    <row r="481" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A481" s="2" t="s">
         <v>1</v>
       </c>
@@ -13290,7 +13291,7 @@
         <v>1934.689625</v>
       </c>
     </row>
-    <row r="482" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A482" s="2" t="s">
         <v>1</v>
       </c>
@@ -13316,7 +13317,7 @@
         <v>2422.0278480000002</v>
       </c>
     </row>
-    <row r="483" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A483" s="2" t="s">
         <v>1</v>
       </c>
@@ -13342,7 +13343,7 @@
         <v>3399.1301960000001</v>
       </c>
     </row>
-    <row r="484" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A484" s="2" t="s">
         <v>1</v>
       </c>
@@ -13368,7 +13369,7 @@
         <v>3674.4949019999999</v>
       </c>
     </row>
-    <row r="485" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A485" s="2" t="s">
         <v>1</v>
       </c>
@@ -13394,7 +13395,7 @@
         <v>4403.3884509999998</v>
       </c>
     </row>
-    <row r="486" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A486" s="2" t="s">
         <v>1</v>
       </c>
@@ -13420,7 +13421,7 @@
         <v>4531.7758880000001</v>
       </c>
     </row>
-    <row r="487" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A487" s="2" t="s">
         <v>1</v>
       </c>
@@ -13446,7 +13447,7 @@
         <v>3924.2309019999998</v>
       </c>
     </row>
-    <row r="488" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A488" s="2" t="s">
         <v>1</v>
       </c>
@@ -13472,7 +13473,7 @@
         <v>2453.7728870000001</v>
       </c>
     </row>
-    <row r="489" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A489" s="2" t="s">
         <v>1</v>
       </c>
@@ -13498,7 +13499,7 @@
         <v>757.85919799999999</v>
       </c>
     </row>
-    <row r="490" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A490" s="2" t="s">
         <v>1</v>
       </c>
@@ -13524,7 +13525,7 @@
         <v>310.64345300000002</v>
       </c>
     </row>
-    <row r="491" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A491" s="2" t="s">
         <v>1</v>
       </c>
@@ -13550,7 +13551,7 @@
         <v>756.88044000000002</v>
       </c>
     </row>
-    <row r="492" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A492" s="2" t="s">
         <v>1</v>
       </c>
@@ -13602,7 +13603,7 @@
         <v>1439.183923</v>
       </c>
     </row>
-    <row r="494" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A494" s="2" t="s">
         <v>1</v>
       </c>
@@ -13628,7 +13629,7 @@
         <v>1578.3720599999999</v>
       </c>
     </row>
-    <row r="495" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A495" s="2" t="s">
         <v>1</v>
       </c>
@@ -13654,7 +13655,7 @@
         <v>1581.399371</v>
       </c>
     </row>
-    <row r="496" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A496" s="2" t="s">
         <v>1</v>
       </c>
@@ -13680,7 +13681,7 @@
         <v>2102.6946240000002</v>
       </c>
     </row>
-    <row r="497" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A497" s="2" t="s">
         <v>1</v>
       </c>
@@ -13706,7 +13707,7 @@
         <v>2396.2831799999999</v>
       </c>
     </row>
-    <row r="498" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A498" s="2" t="s">
         <v>1</v>
       </c>
@@ -13732,7 +13733,7 @@
         <v>3402.2784820000002</v>
       </c>
     </row>
-    <row r="499" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A499" s="2" t="s">
         <v>1</v>
       </c>
@@ -13758,7 +13759,7 @@
         <v>3631.2246300000002</v>
       </c>
     </row>
-    <row r="500" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A500" s="2" t="s">
         <v>1</v>
       </c>
@@ -13784,7 +13785,7 @@
         <v>4207.1273359999996</v>
       </c>
     </row>
-    <row r="501" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A501" s="2" t="s">
         <v>1</v>
       </c>
@@ -13810,7 +13811,7 @@
         <v>4042.8591000000001</v>
       </c>
     </row>
-    <row r="502" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A502" s="2" t="s">
         <v>1</v>
       </c>
@@ -13836,7 +13837,7 @@
         <v>3705.895074</v>
       </c>
     </row>
-    <row r="503" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A503" s="2" t="s">
         <v>1</v>
       </c>
@@ -13862,7 +13863,7 @@
         <v>2015.160112</v>
       </c>
     </row>
-    <row r="504" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A504" s="2" t="s">
         <v>1</v>
       </c>
@@ -13888,7 +13889,7 @@
         <v>781.06213700000001</v>
       </c>
     </row>
-    <row r="505" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A505" s="2" t="s">
         <v>1</v>
       </c>
@@ -13914,7 +13915,7 @@
         <v>336.36402299999997</v>
       </c>
     </row>
-    <row r="506" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A506" s="2" t="s">
         <v>1</v>
       </c>
@@ -13940,7 +13941,7 @@
         <v>1042.036499</v>
       </c>
     </row>
-    <row r="507" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A507" s="2" t="s">
         <v>1</v>
       </c>
@@ -13992,7 +13993,7 @@
         <v>1402.5567470000001</v>
       </c>
     </row>
-    <row r="509" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A509" s="2" t="s">
         <v>1</v>
       </c>
@@ -14018,7 +14019,7 @@
         <v>1579.661932</v>
       </c>
     </row>
-    <row r="510" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A510" s="2" t="s">
         <v>1</v>
       </c>
@@ -14044,7 +14045,7 @@
         <v>1447.4340199999999</v>
       </c>
     </row>
-    <row r="511" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A511" s="2" t="s">
         <v>1</v>
       </c>
@@ -14070,7 +14071,7 @@
         <v>2050.5223919999999</v>
       </c>
     </row>
-    <row r="512" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A512" s="2" t="s">
         <v>1</v>
       </c>
@@ -14096,7 +14097,7 @@
         <v>2610.3542889999999</v>
       </c>
     </row>
-    <row r="513" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A513" s="2" t="s">
         <v>1</v>
       </c>
@@ -14122,7 +14123,7 @@
         <v>3174.0727929999998</v>
       </c>
     </row>
-    <row r="514" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A514" s="2" t="s">
         <v>1</v>
       </c>
@@ -14148,7 +14149,7 @@
         <v>3258.1104529999998</v>
       </c>
     </row>
-    <row r="515" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A515" s="2" t="s">
         <v>1</v>
       </c>
@@ -14174,7 +14175,7 @@
         <v>3980.3658380000002</v>
       </c>
     </row>
-    <row r="516" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A516" s="2" t="s">
         <v>1</v>
       </c>
@@ -14200,7 +14201,7 @@
         <v>4046.4364780000001</v>
       </c>
     </row>
-    <row r="517" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A517" s="2" t="s">
         <v>1</v>
       </c>
@@ -14226,7 +14227,7 @@
         <v>3968.8698639999998</v>
       </c>
     </row>
-    <row r="518" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A518" s="2" t="s">
         <v>1</v>
       </c>
@@ -14252,7 +14253,7 @@
         <v>2415.0965190000002</v>
       </c>
     </row>
-    <row r="519" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A519" s="2" t="s">
         <v>1</v>
       </c>
@@ -14278,7 +14279,7 @@
         <v>765.66647399999999</v>
       </c>
     </row>
-    <row r="520" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A520" s="2" t="s">
         <v>1</v>
       </c>
@@ -14304,7 +14305,7 @@
         <v>467.73619100000002</v>
       </c>
     </row>
-    <row r="521" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A521" s="2" t="s">
         <v>1</v>
       </c>
@@ -14330,7 +14331,7 @@
         <v>988.10147600000005</v>
       </c>
     </row>
-    <row r="522" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A522" s="2" t="s">
         <v>1</v>
       </c>
@@ -14382,7 +14383,7 @@
         <v>1496.0022839999999</v>
       </c>
     </row>
-    <row r="524" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A524" s="2" t="s">
         <v>1</v>
       </c>
@@ -14408,7 +14409,7 @@
         <v>1676.8810350000001</v>
       </c>
     </row>
-    <row r="525" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A525" s="2" t="s">
         <v>1</v>
       </c>
@@ -14434,7 +14435,7 @@
         <v>1707.0963810000001</v>
       </c>
     </row>
-    <row r="526" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A526" s="2" t="s">
         <v>1</v>
       </c>
@@ -14460,7 +14461,7 @@
         <v>2294.5042939999998</v>
       </c>
     </row>
-    <row r="527" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A527" s="2" t="s">
         <v>1</v>
       </c>
@@ -14486,7 +14487,7 @@
         <v>2821.283782</v>
       </c>
     </row>
-    <row r="528" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A528" s="2" t="s">
         <v>1</v>
       </c>
@@ -14512,7 +14513,7 @@
         <v>3025.7174110000001</v>
       </c>
     </row>
-    <row r="529" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A529" s="2" t="s">
         <v>1</v>
       </c>
@@ -14538,7 +14539,7 @@
         <v>3683.2942870000002</v>
       </c>
     </row>
-    <row r="530" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A530" s="2" t="s">
         <v>1</v>
       </c>
@@ -14564,7 +14565,7 @@
         <v>4446.6614079999999</v>
       </c>
     </row>
-    <row r="531" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A531" s="2" t="s">
         <v>1</v>
       </c>
@@ -14590,7 +14591,7 @@
         <v>4555.9201409999996</v>
       </c>
     </row>
-    <row r="532" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A532" s="2" t="s">
         <v>1</v>
       </c>
@@ -14616,7 +14617,7 @@
         <v>4066.8153459999999</v>
       </c>
     </row>
-    <row r="533" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A533" s="2" t="s">
         <v>1</v>
       </c>
@@ -14642,7 +14643,7 @@
         <v>2776.0214030000002</v>
       </c>
     </row>
-    <row r="534" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A534" s="2" t="s">
         <v>1</v>
       </c>
@@ -14668,7 +14669,7 @@
         <v>1031.1554639999999</v>
       </c>
     </row>
-    <row r="535" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A535" s="2" t="s">
         <v>1</v>
       </c>
@@ -14694,7 +14695,7 @@
         <v>458.34775400000001</v>
       </c>
     </row>
-    <row r="536" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A536" s="2" t="s">
         <v>1</v>
       </c>
@@ -14720,7 +14721,7 @@
         <v>1028.5391629999999</v>
       </c>
     </row>
-    <row r="537" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A537" s="2" t="s">
         <v>1</v>
       </c>
@@ -14772,7 +14773,7 @@
         <v>1562.5637409999999</v>
       </c>
     </row>
-    <row r="539" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A539" s="2" t="s">
         <v>1</v>
       </c>
@@ -14798,7 +14799,7 @@
         <v>1461.488257</v>
       </c>
     </row>
-    <row r="540" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A540" s="2" t="s">
         <v>1</v>
       </c>
@@ -14824,7 +14825,7 @@
         <v>1485.4783110000001</v>
       </c>
     </row>
-    <row r="541" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A541" s="2" t="s">
         <v>1</v>
       </c>
@@ -14850,7 +14851,7 @@
         <v>1883.06369</v>
       </c>
     </row>
-    <row r="542" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A542" s="2" t="s">
         <v>1</v>
       </c>
@@ -14876,7 +14877,7 @@
         <v>2363.6866839999998</v>
       </c>
     </row>
-    <row r="543" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A543" s="2" t="s">
         <v>1</v>
       </c>
@@ -14902,7 +14903,7 @@
         <v>3172.2694670000001</v>
       </c>
     </row>
-    <row r="544" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A544" s="2" t="s">
         <v>1</v>
       </c>
@@ -14928,7 +14929,7 @@
         <v>3436.2019869999999</v>
       </c>
     </row>
-    <row r="545" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A545" s="2" t="s">
         <v>1</v>
       </c>
@@ -14954,7 +14955,7 @@
         <v>4059.6580300000001</v>
       </c>
     </row>
-    <row r="546" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A546" s="2" t="s">
         <v>1</v>
       </c>
@@ -14980,7 +14981,7 @@
         <v>4374.4823420000002</v>
       </c>
     </row>
-    <row r="547" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A547" s="2" t="s">
         <v>1</v>
       </c>
@@ -15006,7 +15007,7 @@
         <v>3824.230935</v>
       </c>
     </row>
-    <row r="548" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A548" s="2" t="s">
         <v>1</v>
       </c>
@@ -15032,7 +15033,7 @@
         <v>2364.933141</v>
       </c>
     </row>
-    <row r="549" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A549" s="2" t="s">
         <v>1</v>
       </c>
@@ -15058,7 +15059,7 @@
         <v>739.74610499999994</v>
       </c>
     </row>
-    <row r="550" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A550" s="2" t="s">
         <v>1</v>
       </c>
@@ -15084,7 +15085,7 @@
         <v>459.20778200000001</v>
       </c>
     </row>
-    <row r="551" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A551" s="2" t="s">
         <v>1</v>
       </c>
@@ -15136,7 +15137,7 @@
         <v>1441.304954</v>
       </c>
     </row>
-    <row r="553" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A553" s="2" t="s">
         <v>1</v>
       </c>
@@ -15162,7 +15163,7 @@
         <v>1599.847925</v>
       </c>
     </row>
-    <row r="554" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A554" s="2" t="s">
         <v>1</v>
       </c>
@@ -15188,7 +15189,7 @@
         <v>1487.415493</v>
       </c>
     </row>
-    <row r="555" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A555" s="2" t="s">
         <v>1</v>
       </c>
@@ -15214,7 +15215,7 @@
         <v>1984.2137090000001</v>
       </c>
     </row>
-    <row r="556" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A556" s="2" t="s">
         <v>1</v>
       </c>
@@ -15240,7 +15241,7 @@
         <v>2337.093969</v>
       </c>
     </row>
-    <row r="557" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A557" s="2" t="s">
         <v>1</v>
       </c>
@@ -15266,7 +15267,7 @@
         <v>2935.1661989999998</v>
       </c>
     </row>
-    <row r="558" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A558" s="2" t="s">
         <v>1</v>
       </c>
@@ -15292,7 +15293,7 @@
         <v>3398.039988</v>
       </c>
     </row>
-    <row r="559" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A559" s="2" t="s">
         <v>1</v>
       </c>
@@ -15318,7 +15319,7 @@
         <v>3941.4985710000001</v>
       </c>
     </row>
-    <row r="560" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A560" s="2" t="s">
         <v>1</v>
       </c>
@@ -15344,7 +15345,7 @@
         <v>3854.8877149999998</v>
       </c>
     </row>
-    <row r="561" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A561" s="2" t="s">
         <v>1</v>
       </c>
@@ -15370,7 +15371,7 @@
         <v>3780.1327999999999</v>
       </c>
     </row>
-    <row r="562" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A562" s="2" t="s">
         <v>1</v>
       </c>
@@ -15396,7 +15397,7 @@
         <v>2656.725719</v>
       </c>
     </row>
-    <row r="563" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A563" s="2" t="s">
         <v>1</v>
       </c>
@@ -15422,7 +15423,7 @@
         <v>961.78833899999995</v>
       </c>
     </row>
-    <row r="564" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A564" s="2" t="s">
         <v>1</v>
       </c>
@@ -15448,7 +15449,7 @@
         <v>378.02901400000002</v>
       </c>
     </row>
-    <row r="565" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A565" s="2" t="s">
         <v>1</v>
       </c>
@@ -15474,7 +15475,7 @@
         <v>891.24934800000005</v>
       </c>
     </row>
-    <row r="566" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A566" s="2" t="s">
         <v>1</v>
       </c>
@@ -15526,7 +15527,7 @@
         <v>1456.0952480000001</v>
       </c>
     </row>
-    <row r="568" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A568" s="2" t="s">
         <v>1</v>
       </c>
@@ -15552,7 +15553,7 @@
         <v>1510.0682360000001</v>
       </c>
     </row>
-    <row r="569" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A569" s="2" t="s">
         <v>1</v>
       </c>
@@ -15578,7 +15579,7 @@
         <v>1571.0778519999999</v>
       </c>
     </row>
-    <row r="570" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A570" s="2" t="s">
         <v>1</v>
       </c>
@@ -15604,7 +15605,7 @@
         <v>1957.1621359999999</v>
       </c>
     </row>
-    <row r="571" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A571" s="2" t="s">
         <v>1</v>
       </c>
@@ -15630,7 +15631,7 @@
         <v>2529.0673740000002</v>
       </c>
     </row>
-    <row r="572" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A572" s="2" t="s">
         <v>1</v>
       </c>
@@ -15656,7 +15657,7 @@
         <v>2959.3543410000002</v>
       </c>
     </row>
-    <row r="573" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A573" s="2" t="s">
         <v>1</v>
       </c>
@@ -15682,7 +15683,7 @@
         <v>3449.3311669999998</v>
       </c>
     </row>
-    <row r="574" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A574" s="2" t="s">
         <v>1</v>
       </c>
@@ -15708,7 +15709,7 @@
         <v>4400.0647440000002</v>
       </c>
     </row>
-    <row r="575" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A575" s="2" t="s">
         <v>1</v>
       </c>
@@ -15734,7 +15735,7 @@
         <v>4279.028182</v>
       </c>
     </row>
-    <row r="576" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A576" s="2" t="s">
         <v>1</v>
       </c>
@@ -15760,7 +15761,7 @@
         <v>3710.439989</v>
       </c>
     </row>
-    <row r="577" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A577" s="2" t="s">
         <v>1</v>
       </c>
@@ -15786,7 +15787,7 @@
         <v>1943.568614</v>
       </c>
     </row>
-    <row r="578" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A578" s="2" t="s">
         <v>1</v>
       </c>
@@ -15812,7 +15813,7 @@
         <v>790.62257</v>
       </c>
     </row>
-    <row r="579" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A579" s="2" t="s">
         <v>1</v>
       </c>
@@ -15838,7 +15839,7 @@
         <v>442.69081</v>
       </c>
     </row>
-    <row r="580" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A580" s="2" t="s">
         <v>1</v>
       </c>
@@ -15864,7 +15865,7 @@
         <v>1012.67053</v>
       </c>
     </row>
-    <row r="581" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A581" s="2" t="s">
         <v>1</v>
       </c>
@@ -15907,7 +15908,7 @@
         <v>0.50002314814814797</v>
       </c>
       <c r="F582" s="2" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="G582" s="2">
         <v>1</v>
@@ -15916,7 +15917,7 @@
         <v>1324.021788</v>
       </c>
     </row>
-    <row r="583" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A583" s="2" t="s">
         <v>1</v>
       </c>
@@ -15942,7 +15943,7 @@
         <v>1408.2656280000001</v>
       </c>
     </row>
-    <row r="584" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A584" s="2" t="s">
         <v>1</v>
       </c>
@@ -15968,7 +15969,7 @@
         <v>1654.486195</v>
       </c>
     </row>
-    <row r="585" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A585" s="2" t="s">
         <v>1</v>
       </c>
@@ -15994,7 +15995,7 @@
         <v>2143.0432110000002</v>
       </c>
     </row>
-    <row r="586" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A586" s="2" t="s">
         <v>1</v>
       </c>
@@ -16020,7 +16021,7 @@
         <v>2613.7135320000002</v>
       </c>
     </row>
-    <row r="587" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A587" s="2" t="s">
         <v>1</v>
       </c>
@@ -16046,7 +16047,7 @@
         <v>3202.1952689999998</v>
       </c>
     </row>
-    <row r="588" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A588" s="2" t="s">
         <v>1</v>
       </c>
@@ -16072,7 +16073,7 @@
         <v>3599.8375489999999</v>
       </c>
     </row>
-    <row r="589" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A589" s="2" t="s">
         <v>1</v>
       </c>
@@ -16098,7 +16099,7 @@
         <v>4246.1243270000004</v>
       </c>
     </row>
-    <row r="590" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A590" s="2" t="s">
         <v>1</v>
       </c>
@@ -16124,7 +16125,7 @@
         <v>4102.0695759999999</v>
       </c>
     </row>
-    <row r="591" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A591" s="2" t="s">
         <v>1</v>
       </c>
@@ -16150,7 +16151,7 @@
         <v>3926.6490450000001</v>
       </c>
     </row>
-    <row r="592" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A592" s="2" t="s">
         <v>1</v>
       </c>
@@ -16176,7 +16177,7 @@
         <v>2294.1847779999998</v>
       </c>
     </row>
-    <row r="593" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A593" s="2" t="s">
         <v>1</v>
       </c>
@@ -16202,7 +16203,7 @@
         <v>833.88472100000001</v>
       </c>
     </row>
-    <row r="594" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A594" s="2" t="s">
         <v>1</v>
       </c>
@@ -16228,7 +16229,7 @@
         <v>440.96163799999999</v>
       </c>
     </row>
-    <row r="595" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A595" s="2" t="s">
         <v>1</v>
       </c>
@@ -16254,7 +16255,7 @@
         <v>1053.3430820000001</v>
       </c>
     </row>
-    <row r="596" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A596" s="2" t="s">
         <v>1</v>
       </c>
@@ -16297,7 +16298,7 @@
         <v>0.50003472222222201</v>
       </c>
       <c r="F597" s="2" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="G597" s="2">
         <v>1</v>
@@ -16306,7 +16307,7 @@
         <v>1412.618072</v>
       </c>
     </row>
-    <row r="598" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A598" s="2" t="s">
         <v>1</v>
       </c>
@@ -16332,7 +16333,7 @@
         <v>1460.9776670000001</v>
       </c>
     </row>
-    <row r="599" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A599" s="2" t="s">
         <v>1</v>
       </c>
@@ -16358,7 +16359,7 @@
         <v>1768.670339</v>
       </c>
     </row>
-    <row r="600" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A600" s="2" t="s">
         <v>1</v>
       </c>
@@ -16384,7 +16385,7 @@
         <v>2122.5178179999998</v>
       </c>
     </row>
-    <row r="601" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A601" s="2" t="s">
         <v>1</v>
       </c>
@@ -16410,7 +16411,7 @@
         <v>2709.5500529999999</v>
       </c>
     </row>
-    <row r="602" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A602" s="2" t="s">
         <v>1</v>
       </c>
@@ -16436,7 +16437,7 @@
         <v>3481.6153730000001</v>
       </c>
     </row>
-    <row r="603" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A603" s="2" t="s">
         <v>1</v>
       </c>
@@ -16462,7 +16463,7 @@
         <v>3791.196762</v>
       </c>
     </row>
-    <row r="604" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A604" s="2" t="s">
         <v>1</v>
       </c>
@@ -16488,7 +16489,7 @@
         <v>4375.0133740000001</v>
       </c>
     </row>
-    <row r="605" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A605" s="2" t="s">
         <v>1</v>
       </c>
@@ -16514,7 +16515,7 @@
         <v>4494.912448</v>
       </c>
     </row>
-    <row r="606" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A606" s="2" t="s">
         <v>1</v>
       </c>
@@ -16540,7 +16541,7 @@
         <v>3831.1252300000001</v>
       </c>
     </row>
-    <row r="607" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A607" s="2" t="s">
         <v>1</v>
       </c>
@@ -16566,7 +16567,7 @@
         <v>2277.9633079999999</v>
       </c>
     </row>
-    <row r="608" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:8" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A608" s="2" t="s">
         <v>1</v>
       </c>
@@ -16593,6 +16594,14 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H608" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="HOY"/>
+        <filter val="HOY CELEBREMOS"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -16608,63 +16617,63 @@
   <sheetData>
     <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>3</v>
@@ -16672,114 +16681,114 @@
     </row>
     <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="6"/>
       <c r="B16" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="6"/>
       <c r="B17" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="6"/>
       <c r="B18" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="6"/>
       <c r="B19" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="6"/>
       <c r="B20" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="6"/>
       <c r="B22" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="6"/>
       <c r="B23" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="6"/>
       <c r="B24" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/Programmes Seguimiento LE_2.xlsx
+++ b/Programmes Seguimiento LE_2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Seguimiento-LE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49814366-2DD2-42B3-8038-326E44BD50D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81B4C41D-749B-4630-8529-DEB359F1060F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CON-Las Estrellas" sheetId="2" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1869" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1869" uniqueCount="70">
   <si>
     <t>Targets</t>
   </si>
@@ -231,6 +231,9 @@
   </si>
   <si>
     <t xml:space="preserve">	 For Region [National] Universe 78427.2; Sample 6818 ( 100.00% )</t>
+  </si>
+  <si>
+    <t>HOY CELEBREMOS</t>
   </si>
 </sst>
 </file>
@@ -15908,7 +15911,7 @@
         <v>0.50002314814814797</v>
       </c>
       <c r="F582" s="2" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="G582" s="2">
         <v>1</v>
@@ -16298,7 +16301,7 @@
         <v>0.50003472222222201</v>
       </c>
       <c r="F597" s="2" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="G597" s="2">
         <v>1</v>
